--- a/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
+++ b/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
@@ -2078,7 +2078,7 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 10 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:20:f6901d9c28fd2f28, sg:26:fadb8b44cbf92e38, sg:37:82ae8f8f17419cab, sg:39:fbe37ba1a9e2b863, sg:46:1e975a983138ffd6, sg:4:276bdc000eb55277, sg:54:8bcbddcadf8f1734, sg:60:571f52205287dd41, sg:61:d8495b2ca3ac47d7, sg:8:9551f0c4ea887cb2), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 14 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:20:f6901d9c28fd2f28, sg:26:fadb8b44cbf92e38, sg:37:82ae8f8f17419cab, sg:39:fbe37ba1a9e2b863, sg:46:1e975a983138ffd6, sg:4:276bdc000eb55277, sg:54:8bcbddcadf8f1734, sg:60:571f52205287dd41, sg:61:d8495b2ca3ac47d7, sg:67:3b66f7dac01ccd60, sg:75:229d4e17d8b99c62, sg:81:86d629fb715c366a, sg:82:f7cc594a8b2b486b, sg:8:9551f0c4ea887cb2), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F3" s="14" t="n"/>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 10 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:20:f6901d9c28fd2f28, sg:26:fadb8b44cbf92e38, sg:37:82ae8f8f17419cab, sg:39:fbe37ba1a9e2b863, sg:46:1e975a983138ffd6, sg:4:276bdc000eb55277, sg:54:8bcbddcadf8f1734, sg:60:571f52205287dd41, sg:61:d8495b2ca3ac47d7, sg:8:9551f0c4ea887cb2), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 14 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:20:f6901d9c28fd2f28, sg:26:fadb8b44cbf92e38, sg:37:82ae8f8f17419cab, sg:39:fbe37ba1a9e2b863, sg:46:1e975a983138ffd6, sg:4:276bdc000eb55277, sg:54:8bcbddcadf8f1734, sg:60:571f52205287dd41, sg:61:d8495b2ca3ac47d7, sg:67:3b66f7dac01ccd60, sg:75:229d4e17d8b99c62, sg:81:86d629fb715c366a, sg:82:f7cc594a8b2b486b, sg:8:9551f0c4ea887cb2), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F4" s="18" t="n"/>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
-          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 8 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:12:3fd44ffa4a757a26, sg:23:a008c5fa1d367385, sg:27:ec2b4becd7c77e29, sg:36:330695993f562a6e, sg:49:4a65b4cd43d97bea, sg:56:1aa8e8cd7607771c, sg:57:f00a04ac3328aad2, sg:5:c95b7b06e158da45), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 11 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:12:3fd44ffa4a757a26, sg:23:a008c5fa1d367385, sg:27:ec2b4becd7c77e29, sg:36:330695993f562a6e, sg:49:4a65b4cd43d97bea, sg:56:1aa8e8cd7607771c, sg:57:f00a04ac3328aad2, sg:5:c95b7b06e158da45, sg:70:cb61aa7cb8e712da, sg:77:195c3b7af795e666, sg:78:20569b15038d3d77), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F44" s="18" t="n"/>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 8 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:12:3fd44ffa4a757a26, sg:23:a008c5fa1d367385, sg:27:ec2b4becd7c77e29, sg:36:330695993f562a6e, sg:49:4a65b4cd43d97bea, sg:56:1aa8e8cd7607771c, sg:57:f00a04ac3328aad2, sg:5:c95b7b06e158da45), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 11 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:12:3fd44ffa4a757a26, sg:23:a008c5fa1d367385, sg:27:ec2b4becd7c77e29, sg:36:330695993f562a6e, sg:49:4a65b4cd43d97bea, sg:56:1aa8e8cd7607771c, sg:57:f00a04ac3328aad2, sg:5:c95b7b06e158da45, sg:70:cb61aa7cb8e712da, sg:77:195c3b7af795e666, sg:78:20569b15038d3d77), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F45" s="14" t="n"/>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Offline by default: no runtime path performs an external network call unless anchoring is explicitly enabled, and enabling it announces itself. Proven by 5 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:15:bf273856e947ee23, sg:31:e3f89cd814900706, sg:41:7a7f781b465c9908, sg:58:f4c71b0ec7276039, sg:9:8e229db09d9d3bb6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Offline by default: no runtime path performs an external network call unless anchoring is explicitly enabled, and enabling it announces itself. Proven by 7 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:15:bf273856e947ee23, sg:31:e3f89cd814900706, sg:41:7a7f781b465c9908, sg:58:f4c71b0ec7276039, sg:62:840752dcd3002f50, sg:79:b41619813ad4e433, sg:9:8e229db09d9d3bb6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F112" s="18" t="n"/>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Offline by default: no runtime path performs an external network call unless anchoring is explicitly enabled, and enabling it announces itself. Proven by 5 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:15:bf273856e947ee23, sg:31:e3f89cd814900706, sg:41:7a7f781b465c9908, sg:58:f4c71b0ec7276039, sg:9:8e229db09d9d3bb6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Offline by default: no runtime path performs an external network call unless anchoring is explicitly enabled, and enabling it announces itself. Proven by 7 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:15:bf273856e947ee23, sg:31:e3f89cd814900706, sg:41:7a7f781b465c9908, sg:58:f4c71b0ec7276039, sg:62:840752dcd3002f50, sg:79:b41619813ad4e433, sg:9:8e229db09d9d3bb6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F113" s="14" t="n"/>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="E130" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, and the denial names the contributing artifacts; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 17 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:12:3fd44ffa4a757a26, sg:14:0472ec5ce6c5572b, sg:15:bf273856e947ee23, sg:22:57dd6789598beda0, sg:23:a008c5fa1d367385, sg:32:62e9084ac5c23150, sg:33:26603829d8a2d99d, sg:39:fbe37ba1a9e2b863, sg:40:7881257b3bc9ab46, sg:41:7a7f781b465c9908, sg:47:b88eb327a02935ba, sg:48:18e04efd42076c3b, sg:49:4a65b4cd43d97bea, sg:50:bb2e261c780ea83b, sg:55:075d6757ad9fea62, sg:61:d8495b2ca3ac47d7, sg:9:8e229db09d9d3bb6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, and the denial names the contributing artifacts; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 24 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:12:3fd44ffa4a757a26, sg:14:0472ec5ce6c5572b, sg:15:bf273856e947ee23, sg:22:57dd6789598beda0, sg:23:a008c5fa1d367385, sg:32:62e9084ac5c23150, sg:33:26603829d8a2d99d, sg:39:fbe37ba1a9e2b863, sg:40:7881257b3bc9ab46, sg:41:7a7f781b465c9908, sg:47:b88eb327a02935ba, sg:48:18e04efd42076c3b, sg:49:4a65b4cd43d97bea, sg:50:bb2e261c780ea83b, sg:55:075d6757ad9fea62, sg:61:d8495b2ca3ac47d7, sg:62:840752dcd3002f50, sg:68:ec8a054e28749618, sg:69:96cd89574676b8cc, sg:70:cb61aa7cb8e712da, sg:71:6493aa04c046d505, sg:76:298fd8e47c3f66a8, sg:82:f7cc594a8b2b486b, sg:9:8e229db09d9d3bb6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F130" s="18" t="n"/>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>Offline by default: no runtime path performs an external network call unless anchoring is explicitly enabled, and enabling it announces itself. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:31:e3f89cd814900706, sg:58:f4c71b0ec7276039), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Offline by default: no runtime path performs an external network call unless anchoring is explicitly enabled, and enabling it announces itself. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:31:e3f89cd814900706, sg:58:f4c71b0ec7276039, sg:79:b41619813ad4e433), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F203" s="14" t="n"/>
@@ -8223,7 +8223,7 @@
       </c>
       <c r="E204" s="18" t="inlineStr">
         <is>
-          <t>Offline by default: no runtime path performs an external network call unless anchoring is explicitly enabled, and enabling it announces itself. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:31:e3f89cd814900706, sg:58:f4c71b0ec7276039), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Offline by default: no runtime path performs an external network call unless anchoring is explicitly enabled, and enabling it announces itself. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:31:e3f89cd814900706, sg:58:f4c71b0ec7276039, sg:79:b41619813ad4e433), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F204" s="18" t="n"/>
@@ -8669,7 +8669,7 @@
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 13 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:0:0407b42c97ccb566, sg:16:e56ac532d76e2b76, sg:19:b8eed958f59d640e, sg:20:f6901d9c28fd2f28, sg:25:6dffdc5026b552d8, sg:29:6031e40cffa97197, sg:3:52bf36fd30c28c8e, sg:42:329f422d795cf67d, sg:45:885d91082f72292f, sg:46:1e975a983138ffd6, sg:53:1c2c321ec1d637f7, sg:6:610ab1d78e9b6ffe, sg:8:9551f0c4ea887cb2), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 17 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:0:0407b42c97ccb566, sg:16:e56ac532d76e2b76, sg:19:b8eed958f59d640e, sg:20:f6901d9c28fd2f28, sg:25:6dffdc5026b552d8, sg:29:6031e40cffa97197, sg:3:52bf36fd30c28c8e, sg:42:329f422d795cf67d, sg:45:885d91082f72292f, sg:46:1e975a983138ffd6, sg:53:1c2c321ec1d637f7, sg:63:9c080b5b0f116776, sg:66:901b7c2facbb70d7, sg:67:3b66f7dac01ccd60, sg:6:610ab1d78e9b6ffe, sg:74:9ea2a20a2cf96f5e, sg:8:9551f0c4ea887cb2), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F219" s="14" t="n"/>
@@ -8717,7 +8717,7 @@
       </c>
       <c r="E220" s="18" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 13 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:0:0407b42c97ccb566, sg:16:e56ac532d76e2b76, sg:19:b8eed958f59d640e, sg:20:f6901d9c28fd2f28, sg:25:6dffdc5026b552d8, sg:29:6031e40cffa97197, sg:3:52bf36fd30c28c8e, sg:42:329f422d795cf67d, sg:45:885d91082f72292f, sg:46:1e975a983138ffd6, sg:53:1c2c321ec1d637f7, sg:6:610ab1d78e9b6ffe, sg:8:9551f0c4ea887cb2), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 17 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:0:0407b42c97ccb566, sg:16:e56ac532d76e2b76, sg:19:b8eed958f59d640e, sg:20:f6901d9c28fd2f28, sg:25:6dffdc5026b552d8, sg:29:6031e40cffa97197, sg:3:52bf36fd30c28c8e, sg:42:329f422d795cf67d, sg:45:885d91082f72292f, sg:46:1e975a983138ffd6, sg:53:1c2c321ec1d637f7, sg:63:9c080b5b0f116776, sg:66:901b7c2facbb70d7, sg:67:3b66f7dac01ccd60, sg:6:610ab1d78e9b6ffe, sg:74:9ea2a20a2cf96f5e, sg:8:9551f0c4ea887cb2), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F220" s="18" t="n"/>
@@ -8990,7 +8990,7 @@
       </c>
       <c r="E229" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; The recorder is not reachable by the agent it records: PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 15 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:0:0407b42c97ccb566, sg:16:e56ac532d76e2b76, sg:17:abd9cb98a7931aac, sg:18:0a53a808e1826a22, sg:1:2da04769bddc3d6b, sg:28:3d79c978f5f94865, sg:2:3a6ad16a3f7b631b, sg:33:26603829d8a2d99d, sg:35:a32f87f5a73d99c7, sg:42:329f422d795cf67d, sg:43:f2f5bee2bc12f523, sg:44:5524171aae0946b5, sg:52:2e7f22f8c6c1a019, sg:55:075d6757ad9fea62, sg:59:d3094004aa13722e), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; The recorder is not reachable by the agent it records: PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 21 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:0:0407b42c97ccb566, sg:16:e56ac532d76e2b76, sg:17:abd9cb98a7931aac, sg:18:0a53a808e1826a22, sg:1:2da04769bddc3d6b, sg:28:3d79c978f5f94865, sg:2:3a6ad16a3f7b631b, sg:33:26603829d8a2d99d, sg:35:a32f87f5a73d99c7, sg:42:329f422d795cf67d, sg:43:f2f5bee2bc12f523, sg:44:5524171aae0946b5, sg:52:2e7f22f8c6c1a019, sg:55:075d6757ad9fea62, sg:59:d3094004aa13722e, sg:63:9c080b5b0f116776, sg:64:a3b27f1c9b025094, sg:65:ce198ee91ed4866c, sg:73:32e817ccb1c5e3ff, sg:76:298fd8e47c3f66a8, sg:80:3a06820ff0a3b2dc), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F229" s="14" t="n"/>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="E255" s="14" t="inlineStr">
         <is>
-          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:32:62e9084ac5c23150, sg:50:bb2e261c780ea83b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:32:62e9084ac5c23150, sg:50:bb2e261c780ea83b, sg:71:6493aa04c046d505), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F255" s="14" t="n"/>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="E256" s="18" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:25:6dffdc5026b552d8, sg:29:6031e40cffa97197, sg:3:52bf36fd30c28c8e, sg:53:1c2c321ec1d637f7), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 5 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:25:6dffdc5026b552d8, sg:29:6031e40cffa97197, sg:3:52bf36fd30c28c8e, sg:53:1c2c321ec1d637f7, sg:74:9ea2a20a2cf96f5e), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F256" s="18" t="n"/>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="E257" s="14" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:25:6dffdc5026b552d8, sg:29:6031e40cffa97197, sg:3:52bf36fd30c28c8e, sg:53:1c2c321ec1d637f7), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 5 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:25:6dffdc5026b552d8, sg:29:6031e40cffa97197, sg:3:52bf36fd30c28c8e, sg:53:1c2c321ec1d637f7, sg:74:9ea2a20a2cf96f5e), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F257" s="14" t="n"/>

--- a/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
+++ b/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
@@ -2078,7 +2078,7 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 14 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:20:f6901d9c28fd2f28, sg:26:fadb8b44cbf92e38, sg:37:82ae8f8f17419cab, sg:39:fbe37ba1a9e2b863, sg:46:1e975a983138ffd6, sg:4:276bdc000eb55277, sg:54:8bcbddcadf8f1734, sg:60:571f52205287dd41, sg:61:d8495b2ca3ac47d7, sg:67:3b66f7dac01ccd60, sg:75:229d4e17d8b99c62, sg:81:86d629fb715c366a, sg:82:f7cc594a8b2b486b, sg:8:9551f0c4ea887cb2), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 22 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:102:1a57e64be953671e, sg:103:e8b6c17e04be0f76, sg:110:d3eefe3d8c5969ee, sg:118:47340dfd38fcee2d, sg:124:24bb2fd033133be1, sg:125:6861749dc0b73d3f, sg:20:f6901d9c28fd2f28, sg:26:fadb8b44cbf92e38, sg:37:82ae8f8f17419cab, sg:39:fbe37ba1a9e2b863, sg:46:1e975a983138ffd6, sg:4:276bdc000eb55277, sg:54:8bcbddcadf8f1734, sg:60:571f52205287dd41, sg:61:d8495b2ca3ac47d7, sg:67:3b66f7dac01ccd60, sg:75:229d4e17d8b99c62, sg:81:86d629fb715c366a, sg:82:f7cc594a8b2b486b, sg:88:cad0d4f39c0423ca, sg:8:9551f0c4ea887cb2, sg:96:562d8d258251e9fe), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F3" s="14" t="n"/>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 14 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:20:f6901d9c28fd2f28, sg:26:fadb8b44cbf92e38, sg:37:82ae8f8f17419cab, sg:39:fbe37ba1a9e2b863, sg:46:1e975a983138ffd6, sg:4:276bdc000eb55277, sg:54:8bcbddcadf8f1734, sg:60:571f52205287dd41, sg:61:d8495b2ca3ac47d7, sg:67:3b66f7dac01ccd60, sg:75:229d4e17d8b99c62, sg:81:86d629fb715c366a, sg:82:f7cc594a8b2b486b, sg:8:9551f0c4ea887cb2), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 22 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:102:1a57e64be953671e, sg:103:e8b6c17e04be0f76, sg:110:d3eefe3d8c5969ee, sg:118:47340dfd38fcee2d, sg:124:24bb2fd033133be1, sg:125:6861749dc0b73d3f, sg:20:f6901d9c28fd2f28, sg:26:fadb8b44cbf92e38, sg:37:82ae8f8f17419cab, sg:39:fbe37ba1a9e2b863, sg:46:1e975a983138ffd6, sg:4:276bdc000eb55277, sg:54:8bcbddcadf8f1734, sg:60:571f52205287dd41, sg:61:d8495b2ca3ac47d7, sg:67:3b66f7dac01ccd60, sg:75:229d4e17d8b99c62, sg:81:86d629fb715c366a, sg:82:f7cc594a8b2b486b, sg:88:cad0d4f39c0423ca, sg:8:9551f0c4ea887cb2, sg:96:562d8d258251e9fe), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F4" s="18" t="n"/>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
-          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 11 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:12:3fd44ffa4a757a26, sg:23:a008c5fa1d367385, sg:27:ec2b4becd7c77e29, sg:36:330695993f562a6e, sg:49:4a65b4cd43d97bea, sg:56:1aa8e8cd7607771c, sg:57:f00a04ac3328aad2, sg:5:c95b7b06e158da45, sg:70:cb61aa7cb8e712da, sg:77:195c3b7af795e666, sg:78:20569b15038d3d77), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 17 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:113:8271ad88f2fcd9c6, sg:120:784ba55dad12416e, sg:121:130f6e84f40cfa26, sg:12:3fd44ffa4a757a26, sg:23:a008c5fa1d367385, sg:27:ec2b4becd7c77e29, sg:36:330695993f562a6e, sg:49:4a65b4cd43d97bea, sg:56:1aa8e8cd7607771c, sg:57:f00a04ac3328aad2, sg:5:c95b7b06e158da45, sg:70:cb61aa7cb8e712da, sg:77:195c3b7af795e666, sg:78:20569b15038d3d77, sg:91:36b979feb38418df, sg:98:8a99aa4cd2400d35, sg:99:403b00f65c083d2b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F44" s="18" t="n"/>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 11 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:12:3fd44ffa4a757a26, sg:23:a008c5fa1d367385, sg:27:ec2b4becd7c77e29, sg:36:330695993f562a6e, sg:49:4a65b4cd43d97bea, sg:56:1aa8e8cd7607771c, sg:57:f00a04ac3328aad2, sg:5:c95b7b06e158da45, sg:70:cb61aa7cb8e712da, sg:77:195c3b7af795e666, sg:78:20569b15038d3d77), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 17 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:113:8271ad88f2fcd9c6, sg:120:784ba55dad12416e, sg:121:130f6e84f40cfa26, sg:12:3fd44ffa4a757a26, sg:23:a008c5fa1d367385, sg:27:ec2b4becd7c77e29, sg:36:330695993f562a6e, sg:49:4a65b4cd43d97bea, sg:56:1aa8e8cd7607771c, sg:57:f00a04ac3328aad2, sg:5:c95b7b06e158da45, sg:70:cb61aa7cb8e712da, sg:77:195c3b7af795e666, sg:78:20569b15038d3d77, sg:91:36b979feb38418df, sg:98:8a99aa4cd2400d35, sg:99:403b00f65c083d2b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F45" s="14" t="n"/>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Offline by default: no runtime path performs an external network call unless anchoring is explicitly enabled, and enabling it announces itself. Proven by 7 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:15:bf273856e947ee23, sg:31:e3f89cd814900706, sg:41:7a7f781b465c9908, sg:58:f4c71b0ec7276039, sg:62:840752dcd3002f50, sg:79:b41619813ad4e433, sg:9:8e229db09d9d3bb6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Offline by default: no runtime path performs an external network call unless anchoring is explicitly enabled, and enabling it announces itself. Proven by 11 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:100:45b3fff47c6680f0, sg:105:f03f044029f90661, sg:122:6e1971822861b99a, sg:15:bf273856e947ee23, sg:31:e3f89cd814900706, sg:41:7a7f781b465c9908, sg:58:f4c71b0ec7276039, sg:62:840752dcd3002f50, sg:79:b41619813ad4e433, sg:83:372de70d047ff5b9, sg:9:8e229db09d9d3bb6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F112" s="18" t="n"/>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Offline by default: no runtime path performs an external network call unless anchoring is explicitly enabled, and enabling it announces itself. Proven by 7 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:15:bf273856e947ee23, sg:31:e3f89cd814900706, sg:41:7a7f781b465c9908, sg:58:f4c71b0ec7276039, sg:62:840752dcd3002f50, sg:79:b41619813ad4e433, sg:9:8e229db09d9d3bb6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Offline by default: no runtime path performs an external network call unless anchoring is explicitly enabled, and enabling it announces itself. Proven by 11 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:100:45b3fff47c6680f0, sg:105:f03f044029f90661, sg:122:6e1971822861b99a, sg:15:bf273856e947ee23, sg:31:e3f89cd814900706, sg:41:7a7f781b465c9908, sg:58:f4c71b0ec7276039, sg:62:840752dcd3002f50, sg:79:b41619813ad4e433, sg:83:372de70d047ff5b9, sg:9:8e229db09d9d3bb6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F113" s="14" t="n"/>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="E130" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, and the denial names the contributing artifacts; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 24 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:12:3fd44ffa4a757a26, sg:14:0472ec5ce6c5572b, sg:15:bf273856e947ee23, sg:22:57dd6789598beda0, sg:23:a008c5fa1d367385, sg:32:62e9084ac5c23150, sg:33:26603829d8a2d99d, sg:39:fbe37ba1a9e2b863, sg:40:7881257b3bc9ab46, sg:41:7a7f781b465c9908, sg:47:b88eb327a02935ba, sg:48:18e04efd42076c3b, sg:49:4a65b4cd43d97bea, sg:50:bb2e261c780ea83b, sg:55:075d6757ad9fea62, sg:61:d8495b2ca3ac47d7, sg:62:840752dcd3002f50, sg:68:ec8a054e28749618, sg:69:96cd89574676b8cc, sg:70:cb61aa7cb8e712da, sg:71:6493aa04c046d505, sg:76:298fd8e47c3f66a8, sg:82:f7cc594a8b2b486b, sg:9:8e229db09d9d3bb6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, and the denial names the contributing artifacts; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 38 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:103:e8b6c17e04be0f76, sg:105:f03f044029f90661, sg:111:13f68a28ef715fe1, sg:112:a7e34cfc13937ef6, sg:113:8271ad88f2fcd9c6, sg:114:84532e35fc44e02c, sg:119:1fe284b51575c9ed, sg:125:6861749dc0b73d3f, sg:12:3fd44ffa4a757a26, sg:14:0472ec5ce6c5572b, sg:15:bf273856e947ee23, sg:22:57dd6789598beda0, sg:23:a008c5fa1d367385, sg:32:62e9084ac5c23150, sg:33:26603829d8a2d99d, sg:39:fbe37ba1a9e2b863, sg:40:7881257b3bc9ab46, sg:41:7a7f781b465c9908, sg:47:b88eb327a02935ba, sg:48:18e04efd42076c3b, sg:49:4a65b4cd43d97bea, sg:50:bb2e261c780ea83b, sg:55:075d6757ad9fea62, sg:61:d8495b2ca3ac47d7, sg:62:840752dcd3002f50, sg:68:ec8a054e28749618, sg:69:96cd89574676b8cc, sg:70:cb61aa7cb8e712da, sg:71:6493aa04c046d505, sg:76:298fd8e47c3f66a8, sg:82:f7cc594a8b2b486b, sg:83:372de70d047ff5b9, sg:89:8dca168b634a4a7a, sg:90:cd1c463b43b49e9b, sg:91:36b979feb38418df, sg:92:6902ec516d57670f, sg:97:681acaa39a9bc201, sg:9:8e229db09d9d3bb6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F130" s="18" t="n"/>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>Offline by default: no runtime path performs an external network call unless anchoring is explicitly enabled, and enabling it announces itself. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:31:e3f89cd814900706, sg:58:f4c71b0ec7276039, sg:79:b41619813ad4e433), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Offline by default: no runtime path performs an external network call unless anchoring is explicitly enabled, and enabling it announces itself. Proven by 5 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:100:45b3fff47c6680f0, sg:122:6e1971822861b99a, sg:31:e3f89cd814900706, sg:58:f4c71b0ec7276039, sg:79:b41619813ad4e433), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F203" s="14" t="n"/>
@@ -8223,7 +8223,7 @@
       </c>
       <c r="E204" s="18" t="inlineStr">
         <is>
-          <t>Offline by default: no runtime path performs an external network call unless anchoring is explicitly enabled, and enabling it announces itself. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:31:e3f89cd814900706, sg:58:f4c71b0ec7276039, sg:79:b41619813ad4e433), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Offline by default: no runtime path performs an external network call unless anchoring is explicitly enabled, and enabling it announces itself. Proven by 5 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:100:45b3fff47c6680f0, sg:122:6e1971822861b99a, sg:31:e3f89cd814900706, sg:58:f4c71b0ec7276039, sg:79:b41619813ad4e433), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F204" s="18" t="n"/>
@@ -8669,7 +8669,7 @@
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 17 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:0:0407b42c97ccb566, sg:16:e56ac532d76e2b76, sg:19:b8eed958f59d640e, sg:20:f6901d9c28fd2f28, sg:25:6dffdc5026b552d8, sg:29:6031e40cffa97197, sg:3:52bf36fd30c28c8e, sg:42:329f422d795cf67d, sg:45:885d91082f72292f, sg:46:1e975a983138ffd6, sg:53:1c2c321ec1d637f7, sg:63:9c080b5b0f116776, sg:66:901b7c2facbb70d7, sg:67:3b66f7dac01ccd60, sg:6:610ab1d78e9b6ffe, sg:74:9ea2a20a2cf96f5e, sg:8:9551f0c4ea887cb2), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 26 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:0:0407b42c97ccb566, sg:104:4d2940da495253fb, sg:106:67301075d4081408, sg:109:acb948b3df0aa8af, sg:110:d3eefe3d8c5969ee, sg:117:5f7c32de14792236, sg:16:e56ac532d76e2b76, sg:19:b8eed958f59d640e, sg:20:f6901d9c28fd2f28, sg:25:6dffdc5026b552d8, sg:29:6031e40cffa97197, sg:3:52bf36fd30c28c8e, sg:42:329f422d795cf67d, sg:45:885d91082f72292f, sg:46:1e975a983138ffd6, sg:53:1c2c321ec1d637f7, sg:63:9c080b5b0f116776, sg:66:901b7c2facbb70d7, sg:67:3b66f7dac01ccd60, sg:6:610ab1d78e9b6ffe, sg:74:9ea2a20a2cf96f5e, sg:84:580921fa07043992, sg:87:c94def619838883c, sg:88:cad0d4f39c0423ca, sg:8:9551f0c4ea887cb2, sg:95:107e1bada3f0fcc1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F219" s="14" t="n"/>
@@ -8717,7 +8717,7 @@
       </c>
       <c r="E220" s="18" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 17 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:0:0407b42c97ccb566, sg:16:e56ac532d76e2b76, sg:19:b8eed958f59d640e, sg:20:f6901d9c28fd2f28, sg:25:6dffdc5026b552d8, sg:29:6031e40cffa97197, sg:3:52bf36fd30c28c8e, sg:42:329f422d795cf67d, sg:45:885d91082f72292f, sg:46:1e975a983138ffd6, sg:53:1c2c321ec1d637f7, sg:63:9c080b5b0f116776, sg:66:901b7c2facbb70d7, sg:67:3b66f7dac01ccd60, sg:6:610ab1d78e9b6ffe, sg:74:9ea2a20a2cf96f5e, sg:8:9551f0c4ea887cb2), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 26 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:0:0407b42c97ccb566, sg:104:4d2940da495253fb, sg:106:67301075d4081408, sg:109:acb948b3df0aa8af, sg:110:d3eefe3d8c5969ee, sg:117:5f7c32de14792236, sg:16:e56ac532d76e2b76, sg:19:b8eed958f59d640e, sg:20:f6901d9c28fd2f28, sg:25:6dffdc5026b552d8, sg:29:6031e40cffa97197, sg:3:52bf36fd30c28c8e, sg:42:329f422d795cf67d, sg:45:885d91082f72292f, sg:46:1e975a983138ffd6, sg:53:1c2c321ec1d637f7, sg:63:9c080b5b0f116776, sg:66:901b7c2facbb70d7, sg:67:3b66f7dac01ccd60, sg:6:610ab1d78e9b6ffe, sg:74:9ea2a20a2cf96f5e, sg:84:580921fa07043992, sg:87:c94def619838883c, sg:88:cad0d4f39c0423ca, sg:8:9551f0c4ea887cb2, sg:95:107e1bada3f0fcc1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F220" s="18" t="n"/>
@@ -8990,7 +8990,7 @@
       </c>
       <c r="E229" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; The recorder is not reachable by the agent it records: PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 21 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:0:0407b42c97ccb566, sg:16:e56ac532d76e2b76, sg:17:abd9cb98a7931aac, sg:18:0a53a808e1826a22, sg:1:2da04769bddc3d6b, sg:28:3d79c978f5f94865, sg:2:3a6ad16a3f7b631b, sg:33:26603829d8a2d99d, sg:35:a32f87f5a73d99c7, sg:42:329f422d795cf67d, sg:43:f2f5bee2bc12f523, sg:44:5524171aae0946b5, sg:52:2e7f22f8c6c1a019, sg:55:075d6757ad9fea62, sg:59:d3094004aa13722e, sg:63:9c080b5b0f116776, sg:64:a3b27f1c9b025094, sg:65:ce198ee91ed4866c, sg:73:32e817ccb1c5e3ff, sg:76:298fd8e47c3f66a8, sg:80:3a06820ff0a3b2dc), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; The recorder is not reachable by the agent it records: PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 34 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:0:0407b42c97ccb566, sg:101:5769cff7b0eb1e4f, sg:104:4d2940da495253fb, sg:106:67301075d4081408, sg:107:9bfba4a8ddb2ec11, sg:108:5d16da9224a94243, sg:116:7bb23be2c7b89862, sg:119:1fe284b51575c9ed, sg:123:fe58b9416b23b75a, sg:16:e56ac532d76e2b76, sg:17:abd9cb98a7931aac, sg:18:0a53a808e1826a22, sg:1:2da04769bddc3d6b, sg:28:3d79c978f5f94865, sg:2:3a6ad16a3f7b631b, sg:33:26603829d8a2d99d, sg:35:a32f87f5a73d99c7, sg:42:329f422d795cf67d, sg:43:f2f5bee2bc12f523, sg:44:5524171aae0946b5, sg:52:2e7f22f8c6c1a019, sg:55:075d6757ad9fea62, sg:59:d3094004aa13722e, sg:63:9c080b5b0f116776, sg:64:a3b27f1c9b025094, sg:65:ce198ee91ed4866c, sg:73:32e817ccb1c5e3ff, sg:76:298fd8e47c3f66a8, sg:80:3a06820ff0a3b2dc, sg:84:580921fa07043992, sg:85:48f0430177edc288, sg:86:b5337a996a62e16a, sg:94:ebdc80663fd930b2, sg:97:681acaa39a9bc201), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F229" s="14" t="n"/>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="E255" s="14" t="inlineStr">
         <is>
-          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:32:62e9084ac5c23150, sg:50:bb2e261c780ea83b, sg:71:6493aa04c046d505), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 5 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:114:84532e35fc44e02c, sg:32:62e9084ac5c23150, sg:50:bb2e261c780ea83b, sg:71:6493aa04c046d505, sg:92:6902ec516d57670f), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F255" s="14" t="n"/>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="E256" s="18" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 5 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:25:6dffdc5026b552d8, sg:29:6031e40cffa97197, sg:3:52bf36fd30c28c8e, sg:53:1c2c321ec1d637f7, sg:74:9ea2a20a2cf96f5e), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 7 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:117:5f7c32de14792236, sg:25:6dffdc5026b552d8, sg:29:6031e40cffa97197, sg:3:52bf36fd30c28c8e, sg:53:1c2c321ec1d637f7, sg:74:9ea2a20a2cf96f5e, sg:95:107e1bada3f0fcc1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F256" s="18" t="n"/>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="E257" s="14" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 5 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:25:6dffdc5026b552d8, sg:29:6031e40cffa97197, sg:3:52bf36fd30c28c8e, sg:53:1c2c321ec1d637f7, sg:74:9ea2a20a2cf96f5e), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 7 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:117:5f7c32de14792236, sg:25:6dffdc5026b552d8, sg:29:6031e40cffa97197, sg:3:52bf36fd30c28c8e, sg:53:1c2c321ec1d637f7, sg:74:9ea2a20a2cf96f5e, sg:95:107e1bada3f0fcc1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F257" s="14" t="n"/>

--- a/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
+++ b/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
@@ -2078,7 +2078,7 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 22 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:102:1a57e64be953671e, sg:103:e8b6c17e04be0f76, sg:110:d3eefe3d8c5969ee, sg:118:47340dfd38fcee2d, sg:124:24bb2fd033133be1, sg:125:6861749dc0b73d3f, sg:20:f6901d9c28fd2f28, sg:26:fadb8b44cbf92e38, sg:37:82ae8f8f17419cab, sg:39:fbe37ba1a9e2b863, sg:46:1e975a983138ffd6, sg:4:276bdc000eb55277, sg:54:8bcbddcadf8f1734, sg:60:571f52205287dd41, sg:61:d8495b2ca3ac47d7, sg:67:3b66f7dac01ccd60, sg:75:229d4e17d8b99c62, sg:81:86d629fb715c366a, sg:82:f7cc594a8b2b486b, sg:88:cad0d4f39c0423ca, sg:8:9551f0c4ea887cb2, sg:96:562d8d258251e9fe), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 26 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:102:1a57e64be953671e, sg:103:e8b6c17e04be0f76, sg:110:d3eefe3d8c5969ee, sg:118:47340dfd38fcee2d, sg:124:24bb2fd033133be1, sg:125:6861749dc0b73d3f, sg:131:3c75b8d92bea016e, sg:139:4d6cc018d40c3a62, sg:145:0f1d057757915f05, sg:146:87d4975ef6102f15, sg:20:f6901d9c28fd2f28, sg:26:fadb8b44cbf92e38, sg:37:82ae8f8f17419cab, sg:39:fbe37ba1a9e2b863, sg:46:1e975a983138ffd6, sg:4:276bdc000eb55277, sg:54:8bcbddcadf8f1734, sg:60:571f52205287dd41, sg:61:d8495b2ca3ac47d7, sg:67:3b66f7dac01ccd60, sg:75:229d4e17d8b99c62, sg:81:86d629fb715c366a, sg:82:f7cc594a8b2b486b, sg:88:cad0d4f39c0423ca, sg:8:9551f0c4ea887cb2, sg:96:562d8d258251e9fe), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F3" s="14" t="n"/>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 22 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:102:1a57e64be953671e, sg:103:e8b6c17e04be0f76, sg:110:d3eefe3d8c5969ee, sg:118:47340dfd38fcee2d, sg:124:24bb2fd033133be1, sg:125:6861749dc0b73d3f, sg:20:f6901d9c28fd2f28, sg:26:fadb8b44cbf92e38, sg:37:82ae8f8f17419cab, sg:39:fbe37ba1a9e2b863, sg:46:1e975a983138ffd6, sg:4:276bdc000eb55277, sg:54:8bcbddcadf8f1734, sg:60:571f52205287dd41, sg:61:d8495b2ca3ac47d7, sg:67:3b66f7dac01ccd60, sg:75:229d4e17d8b99c62, sg:81:86d629fb715c366a, sg:82:f7cc594a8b2b486b, sg:88:cad0d4f39c0423ca, sg:8:9551f0c4ea887cb2, sg:96:562d8d258251e9fe), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 26 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:102:1a57e64be953671e, sg:103:e8b6c17e04be0f76, sg:110:d3eefe3d8c5969ee, sg:118:47340dfd38fcee2d, sg:124:24bb2fd033133be1, sg:125:6861749dc0b73d3f, sg:131:3c75b8d92bea016e, sg:139:4d6cc018d40c3a62, sg:145:0f1d057757915f05, sg:146:87d4975ef6102f15, sg:20:f6901d9c28fd2f28, sg:26:fadb8b44cbf92e38, sg:37:82ae8f8f17419cab, sg:39:fbe37ba1a9e2b863, sg:46:1e975a983138ffd6, sg:4:276bdc000eb55277, sg:54:8bcbddcadf8f1734, sg:60:571f52205287dd41, sg:61:d8495b2ca3ac47d7, sg:67:3b66f7dac01ccd60, sg:75:229d4e17d8b99c62, sg:81:86d629fb715c366a, sg:82:f7cc594a8b2b486b, sg:88:cad0d4f39c0423ca, sg:8:9551f0c4ea887cb2, sg:96:562d8d258251e9fe), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F4" s="18" t="n"/>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
-          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 17 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:113:8271ad88f2fcd9c6, sg:120:784ba55dad12416e, sg:121:130f6e84f40cfa26, sg:12:3fd44ffa4a757a26, sg:23:a008c5fa1d367385, sg:27:ec2b4becd7c77e29, sg:36:330695993f562a6e, sg:49:4a65b4cd43d97bea, sg:56:1aa8e8cd7607771c, sg:57:f00a04ac3328aad2, sg:5:c95b7b06e158da45, sg:70:cb61aa7cb8e712da, sg:77:195c3b7af795e666, sg:78:20569b15038d3d77, sg:91:36b979feb38418df, sg:98:8a99aa4cd2400d35, sg:99:403b00f65c083d2b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 20 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:113:8271ad88f2fcd9c6, sg:120:784ba55dad12416e, sg:121:130f6e84f40cfa26, sg:12:3fd44ffa4a757a26, sg:134:b89516016bf65808, sg:141:eae4b631af0c4b7e, sg:142:05dc402d846c94bc, sg:23:a008c5fa1d367385, sg:27:ec2b4becd7c77e29, sg:36:330695993f562a6e, sg:49:4a65b4cd43d97bea, sg:56:1aa8e8cd7607771c, sg:57:f00a04ac3328aad2, sg:5:c95b7b06e158da45, sg:70:cb61aa7cb8e712da, sg:77:195c3b7af795e666, sg:78:20569b15038d3d77, sg:91:36b979feb38418df, sg:98:8a99aa4cd2400d35, sg:99:403b00f65c083d2b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F44" s="18" t="n"/>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 17 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:113:8271ad88f2fcd9c6, sg:120:784ba55dad12416e, sg:121:130f6e84f40cfa26, sg:12:3fd44ffa4a757a26, sg:23:a008c5fa1d367385, sg:27:ec2b4becd7c77e29, sg:36:330695993f562a6e, sg:49:4a65b4cd43d97bea, sg:56:1aa8e8cd7607771c, sg:57:f00a04ac3328aad2, sg:5:c95b7b06e158da45, sg:70:cb61aa7cb8e712da, sg:77:195c3b7af795e666, sg:78:20569b15038d3d77, sg:91:36b979feb38418df, sg:98:8a99aa4cd2400d35, sg:99:403b00f65c083d2b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 20 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:113:8271ad88f2fcd9c6, sg:120:784ba55dad12416e, sg:121:130f6e84f40cfa26, sg:12:3fd44ffa4a757a26, sg:134:b89516016bf65808, sg:141:eae4b631af0c4b7e, sg:142:05dc402d846c94bc, sg:23:a008c5fa1d367385, sg:27:ec2b4becd7c77e29, sg:36:330695993f562a6e, sg:49:4a65b4cd43d97bea, sg:56:1aa8e8cd7607771c, sg:57:f00a04ac3328aad2, sg:5:c95b7b06e158da45, sg:70:cb61aa7cb8e712da, sg:77:195c3b7af795e666, sg:78:20569b15038d3d77, sg:91:36b979feb38418df, sg:98:8a99aa4cd2400d35, sg:99:403b00f65c083d2b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F45" s="14" t="n"/>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Offline by default: no runtime path performs an external network call unless anchoring is explicitly enabled, and enabling it announces itself. Proven by 11 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:100:45b3fff47c6680f0, sg:105:f03f044029f90661, sg:122:6e1971822861b99a, sg:15:bf273856e947ee23, sg:31:e3f89cd814900706, sg:41:7a7f781b465c9908, sg:58:f4c71b0ec7276039, sg:62:840752dcd3002f50, sg:79:b41619813ad4e433, sg:83:372de70d047ff5b9, sg:9:8e229db09d9d3bb6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 8 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:105:f03f044029f90661, sg:126:6823cebf0934135d, sg:143:d9c2d5aed3fb3892, sg:15:bf273856e947ee23, sg:41:7a7f781b465c9908, sg:62:840752dcd3002f50, sg:83:372de70d047ff5b9, sg:9:8e229db09d9d3bb6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F112" s="18" t="n"/>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Offline by default: no runtime path performs an external network call unless anchoring is explicitly enabled, and enabling it announces itself. Proven by 11 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:100:45b3fff47c6680f0, sg:105:f03f044029f90661, sg:122:6e1971822861b99a, sg:15:bf273856e947ee23, sg:31:e3f89cd814900706, sg:41:7a7f781b465c9908, sg:58:f4c71b0ec7276039, sg:62:840752dcd3002f50, sg:79:b41619813ad4e433, sg:83:372de70d047ff5b9, sg:9:8e229db09d9d3bb6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 8 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:105:f03f044029f90661, sg:126:6823cebf0934135d, sg:143:d9c2d5aed3fb3892, sg:15:bf273856e947ee23, sg:41:7a7f781b465c9908, sg:62:840752dcd3002f50, sg:83:372de70d047ff5b9, sg:9:8e229db09d9d3bb6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F113" s="14" t="n"/>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="E130" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, and the denial names the contributing artifacts; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 38 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:103:e8b6c17e04be0f76, sg:105:f03f044029f90661, sg:111:13f68a28ef715fe1, sg:112:a7e34cfc13937ef6, sg:113:8271ad88f2fcd9c6, sg:114:84532e35fc44e02c, sg:119:1fe284b51575c9ed, sg:125:6861749dc0b73d3f, sg:12:3fd44ffa4a757a26, sg:14:0472ec5ce6c5572b, sg:15:bf273856e947ee23, sg:22:57dd6789598beda0, sg:23:a008c5fa1d367385, sg:32:62e9084ac5c23150, sg:33:26603829d8a2d99d, sg:39:fbe37ba1a9e2b863, sg:40:7881257b3bc9ab46, sg:41:7a7f781b465c9908, sg:47:b88eb327a02935ba, sg:48:18e04efd42076c3b, sg:49:4a65b4cd43d97bea, sg:50:bb2e261c780ea83b, sg:55:075d6757ad9fea62, sg:61:d8495b2ca3ac47d7, sg:62:840752dcd3002f50, sg:68:ec8a054e28749618, sg:69:96cd89574676b8cc, sg:70:cb61aa7cb8e712da, sg:71:6493aa04c046d505, sg:76:298fd8e47c3f66a8, sg:82:f7cc594a8b2b486b, sg:83:372de70d047ff5b9, sg:89:8dca168b634a4a7a, sg:90:cd1c463b43b49e9b, sg:91:36b979feb38418df, sg:92:6902ec516d57670f, sg:97:681acaa39a9bc201, sg:9:8e229db09d9d3bb6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 45 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:103:e8b6c17e04be0f76, sg:105:f03f044029f90661, sg:111:13f68a28ef715fe1, sg:112:a7e34cfc13937ef6, sg:113:8271ad88f2fcd9c6, sg:114:84532e35fc44e02c, sg:119:1fe284b51575c9ed, sg:125:6861749dc0b73d3f, sg:126:6823cebf0934135d, sg:12:3fd44ffa4a757a26, sg:132:08c49efbc4792ac9, sg:133:00724de667c9dc66, sg:134:b89516016bf65808, sg:135:ea77e9f3504abbcd, sg:140:7f5318eb71a53338, sg:146:87d4975ef6102f15, sg:14:0472ec5ce6c5572b, sg:15:bf273856e947ee23, sg:22:57dd6789598beda0, sg:23:a008c5fa1d367385, sg:32:62e9084ac5c23150, sg:33:26603829d8a2d99d, sg:39:fbe37ba1a9e2b863, sg:40:7881257b3bc9ab46, sg:41:7a7f781b465c9908, sg:47:b88eb327a02935ba, sg:48:18e04efd42076c3b, sg:49:4a65b4cd43d97bea, sg:50:bb2e261c780ea83b, sg:55:075d6757ad9fea62, sg:61:d8495b2ca3ac47d7, sg:62:840752dcd3002f50, sg:68:ec8a054e28749618, sg:69:96cd89574676b8cc, sg:70:cb61aa7cb8e712da, sg:71:6493aa04c046d505, sg:76:298fd8e47c3f66a8, sg:82:f7cc594a8b2b486b, sg:83:372de70d047ff5b9, sg:89:8dca168b634a4a7a, sg:90:cd1c463b43b49e9b, sg:91:36b979feb38418df, sg:92:6902ec516d57670f, sg:97:681acaa39a9bc201, sg:9:8e229db09d9d3bb6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F130" s="18" t="n"/>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>Offline by default: no runtime path performs an external network call unless anchoring is explicitly enabled, and enabling it announces itself. Proven by 5 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:100:45b3fff47c6680f0, sg:122:6e1971822861b99a, sg:31:e3f89cd814900706, sg:58:f4c71b0ec7276039, sg:79:b41619813ad4e433), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:143:d9c2d5aed3fb3892), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F203" s="14" t="n"/>
@@ -8223,7 +8223,7 @@
       </c>
       <c r="E204" s="18" t="inlineStr">
         <is>
-          <t>Offline by default: no runtime path performs an external network call unless anchoring is explicitly enabled, and enabling it announces itself. Proven by 5 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:100:45b3fff47c6680f0, sg:122:6e1971822861b99a, sg:31:e3f89cd814900706, sg:58:f4c71b0ec7276039, sg:79:b41619813ad4e433), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:143:d9c2d5aed3fb3892), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F204" s="18" t="n"/>
@@ -8669,7 +8669,7 @@
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 26 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:0:0407b42c97ccb566, sg:104:4d2940da495253fb, sg:106:67301075d4081408, sg:109:acb948b3df0aa8af, sg:110:d3eefe3d8c5969ee, sg:117:5f7c32de14792236, sg:16:e56ac532d76e2b76, sg:19:b8eed958f59d640e, sg:20:f6901d9c28fd2f28, sg:25:6dffdc5026b552d8, sg:29:6031e40cffa97197, sg:3:52bf36fd30c28c8e, sg:42:329f422d795cf67d, sg:45:885d91082f72292f, sg:46:1e975a983138ffd6, sg:53:1c2c321ec1d637f7, sg:63:9c080b5b0f116776, sg:66:901b7c2facbb70d7, sg:67:3b66f7dac01ccd60, sg:6:610ab1d78e9b6ffe, sg:74:9ea2a20a2cf96f5e, sg:84:580921fa07043992, sg:87:c94def619838883c, sg:88:cad0d4f39c0423ca, sg:8:9551f0c4ea887cb2, sg:95:107e1bada3f0fcc1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 30 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:0:0407b42c97ccb566, sg:104:4d2940da495253fb, sg:106:67301075d4081408, sg:109:acb948b3df0aa8af, sg:110:d3eefe3d8c5969ee, sg:117:5f7c32de14792236, sg:127:90665017475bfab1, sg:130:25e4577eb8595e25, sg:131:3c75b8d92bea016e, sg:138:0da49d2557aa5fbb, sg:16:e56ac532d76e2b76, sg:19:b8eed958f59d640e, sg:20:f6901d9c28fd2f28, sg:25:6dffdc5026b552d8, sg:29:6031e40cffa97197, sg:3:52bf36fd30c28c8e, sg:42:329f422d795cf67d, sg:45:885d91082f72292f, sg:46:1e975a983138ffd6, sg:53:1c2c321ec1d637f7, sg:63:9c080b5b0f116776, sg:66:901b7c2facbb70d7, sg:67:3b66f7dac01ccd60, sg:6:610ab1d78e9b6ffe, sg:74:9ea2a20a2cf96f5e, sg:84:580921fa07043992, sg:87:c94def619838883c, sg:88:cad0d4f39c0423ca, sg:8:9551f0c4ea887cb2, sg:95:107e1bada3f0fcc1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F219" s="14" t="n"/>
@@ -8717,7 +8717,7 @@
       </c>
       <c r="E220" s="18" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 26 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:0:0407b42c97ccb566, sg:104:4d2940da495253fb, sg:106:67301075d4081408, sg:109:acb948b3df0aa8af, sg:110:d3eefe3d8c5969ee, sg:117:5f7c32de14792236, sg:16:e56ac532d76e2b76, sg:19:b8eed958f59d640e, sg:20:f6901d9c28fd2f28, sg:25:6dffdc5026b552d8, sg:29:6031e40cffa97197, sg:3:52bf36fd30c28c8e, sg:42:329f422d795cf67d, sg:45:885d91082f72292f, sg:46:1e975a983138ffd6, sg:53:1c2c321ec1d637f7, sg:63:9c080b5b0f116776, sg:66:901b7c2facbb70d7, sg:67:3b66f7dac01ccd60, sg:6:610ab1d78e9b6ffe, sg:74:9ea2a20a2cf96f5e, sg:84:580921fa07043992, sg:87:c94def619838883c, sg:88:cad0d4f39c0423ca, sg:8:9551f0c4ea887cb2, sg:95:107e1bada3f0fcc1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 30 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:0:0407b42c97ccb566, sg:104:4d2940da495253fb, sg:106:67301075d4081408, sg:109:acb948b3df0aa8af, sg:110:d3eefe3d8c5969ee, sg:117:5f7c32de14792236, sg:127:90665017475bfab1, sg:130:25e4577eb8595e25, sg:131:3c75b8d92bea016e, sg:138:0da49d2557aa5fbb, sg:16:e56ac532d76e2b76, sg:19:b8eed958f59d640e, sg:20:f6901d9c28fd2f28, sg:25:6dffdc5026b552d8, sg:29:6031e40cffa97197, sg:3:52bf36fd30c28c8e, sg:42:329f422d795cf67d, sg:45:885d91082f72292f, sg:46:1e975a983138ffd6, sg:53:1c2c321ec1d637f7, sg:63:9c080b5b0f116776, sg:66:901b7c2facbb70d7, sg:67:3b66f7dac01ccd60, sg:6:610ab1d78e9b6ffe, sg:74:9ea2a20a2cf96f5e, sg:84:580921fa07043992, sg:87:c94def619838883c, sg:88:cad0d4f39c0423ca, sg:8:9551f0c4ea887cb2, sg:95:107e1bada3f0fcc1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F220" s="18" t="n"/>
@@ -8990,7 +8990,7 @@
       </c>
       <c r="E229" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; The recorder is not reachable by the agent it records: PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 34 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:0:0407b42c97ccb566, sg:101:5769cff7b0eb1e4f, sg:104:4d2940da495253fb, sg:106:67301075d4081408, sg:107:9bfba4a8ddb2ec11, sg:108:5d16da9224a94243, sg:116:7bb23be2c7b89862, sg:119:1fe284b51575c9ed, sg:123:fe58b9416b23b75a, sg:16:e56ac532d76e2b76, sg:17:abd9cb98a7931aac, sg:18:0a53a808e1826a22, sg:1:2da04769bddc3d6b, sg:28:3d79c978f5f94865, sg:2:3a6ad16a3f7b631b, sg:33:26603829d8a2d99d, sg:35:a32f87f5a73d99c7, sg:42:329f422d795cf67d, sg:43:f2f5bee2bc12f523, sg:44:5524171aae0946b5, sg:52:2e7f22f8c6c1a019, sg:55:075d6757ad9fea62, sg:59:d3094004aa13722e, sg:63:9c080b5b0f116776, sg:64:a3b27f1c9b025094, sg:65:ce198ee91ed4866c, sg:73:32e817ccb1c5e3ff, sg:76:298fd8e47c3f66a8, sg:80:3a06820ff0a3b2dc, sg:84:580921fa07043992, sg:85:48f0430177edc288, sg:86:b5337a996a62e16a, sg:94:ebdc80663fd930b2, sg:97:681acaa39a9bc201), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; The recorder is not reachable by the agent it records: PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 40 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:0:0407b42c97ccb566, sg:101:5769cff7b0eb1e4f, sg:104:4d2940da495253fb, sg:106:67301075d4081408, sg:107:9bfba4a8ddb2ec11, sg:108:5d16da9224a94243, sg:116:7bb23be2c7b89862, sg:119:1fe284b51575c9ed, sg:123:fe58b9416b23b75a, sg:127:90665017475bfab1, sg:128:a3575e7244198146, sg:129:a40cc07b84e640b9, sg:137:1475b3b8f35b12c9, sg:140:7f5318eb71a53338, sg:144:49c57b3bf0dd9d97, sg:16:e56ac532d76e2b76, sg:17:abd9cb98a7931aac, sg:18:0a53a808e1826a22, sg:1:2da04769bddc3d6b, sg:28:3d79c978f5f94865, sg:2:3a6ad16a3f7b631b, sg:33:26603829d8a2d99d, sg:35:a32f87f5a73d99c7, sg:42:329f422d795cf67d, sg:43:f2f5bee2bc12f523, sg:44:5524171aae0946b5, sg:52:2e7f22f8c6c1a019, sg:55:075d6757ad9fea62, sg:59:d3094004aa13722e, sg:63:9c080b5b0f116776, sg:64:a3b27f1c9b025094, sg:65:ce198ee91ed4866c, sg:73:32e817ccb1c5e3ff, sg:76:298fd8e47c3f66a8, sg:80:3a06820ff0a3b2dc, sg:84:580921fa07043992, sg:85:48f0430177edc288, sg:86:b5337a996a62e16a, sg:94:ebdc80663fd930b2, sg:97:681acaa39a9bc201), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F229" s="14" t="n"/>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="E255" s="14" t="inlineStr">
         <is>
-          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 5 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:114:84532e35fc44e02c, sg:32:62e9084ac5c23150, sg:50:bb2e261c780ea83b, sg:71:6493aa04c046d505, sg:92:6902ec516d57670f), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:114:84532e35fc44e02c, sg:135:ea77e9f3504abbcd, sg:32:62e9084ac5c23150, sg:50:bb2e261c780ea83b, sg:71:6493aa04c046d505, sg:92:6902ec516d57670f), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F255" s="14" t="n"/>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="E256" s="18" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 7 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:117:5f7c32de14792236, sg:25:6dffdc5026b552d8, sg:29:6031e40cffa97197, sg:3:52bf36fd30c28c8e, sg:53:1c2c321ec1d637f7, sg:74:9ea2a20a2cf96f5e, sg:95:107e1bada3f0fcc1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 8 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:117:5f7c32de14792236, sg:138:0da49d2557aa5fbb, sg:25:6dffdc5026b552d8, sg:29:6031e40cffa97197, sg:3:52bf36fd30c28c8e, sg:53:1c2c321ec1d637f7, sg:74:9ea2a20a2cf96f5e, sg:95:107e1bada3f0fcc1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F256" s="18" t="n"/>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="E257" s="14" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 7 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:117:5f7c32de14792236, sg:25:6dffdc5026b552d8, sg:29:6031e40cffa97197, sg:3:52bf36fd30c28c8e, sg:53:1c2c321ec1d637f7, sg:74:9ea2a20a2cf96f5e, sg:95:107e1bada3f0fcc1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 8 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:117:5f7c32de14792236, sg:138:0da49d2557aa5fbb, sg:25:6dffdc5026b552d8, sg:29:6031e40cffa97197, sg:3:52bf36fd30c28c8e, sg:53:1c2c321ec1d637f7, sg:74:9ea2a20a2cf96f5e, sg:95:107e1bada3f0fcc1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F257" s="14" t="n"/>

--- a/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
+++ b/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
@@ -2078,7 +2078,7 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 26 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:102:1a57e64be953671e, sg:103:e8b6c17e04be0f76, sg:110:d3eefe3d8c5969ee, sg:118:47340dfd38fcee2d, sg:124:24bb2fd033133be1, sg:125:6861749dc0b73d3f, sg:131:3c75b8d92bea016e, sg:139:4d6cc018d40c3a62, sg:145:0f1d057757915f05, sg:146:87d4975ef6102f15, sg:20:f6901d9c28fd2f28, sg:26:fadb8b44cbf92e38, sg:37:82ae8f8f17419cab, sg:39:fbe37ba1a9e2b863, sg:46:1e975a983138ffd6, sg:4:276bdc000eb55277, sg:54:8bcbddcadf8f1734, sg:60:571f52205287dd41, sg:61:d8495b2ca3ac47d7, sg:67:3b66f7dac01ccd60, sg:75:229d4e17d8b99c62, sg:81:86d629fb715c366a, sg:82:f7cc594a8b2b486b, sg:88:cad0d4f39c0423ca, sg:8:9551f0c4ea887cb2, sg:96:562d8d258251e9fe), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 14 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:152:f5dd0f16ab185e0b, sg:160:8732eae8813b1682, sg:167:af6bb479c89079c9, sg:173:6ce0b01108cbc4b8, sg:181:1d0e1089dc62847e, sg:188:95a9e64d9906694a, sg:194:38e25eb804466a9c, sg:202:e4c30c95efb6cf33, sg:208:0bfb428b6e0f581c, sg:209:971e683e2e94b943, sg:215:4ecc0ca415f27b19, sg:223:503487865ccbe701, sg:229:ffe959c28f930b9c, sg:230:8e3a080457b52971), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F3" s="14" t="n"/>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 26 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:102:1a57e64be953671e, sg:103:e8b6c17e04be0f76, sg:110:d3eefe3d8c5969ee, sg:118:47340dfd38fcee2d, sg:124:24bb2fd033133be1, sg:125:6861749dc0b73d3f, sg:131:3c75b8d92bea016e, sg:139:4d6cc018d40c3a62, sg:145:0f1d057757915f05, sg:146:87d4975ef6102f15, sg:20:f6901d9c28fd2f28, sg:26:fadb8b44cbf92e38, sg:37:82ae8f8f17419cab, sg:39:fbe37ba1a9e2b863, sg:46:1e975a983138ffd6, sg:4:276bdc000eb55277, sg:54:8bcbddcadf8f1734, sg:60:571f52205287dd41, sg:61:d8495b2ca3ac47d7, sg:67:3b66f7dac01ccd60, sg:75:229d4e17d8b99c62, sg:81:86d629fb715c366a, sg:82:f7cc594a8b2b486b, sg:88:cad0d4f39c0423ca, sg:8:9551f0c4ea887cb2, sg:96:562d8d258251e9fe), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 14 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:152:f5dd0f16ab185e0b, sg:160:8732eae8813b1682, sg:167:af6bb479c89079c9, sg:173:6ce0b01108cbc4b8, sg:181:1d0e1089dc62847e, sg:188:95a9e64d9906694a, sg:194:38e25eb804466a9c, sg:202:e4c30c95efb6cf33, sg:208:0bfb428b6e0f581c, sg:209:971e683e2e94b943, sg:215:4ecc0ca415f27b19, sg:223:503487865ccbe701, sg:229:ffe959c28f930b9c, sg:230:8e3a080457b52971), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F4" s="18" t="n"/>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
-          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 20 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:113:8271ad88f2fcd9c6, sg:120:784ba55dad12416e, sg:121:130f6e84f40cfa26, sg:12:3fd44ffa4a757a26, sg:134:b89516016bf65808, sg:141:eae4b631af0c4b7e, sg:142:05dc402d846c94bc, sg:23:a008c5fa1d367385, sg:27:ec2b4becd7c77e29, sg:36:330695993f562a6e, sg:49:4a65b4cd43d97bea, sg:56:1aa8e8cd7607771c, sg:57:f00a04ac3328aad2, sg:5:c95b7b06e158da45, sg:70:cb61aa7cb8e712da, sg:77:195c3b7af795e666, sg:78:20569b15038d3d77, sg:91:36b979feb38418df, sg:98:8a99aa4cd2400d35, sg:99:403b00f65c083d2b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 10 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:155:b39ce17aaccb624b, sg:163:4522da66473b0891, sg:176:dd3e103543a5f403, sg:184:c86849434d37f2ca, sg:197:1ed5320c1a29c0e4, sg:204:9ea6d3672f1cbb6c, sg:205:3e8f79273c4d99e8, sg:218:fe0f5eee9fdb542d, sg:225:80c4d796e03c26e4, sg:226:6a59e2af4b4ca71b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F44" s="18" t="n"/>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 20 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:113:8271ad88f2fcd9c6, sg:120:784ba55dad12416e, sg:121:130f6e84f40cfa26, sg:12:3fd44ffa4a757a26, sg:134:b89516016bf65808, sg:141:eae4b631af0c4b7e, sg:142:05dc402d846c94bc, sg:23:a008c5fa1d367385, sg:27:ec2b4becd7c77e29, sg:36:330695993f562a6e, sg:49:4a65b4cd43d97bea, sg:56:1aa8e8cd7607771c, sg:57:f00a04ac3328aad2, sg:5:c95b7b06e158da45, sg:70:cb61aa7cb8e712da, sg:77:195c3b7af795e666, sg:78:20569b15038d3d77, sg:91:36b979feb38418df, sg:98:8a99aa4cd2400d35, sg:99:403b00f65c083d2b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 10 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:155:b39ce17aaccb624b, sg:163:4522da66473b0891, sg:176:dd3e103543a5f403, sg:184:c86849434d37f2ca, sg:197:1ed5320c1a29c0e4, sg:204:9ea6d3672f1cbb6c, sg:205:3e8f79273c4d99e8, sg:218:fe0f5eee9fdb542d, sg:225:80c4d796e03c26e4, sg:226:6a59e2af4b4ca71b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F45" s="14" t="n"/>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 8 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:105:f03f044029f90661, sg:126:6823cebf0934135d, sg:143:d9c2d5aed3fb3892, sg:15:bf273856e947ee23, sg:41:7a7f781b465c9908, sg:62:840752dcd3002f50, sg:83:372de70d047ff5b9, sg:9:8e229db09d9d3bb6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 8 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:147:9bebca7095710e7b, sg:164:0a17213da88916a0, sg:168:673efa781a5886af, sg:185:722aa012e9e81176, sg:189:6da7e8855e27abf3, sg:206:e376384aa84cb442, sg:210:b32620de15f05a8a, sg:227:395621be5822edd0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F112" s="18" t="n"/>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 8 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:105:f03f044029f90661, sg:126:6823cebf0934135d, sg:143:d9c2d5aed3fb3892, sg:15:bf273856e947ee23, sg:41:7a7f781b465c9908, sg:62:840752dcd3002f50, sg:83:372de70d047ff5b9, sg:9:8e229db09d9d3bb6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 8 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:147:9bebca7095710e7b, sg:164:0a17213da88916a0, sg:168:673efa781a5886af, sg:185:722aa012e9e81176, sg:189:6da7e8855e27abf3, sg:206:e376384aa84cb442, sg:210:b32620de15f05a8a, sg:227:395621be5822edd0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F113" s="14" t="n"/>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="E130" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 45 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:103:e8b6c17e04be0f76, sg:105:f03f044029f90661, sg:111:13f68a28ef715fe1, sg:112:a7e34cfc13937ef6, sg:113:8271ad88f2fcd9c6, sg:114:84532e35fc44e02c, sg:119:1fe284b51575c9ed, sg:125:6861749dc0b73d3f, sg:126:6823cebf0934135d, sg:12:3fd44ffa4a757a26, sg:132:08c49efbc4792ac9, sg:133:00724de667c9dc66, sg:134:b89516016bf65808, sg:135:ea77e9f3504abbcd, sg:140:7f5318eb71a53338, sg:146:87d4975ef6102f15, sg:14:0472ec5ce6c5572b, sg:15:bf273856e947ee23, sg:22:57dd6789598beda0, sg:23:a008c5fa1d367385, sg:32:62e9084ac5c23150, sg:33:26603829d8a2d99d, sg:39:fbe37ba1a9e2b863, sg:40:7881257b3bc9ab46, sg:41:7a7f781b465c9908, sg:47:b88eb327a02935ba, sg:48:18e04efd42076c3b, sg:49:4a65b4cd43d97bea, sg:50:bb2e261c780ea83b, sg:55:075d6757ad9fea62, sg:61:d8495b2ca3ac47d7, sg:62:840752dcd3002f50, sg:68:ec8a054e28749618, sg:69:96cd89574676b8cc, sg:70:cb61aa7cb8e712da, sg:71:6493aa04c046d505, sg:76:298fd8e47c3f66a8, sg:82:f7cc594a8b2b486b, sg:83:372de70d047ff5b9, sg:89:8dca168b634a4a7a, sg:90:cd1c463b43b49e9b, sg:91:36b979feb38418df, sg:92:6902ec516d57670f, sg:97:681acaa39a9bc201, sg:9:8e229db09d9d3bb6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 28 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:147:9bebca7095710e7b, sg:153:917bc028692cdd65, sg:154:2aafc34476d15d60, sg:155:b39ce17aaccb624b, sg:156:0410d01f11f7a67b, sg:161:031e2e8d26da6042, sg:167:af6bb479c89079c9, sg:168:673efa781a5886af, sg:174:13f58e0526f7181d, sg:175:ae266bdaf3bcce83, sg:176:dd3e103543a5f403, sg:177:c0fc068544402740, sg:182:316038988f1c15b5, sg:188:95a9e64d9906694a, sg:189:6da7e8855e27abf3, sg:195:7e21be5aabc730de, sg:196:658be324c2a38ac1, sg:197:1ed5320c1a29c0e4, sg:198:2ebfa924ad6244b2, sg:203:35588c7155777fa3, sg:209:971e683e2e94b943, sg:210:b32620de15f05a8a, sg:216:41e4f43c86d8a50c, sg:217:3d31aa054b4df3be, sg:218:fe0f5eee9fdb542d, sg:219:8f64ef8ae036aae4, sg:224:261113f46c0a132c, sg:230:8e3a080457b52971), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F130" s="18" t="n"/>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:143:d9c2d5aed3fb3892), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:164:0a17213da88916a0, sg:185:722aa012e9e81176, sg:206:e376384aa84cb442, sg:227:395621be5822edd0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F203" s="14" t="n"/>
@@ -8223,7 +8223,7 @@
       </c>
       <c r="E204" s="18" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:143:d9c2d5aed3fb3892), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:164:0a17213da88916a0, sg:185:722aa012e9e81176, sg:206:e376384aa84cb442, sg:227:395621be5822edd0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F204" s="18" t="n"/>
@@ -8669,7 +8669,7 @@
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 30 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:0:0407b42c97ccb566, sg:104:4d2940da495253fb, sg:106:67301075d4081408, sg:109:acb948b3df0aa8af, sg:110:d3eefe3d8c5969ee, sg:117:5f7c32de14792236, sg:127:90665017475bfab1, sg:130:25e4577eb8595e25, sg:131:3c75b8d92bea016e, sg:138:0da49d2557aa5fbb, sg:16:e56ac532d76e2b76, sg:19:b8eed958f59d640e, sg:20:f6901d9c28fd2f28, sg:25:6dffdc5026b552d8, sg:29:6031e40cffa97197, sg:3:52bf36fd30c28c8e, sg:42:329f422d795cf67d, sg:45:885d91082f72292f, sg:46:1e975a983138ffd6, sg:53:1c2c321ec1d637f7, sg:63:9c080b5b0f116776, sg:66:901b7c2facbb70d7, sg:67:3b66f7dac01ccd60, sg:6:610ab1d78e9b6ffe, sg:74:9ea2a20a2cf96f5e, sg:84:580921fa07043992, sg:87:c94def619838883c, sg:88:cad0d4f39c0423ca, sg:8:9551f0c4ea887cb2, sg:95:107e1bada3f0fcc1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 16 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:148:bf16ebd320021812, sg:151:09827d850c759c55, sg:152:f5dd0f16ab185e0b, sg:159:d2f56027459525a6, sg:169:48b4d0685cddb97c, sg:172:5926dd73b82f20ac, sg:173:6ce0b01108cbc4b8, sg:180:7bd687cabc9b8fae, sg:190:2c686e6a0a4325ea, sg:193:6533b7a7ff0dc797, sg:194:38e25eb804466a9c, sg:201:42177fa99ba5562a, sg:211:b0c734a6d6203dd9, sg:214:b56d0a70c597d937, sg:215:4ecc0ca415f27b19, sg:222:2c44c57502077f4b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F219" s="14" t="n"/>
@@ -8717,7 +8717,7 @@
       </c>
       <c r="E220" s="18" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 30 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:0:0407b42c97ccb566, sg:104:4d2940da495253fb, sg:106:67301075d4081408, sg:109:acb948b3df0aa8af, sg:110:d3eefe3d8c5969ee, sg:117:5f7c32de14792236, sg:127:90665017475bfab1, sg:130:25e4577eb8595e25, sg:131:3c75b8d92bea016e, sg:138:0da49d2557aa5fbb, sg:16:e56ac532d76e2b76, sg:19:b8eed958f59d640e, sg:20:f6901d9c28fd2f28, sg:25:6dffdc5026b552d8, sg:29:6031e40cffa97197, sg:3:52bf36fd30c28c8e, sg:42:329f422d795cf67d, sg:45:885d91082f72292f, sg:46:1e975a983138ffd6, sg:53:1c2c321ec1d637f7, sg:63:9c080b5b0f116776, sg:66:901b7c2facbb70d7, sg:67:3b66f7dac01ccd60, sg:6:610ab1d78e9b6ffe, sg:74:9ea2a20a2cf96f5e, sg:84:580921fa07043992, sg:87:c94def619838883c, sg:88:cad0d4f39c0423ca, sg:8:9551f0c4ea887cb2, sg:95:107e1bada3f0fcc1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 16 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:148:bf16ebd320021812, sg:151:09827d850c759c55, sg:152:f5dd0f16ab185e0b, sg:159:d2f56027459525a6, sg:169:48b4d0685cddb97c, sg:172:5926dd73b82f20ac, sg:173:6ce0b01108cbc4b8, sg:180:7bd687cabc9b8fae, sg:190:2c686e6a0a4325ea, sg:193:6533b7a7ff0dc797, sg:194:38e25eb804466a9c, sg:201:42177fa99ba5562a, sg:211:b0c734a6d6203dd9, sg:214:b56d0a70c597d937, sg:215:4ecc0ca415f27b19, sg:222:2c44c57502077f4b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F220" s="18" t="n"/>
@@ -8990,7 +8990,7 @@
       </c>
       <c r="E229" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; The recorder is not reachable by the agent it records: PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 40 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:0:0407b42c97ccb566, sg:101:5769cff7b0eb1e4f, sg:104:4d2940da495253fb, sg:106:67301075d4081408, sg:107:9bfba4a8ddb2ec11, sg:108:5d16da9224a94243, sg:116:7bb23be2c7b89862, sg:119:1fe284b51575c9ed, sg:123:fe58b9416b23b75a, sg:127:90665017475bfab1, sg:128:a3575e7244198146, sg:129:a40cc07b84e640b9, sg:137:1475b3b8f35b12c9, sg:140:7f5318eb71a53338, sg:144:49c57b3bf0dd9d97, sg:16:e56ac532d76e2b76, sg:17:abd9cb98a7931aac, sg:18:0a53a808e1826a22, sg:1:2da04769bddc3d6b, sg:28:3d79c978f5f94865, sg:2:3a6ad16a3f7b631b, sg:33:26603829d8a2d99d, sg:35:a32f87f5a73d99c7, sg:42:329f422d795cf67d, sg:43:f2f5bee2bc12f523, sg:44:5524171aae0946b5, sg:52:2e7f22f8c6c1a019, sg:55:075d6757ad9fea62, sg:59:d3094004aa13722e, sg:63:9c080b5b0f116776, sg:64:a3b27f1c9b025094, sg:65:ce198ee91ed4866c, sg:73:32e817ccb1c5e3ff, sg:76:298fd8e47c3f66a8, sg:80:3a06820ff0a3b2dc, sg:84:580921fa07043992, sg:85:48f0430177edc288, sg:86:b5337a996a62e16a, sg:94:ebdc80663fd930b2, sg:97:681acaa39a9bc201), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; The recorder is not reachable by the agent it records: PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 24 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:148:bf16ebd320021812, sg:149:3a457b22d02d5d00, sg:150:c7d8c1f4e3ba922f, sg:158:990028f1af93efe0, sg:161:031e2e8d26da6042, sg:165:16a2dc1cdba5042c, sg:169:48b4d0685cddb97c, sg:170:0cac8deabbdeb2be, sg:171:668aeb3d76ddd965, sg:179:633e78abdb22cde9, sg:182:316038988f1c15b5, sg:186:c824e180049dd2b9, sg:190:2c686e6a0a4325ea, sg:191:1d4bb4d51ca47470, sg:192:d59dee5e3cfdf13f, sg:200:5b4e409881f95024, sg:203:35588c7155777fa3, sg:207:6c0a670149e7e8b4, sg:211:b0c734a6d6203dd9, sg:212:8d2949464058f0d6, sg:213:9702a206fa3a6787, sg:221:c0f53e4491dfaf77, sg:224:261113f46c0a132c, sg:228:81382ed63fbaed5e), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F229" s="14" t="n"/>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="E255" s="14" t="inlineStr">
         <is>
-          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:114:84532e35fc44e02c, sg:135:ea77e9f3504abbcd, sg:32:62e9084ac5c23150, sg:50:bb2e261c780ea83b, sg:71:6493aa04c046d505, sg:92:6902ec516d57670f), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:156:0410d01f11f7a67b, sg:177:c0fc068544402740, sg:198:2ebfa924ad6244b2, sg:219:8f64ef8ae036aae4), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F255" s="14" t="n"/>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="E256" s="18" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 8 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:117:5f7c32de14792236, sg:138:0da49d2557aa5fbb, sg:25:6dffdc5026b552d8, sg:29:6031e40cffa97197, sg:3:52bf36fd30c28c8e, sg:53:1c2c321ec1d637f7, sg:74:9ea2a20a2cf96f5e, sg:95:107e1bada3f0fcc1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:159:d2f56027459525a6, sg:180:7bd687cabc9b8fae, sg:201:42177fa99ba5562a, sg:222:2c44c57502077f4b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F256" s="18" t="n"/>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="E257" s="14" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 8 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:117:5f7c32de14792236, sg:138:0da49d2557aa5fbb, sg:25:6dffdc5026b552d8, sg:29:6031e40cffa97197, sg:3:52bf36fd30c28c8e, sg:53:1c2c321ec1d637f7, sg:74:9ea2a20a2cf96f5e, sg:95:107e1bada3f0fcc1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:159:d2f56027459525a6, sg:180:7bd687cabc9b8fae, sg:201:42177fa99ba5562a, sg:222:2c44c57502077f4b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F257" s="14" t="n"/>

--- a/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
+++ b/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
@@ -2078,10 +2078,14 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 14 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:152:f5dd0f16ab185e0b, sg:160:8732eae8813b1682, sg:167:af6bb479c89079c9, sg:173:6ce0b01108cbc4b8, sg:181:1d0e1089dc62847e, sg:188:95a9e64d9906694a, sg:194:38e25eb804466a9c, sg:202:e4c30c95efb6cf33, sg:208:0bfb428b6e0f581c, sg:209:971e683e2e94b943, sg:215:4ecc0ca415f27b19, sg:223:503487865ccbe701, sg:229:ffe959c28f930b9c, sg:230:8e3a080457b52971), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F3" s="14" t="n"/>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 24 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:152:f5dd0f16ab185e0b, sg:160:8732eae8813b1682, sg:167:af6bb479c89079c9, sg:173:6ce0b01108cbc4b8, sg:181:1d0e1089dc62847e, sg:188:95a9e64d9906694a, sg:194:38e25eb804466a9c, sg:202:e4c30c95efb6cf33, sg:208:0bfb428b6e0f581c, sg:209:971e683e2e94b943, sg:215:4ecc0ca415f27b19, sg:223:503487865ccbe701, sg:229:ffe959c28f930b9c, sg:230:8e3a080457b52971, sg:231:df82a72a916e2e39, sg:237:c0df5a88e98942f9, sg:245:88c5e56e84954b83, sg:251:a7661561df8dc40a, sg:252:b528a312a5f21438, sg:253:0cb356e7b6fa507b, sg:259:881f49b604e9cbd3, sg:267:92b6a086249dffe3, sg:273:868256386c8ff208, sg:274:6a558da4464d9df1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I3" s="21" t="inlineStr">
         <is>
           <t>A&amp;A-01</t>
@@ -2127,10 +2131,14 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 14 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:152:f5dd0f16ab185e0b, sg:160:8732eae8813b1682, sg:167:af6bb479c89079c9, sg:173:6ce0b01108cbc4b8, sg:181:1d0e1089dc62847e, sg:188:95a9e64d9906694a, sg:194:38e25eb804466a9c, sg:202:e4c30c95efb6cf33, sg:208:0bfb428b6e0f581c, sg:209:971e683e2e94b943, sg:215:4ecc0ca415f27b19, sg:223:503487865ccbe701, sg:229:ffe959c28f930b9c, sg:230:8e3a080457b52971), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F4" s="18" t="n"/>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 24 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:152:f5dd0f16ab185e0b, sg:160:8732eae8813b1682, sg:167:af6bb479c89079c9, sg:173:6ce0b01108cbc4b8, sg:181:1d0e1089dc62847e, sg:188:95a9e64d9906694a, sg:194:38e25eb804466a9c, sg:202:e4c30c95efb6cf33, sg:208:0bfb428b6e0f581c, sg:209:971e683e2e94b943, sg:215:4ecc0ca415f27b19, sg:223:503487865ccbe701, sg:229:ffe959c28f930b9c, sg:230:8e3a080457b52971, sg:231:df82a72a916e2e39, sg:237:c0df5a88e98942f9, sg:245:88c5e56e84954b83, sg:251:a7661561df8dc40a, sg:252:b528a312a5f21438, sg:253:0cb356e7b6fa507b, sg:259:881f49b604e9cbd3, sg:267:92b6a086249dffe3, sg:273:868256386c8ff208, sg:274:6a558da4464d9df1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I4" s="27" t="n"/>
       <c r="J4" s="27" t="n"/>
       <c r="K4" s="27" t="n"/>
@@ -3331,10 +3339,14 @@
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
-          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 10 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:155:b39ce17aaccb624b, sg:163:4522da66473b0891, sg:176:dd3e103543a5f403, sg:184:c86849434d37f2ca, sg:197:1ed5320c1a29c0e4, sg:204:9ea6d3672f1cbb6c, sg:205:3e8f79273c4d99e8, sg:218:fe0f5eee9fdb542d, sg:225:80c4d796e03c26e4, sg:226:6a59e2af4b4ca71b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F44" s="18" t="n"/>
+          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 12 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:163:4522da66473b0891, sg:184:c86849434d37f2ca, sg:204:9ea6d3672f1cbb6c, sg:205:3e8f79273c4d99e8, sg:225:80c4d796e03c26e4, sg:226:6a59e2af4b4ca71b, sg:240:a5d2cdeff651719f, sg:247:701124238565aea3, sg:248:8387bb110d3df1b5, sg:262:3469a49c5dfe33df, sg:269:1b515696ec660f7e, sg:270:bed799f2391778f8), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F44" s="18" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I44" s="21" t="inlineStr">
         <is>
           <t>CCC-01</t>
@@ -3379,10 +3391,14 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 10 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:155:b39ce17aaccb624b, sg:163:4522da66473b0891, sg:176:dd3e103543a5f403, sg:184:c86849434d37f2ca, sg:197:1ed5320c1a29c0e4, sg:204:9ea6d3672f1cbb6c, sg:205:3e8f79273c4d99e8, sg:218:fe0f5eee9fdb542d, sg:225:80c4d796e03c26e4, sg:226:6a59e2af4b4ca71b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F45" s="14" t="n"/>
+          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 12 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:163:4522da66473b0891, sg:184:c86849434d37f2ca, sg:204:9ea6d3672f1cbb6c, sg:205:3e8f79273c4d99e8, sg:225:80c4d796e03c26e4, sg:226:6a59e2af4b4ca71b, sg:240:a5d2cdeff651719f, sg:247:701124238565aea3, sg:248:8387bb110d3df1b5, sg:262:3469a49c5dfe33df, sg:269:1b515696ec660f7e, sg:270:bed799f2391778f8), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I45" s="27" t="n"/>
       <c r="J45" s="27" t="n"/>
       <c r="K45" s="27" t="n"/>
@@ -5365,10 +5381,14 @@
       </c>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 8 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:147:9bebca7095710e7b, sg:164:0a17213da88916a0, sg:168:673efa781a5886af, sg:185:722aa012e9e81176, sg:189:6da7e8855e27abf3, sg:206:e376384aa84cb442, sg:210:b32620de15f05a8a, sg:227:395621be5822edd0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F112" s="18" t="n"/>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 12 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:147:9bebca7095710e7b, sg:164:0a17213da88916a0, sg:168:673efa781a5886af, sg:185:722aa012e9e81176, sg:189:6da7e8855e27abf3, sg:206:e376384aa84cb442, sg:210:b32620de15f05a8a, sg:227:395621be5822edd0, sg:232:51c5900fb397b7a9, sg:249:3593fb118d2fca63, sg:254:0db7ce23ccc53be3, sg:271:d364696547ebe95c), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F112" s="18" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I112" s="21" t="inlineStr">
         <is>
           <t>DSP-05</t>
@@ -5409,10 +5429,14 @@
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 8 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:147:9bebca7095710e7b, sg:164:0a17213da88916a0, sg:168:673efa781a5886af, sg:185:722aa012e9e81176, sg:189:6da7e8855e27abf3, sg:206:e376384aa84cb442, sg:210:b32620de15f05a8a, sg:227:395621be5822edd0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F113" s="14" t="n"/>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 12 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:147:9bebca7095710e7b, sg:164:0a17213da88916a0, sg:168:673efa781a5886af, sg:185:722aa012e9e81176, sg:189:6da7e8855e27abf3, sg:206:e376384aa84cb442, sg:210:b32620de15f05a8a, sg:227:395621be5822edd0, sg:232:51c5900fb397b7a9, sg:249:3593fb118d2fca63, sg:254:0db7ce23ccc53be3, sg:271:d364696547ebe95c), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F113" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I113" s="27" t="n"/>
       <c r="J113" s="27" t="n"/>
       <c r="K113" s="27" t="n"/>
@@ -5930,10 +5954,14 @@
       </c>
       <c r="E130" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 28 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:147:9bebca7095710e7b, sg:153:917bc028692cdd65, sg:154:2aafc34476d15d60, sg:155:b39ce17aaccb624b, sg:156:0410d01f11f7a67b, sg:161:031e2e8d26da6042, sg:167:af6bb479c89079c9, sg:168:673efa781a5886af, sg:174:13f58e0526f7181d, sg:175:ae266bdaf3bcce83, sg:176:dd3e103543a5f403, sg:177:c0fc068544402740, sg:182:316038988f1c15b5, sg:188:95a9e64d9906694a, sg:189:6da7e8855e27abf3, sg:195:7e21be5aabc730de, sg:196:658be324c2a38ac1, sg:197:1ed5320c1a29c0e4, sg:198:2ebfa924ad6244b2, sg:203:35588c7155777fa3, sg:209:971e683e2e94b943, sg:210:b32620de15f05a8a, sg:216:41e4f43c86d8a50c, sg:217:3d31aa054b4df3be, sg:218:fe0f5eee9fdb542d, sg:219:8f64ef8ae036aae4, sg:224:261113f46c0a132c, sg:230:8e3a080457b52971), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F130" s="18" t="n"/>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 36 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:147:9bebca7095710e7b, sg:153:917bc028692cdd65, sg:154:2aafc34476d15d60, sg:161:031e2e8d26da6042, sg:167:af6bb479c89079c9, sg:168:673efa781a5886af, sg:174:13f58e0526f7181d, sg:175:ae266bdaf3bcce83, sg:182:316038988f1c15b5, sg:188:95a9e64d9906694a, sg:189:6da7e8855e27abf3, sg:195:7e21be5aabc730de, sg:196:658be324c2a38ac1, sg:203:35588c7155777fa3, sg:209:971e683e2e94b943, sg:210:b32620de15f05a8a, sg:216:41e4f43c86d8a50c, sg:217:3d31aa054b4df3be, sg:224:261113f46c0a132c, sg:230:8e3a080457b52971, sg:231:df82a72a916e2e39, sg:232:51c5900fb397b7a9, sg:238:79b0a819923d99e7, sg:239:480f556da4997f37, sg:240:a5d2cdeff651719f, sg:241:6ac43f1af968ab3b, sg:246:2f33e49e67f6479d, sg:252:b528a312a5f21438, sg:253:0cb356e7b6fa507b, sg:254:0db7ce23ccc53be3, sg:260:400efe2f44aa8a1d, sg:261:365b5881e76193a9, sg:262:3469a49c5dfe33df, sg:263:28fb5e8aa73620af, sg:268:2bee81eec3bf6fb7, sg:274:6a558da4464d9df1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F130" s="18" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I130" s="21" t="inlineStr">
         <is>
           <t>DSP-20</t>
@@ -8175,10 +8203,14 @@
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:164:0a17213da88916a0, sg:185:722aa012e9e81176, sg:206:e376384aa84cb442, sg:227:395621be5822edd0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F203" s="14" t="n"/>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:164:0a17213da88916a0, sg:185:722aa012e9e81176, sg:206:e376384aa84cb442, sg:227:395621be5822edd0, sg:249:3593fb118d2fca63, sg:271:d364696547ebe95c), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F203" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I203" s="21" t="inlineStr">
         <is>
           <t>I&amp;S-01</t>
@@ -8223,10 +8255,14 @@
       </c>
       <c r="E204" s="18" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:164:0a17213da88916a0, sg:185:722aa012e9e81176, sg:206:e376384aa84cb442, sg:227:395621be5822edd0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F204" s="18" t="n"/>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:164:0a17213da88916a0, sg:185:722aa012e9e81176, sg:206:e376384aa84cb442, sg:227:395621be5822edd0, sg:249:3593fb118d2fca63, sg:271:d364696547ebe95c), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F204" s="18" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I204" s="27" t="n"/>
       <c r="J204" s="27" t="n"/>
       <c r="K204" s="27" t="n"/>
@@ -8669,10 +8705,14 @@
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 16 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:148:bf16ebd320021812, sg:151:09827d850c759c55, sg:152:f5dd0f16ab185e0b, sg:159:d2f56027459525a6, sg:169:48b4d0685cddb97c, sg:172:5926dd73b82f20ac, sg:173:6ce0b01108cbc4b8, sg:180:7bd687cabc9b8fae, sg:190:2c686e6a0a4325ea, sg:193:6533b7a7ff0dc797, sg:194:38e25eb804466a9c, sg:201:42177fa99ba5562a, sg:211:b0c734a6d6203dd9, sg:214:b56d0a70c597d937, sg:215:4ecc0ca415f27b19, sg:222:2c44c57502077f4b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F219" s="14" t="n"/>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 24 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:148:bf16ebd320021812, sg:151:09827d850c759c55, sg:152:f5dd0f16ab185e0b, sg:159:d2f56027459525a6, sg:169:48b4d0685cddb97c, sg:172:5926dd73b82f20ac, sg:173:6ce0b01108cbc4b8, sg:180:7bd687cabc9b8fae, sg:190:2c686e6a0a4325ea, sg:193:6533b7a7ff0dc797, sg:194:38e25eb804466a9c, sg:201:42177fa99ba5562a, sg:211:b0c734a6d6203dd9, sg:214:b56d0a70c597d937, sg:215:4ecc0ca415f27b19, sg:222:2c44c57502077f4b, sg:233:1efbe62fc88b526e, sg:236:7f50e965f9dc790f, sg:237:c0df5a88e98942f9, sg:244:8826477dd70d712c, sg:255:39ea635315afb679, sg:258:b0024a88e878db5d, sg:259:881f49b604e9cbd3, sg:266:92bc3e0f05ebea4e), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F219" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I219" s="21" t="inlineStr">
         <is>
           <t>LOG-03</t>
@@ -8717,10 +8757,14 @@
       </c>
       <c r="E220" s="18" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 16 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:148:bf16ebd320021812, sg:151:09827d850c759c55, sg:152:f5dd0f16ab185e0b, sg:159:d2f56027459525a6, sg:169:48b4d0685cddb97c, sg:172:5926dd73b82f20ac, sg:173:6ce0b01108cbc4b8, sg:180:7bd687cabc9b8fae, sg:190:2c686e6a0a4325ea, sg:193:6533b7a7ff0dc797, sg:194:38e25eb804466a9c, sg:201:42177fa99ba5562a, sg:211:b0c734a6d6203dd9, sg:214:b56d0a70c597d937, sg:215:4ecc0ca415f27b19, sg:222:2c44c57502077f4b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F220" s="18" t="n"/>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 24 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:148:bf16ebd320021812, sg:151:09827d850c759c55, sg:152:f5dd0f16ab185e0b, sg:159:d2f56027459525a6, sg:169:48b4d0685cddb97c, sg:172:5926dd73b82f20ac, sg:173:6ce0b01108cbc4b8, sg:180:7bd687cabc9b8fae, sg:190:2c686e6a0a4325ea, sg:193:6533b7a7ff0dc797, sg:194:38e25eb804466a9c, sg:201:42177fa99ba5562a, sg:211:b0c734a6d6203dd9, sg:214:b56d0a70c597d937, sg:215:4ecc0ca415f27b19, sg:222:2c44c57502077f4b, sg:233:1efbe62fc88b526e, sg:236:7f50e965f9dc790f, sg:237:c0df5a88e98942f9, sg:244:8826477dd70d712c, sg:255:39ea635315afb679, sg:258:b0024a88e878db5d, sg:259:881f49b604e9cbd3, sg:266:92bc3e0f05ebea4e), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F220" s="18" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I220" s="27" t="n"/>
       <c r="J220" s="27" t="n"/>
       <c r="K220" s="27" t="n"/>
@@ -8990,10 +9034,14 @@
       </c>
       <c r="E229" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; The recorder is not reachable by the agent it records: PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 24 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:148:bf16ebd320021812, sg:149:3a457b22d02d5d00, sg:150:c7d8c1f4e3ba922f, sg:158:990028f1af93efe0, sg:161:031e2e8d26da6042, sg:165:16a2dc1cdba5042c, sg:169:48b4d0685cddb97c, sg:170:0cac8deabbdeb2be, sg:171:668aeb3d76ddd965, sg:179:633e78abdb22cde9, sg:182:316038988f1c15b5, sg:186:c824e180049dd2b9, sg:190:2c686e6a0a4325ea, sg:191:1d4bb4d51ca47470, sg:192:d59dee5e3cfdf13f, sg:200:5b4e409881f95024, sg:203:35588c7155777fa3, sg:207:6c0a670149e7e8b4, sg:211:b0c734a6d6203dd9, sg:212:8d2949464058f0d6, sg:213:9702a206fa3a6787, sg:221:c0f53e4491dfaf77, sg:224:261113f46c0a132c, sg:228:81382ed63fbaed5e), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F229" s="14" t="n"/>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; The recorder is not reachable by the agent it records: PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 36 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:148:bf16ebd320021812, sg:149:3a457b22d02d5d00, sg:150:c7d8c1f4e3ba922f, sg:158:990028f1af93efe0, sg:161:031e2e8d26da6042, sg:165:16a2dc1cdba5042c, sg:169:48b4d0685cddb97c, sg:170:0cac8deabbdeb2be, sg:171:668aeb3d76ddd965, sg:179:633e78abdb22cde9, sg:182:316038988f1c15b5, sg:186:c824e180049dd2b9, sg:190:2c686e6a0a4325ea, sg:191:1d4bb4d51ca47470, sg:192:d59dee5e3cfdf13f, sg:200:5b4e409881f95024, sg:203:35588c7155777fa3, sg:207:6c0a670149e7e8b4, sg:211:b0c734a6d6203dd9, sg:212:8d2949464058f0d6, sg:213:9702a206fa3a6787, sg:221:c0f53e4491dfaf77, sg:224:261113f46c0a132c, sg:228:81382ed63fbaed5e, sg:233:1efbe62fc88b526e, sg:234:97e84699bae989a7, sg:235:f85e4d3d4524f521, sg:243:afd6d8a495c70f64, sg:246:2f33e49e67f6479d, sg:250:53492bd4e3472c80, sg:255:39ea635315afb679, sg:256:8548adf23e7b24c7, sg:257:a9a52f5a89458875, sg:265:99c5554aae1129ba, sg:268:2bee81eec3bf6fb7, sg:272:1b9b7f40f252c52a), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F229" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I229" s="21" t="inlineStr">
         <is>
           <t>LOG-10</t>
@@ -9069,7 +9117,11 @@
           <t>No. There is artifact-level and decision-level provenance, but no continuous activity log for cryptographic key lifecycle events specifically. Evidence searched: stop_guessing/attest/keys.py, stop_guessing/ledger/, rules/, policy/coc.policy.d/.</t>
         </is>
       </c>
-      <c r="F231" s="14" t="n"/>
+      <c r="F231" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I231" s="21" t="inlineStr">
         <is>
           <t>LOG-12</t>
@@ -9766,10 +9818,14 @@
       </c>
       <c r="E255" s="14" t="inlineStr">
         <is>
-          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:156:0410d01f11f7a67b, sg:177:c0fc068544402740, sg:198:2ebfa924ad6244b2, sg:219:8f64ef8ae036aae4), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F255" s="14" t="n"/>
+          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:241:6ac43f1af968ab3b, sg:263:28fb5e8aa73620af), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F255" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I255" s="21" t="inlineStr">
         <is>
           <t>MDS-13</t>
@@ -9810,10 +9866,14 @@
       </c>
       <c r="E256" s="18" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:159:d2f56027459525a6, sg:180:7bd687cabc9b8fae, sg:201:42177fa99ba5562a, sg:222:2c44c57502077f4b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F256" s="18" t="n"/>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:159:d2f56027459525a6, sg:180:7bd687cabc9b8fae, sg:201:42177fa99ba5562a, sg:222:2c44c57502077f4b, sg:244:8826477dd70d712c, sg:266:92bc3e0f05ebea4e), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F256" s="18" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I256" s="21" t="inlineStr">
         <is>
           <t>SEF-01</t>
@@ -9858,10 +9918,14 @@
       </c>
       <c r="E257" s="14" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:159:d2f56027459525a6, sg:180:7bd687cabc9b8fae, sg:201:42177fa99ba5562a, sg:222:2c44c57502077f4b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F257" s="14" t="n"/>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:159:d2f56027459525a6, sg:180:7bd687cabc9b8fae, sg:201:42177fa99ba5562a, sg:222:2c44c57502077f4b, sg:244:8826477dd70d712c, sg:266:92bc3e0f05ebea4e), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F257" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I257" s="27" t="n"/>
       <c r="J257" s="27" t="n"/>
       <c r="K257" s="27" t="n"/>
@@ -10601,7 +10665,11 @@
           <t>No. A service Bill of Materials is not emitted. The in-toto Statement envelope and the pinned MANIFEST.sha256 over the vendored tree are adjacent but are not an SBOM. Evidence searched: stop_guessing/attest/, stop_guessing/compat/, .github/workflows/.</t>
         </is>
       </c>
-      <c r="F282" s="18" t="n"/>
+      <c r="F282" s="18" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I282" s="21" t="inlineStr">
         <is>
           <t>STA-09</t>
@@ -10645,7 +10713,11 @@
           <t>No. A service Bill of Materials is not emitted. The in-toto Statement envelope and the pinned MANIFEST.sha256 over the vendored tree are adjacent but are not an SBOM. Evidence searched: stop_guessing/attest/, stop_guessing/compat/, .github/workflows/.</t>
         </is>
       </c>
-      <c r="F283" s="14" t="n"/>
+      <c r="F283" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I283" s="27" t="n"/>
       <c r="J283" s="27" t="n"/>
       <c r="K283" s="27" t="n"/>

--- a/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
+++ b/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
@@ -2078,7 +2078,7 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 24 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:152:f5dd0f16ab185e0b, sg:160:8732eae8813b1682, sg:167:af6bb479c89079c9, sg:173:6ce0b01108cbc4b8, sg:181:1d0e1089dc62847e, sg:188:95a9e64d9906694a, sg:194:38e25eb804466a9c, sg:202:e4c30c95efb6cf33, sg:208:0bfb428b6e0f581c, sg:209:971e683e2e94b943, sg:215:4ecc0ca415f27b19, sg:223:503487865ccbe701, sg:229:ffe959c28f930b9c, sg:230:8e3a080457b52971, sg:231:df82a72a916e2e39, sg:237:c0df5a88e98942f9, sg:245:88c5e56e84954b83, sg:251:a7661561df8dc40a, sg:252:b528a312a5f21438, sg:253:0cb356e7b6fa507b, sg:259:881f49b604e9cbd3, sg:267:92b6a086249dffe3, sg:273:868256386c8ff208, sg:274:6a558da4464d9df1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 34 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:152:f5dd0f16ab185e0b, sg:160:8732eae8813b1682, sg:167:af6bb479c89079c9, sg:173:6ce0b01108cbc4b8, sg:181:1d0e1089dc62847e, sg:188:95a9e64d9906694a, sg:194:38e25eb804466a9c, sg:202:e4c30c95efb6cf33, sg:208:0bfb428b6e0f581c, sg:209:971e683e2e94b943, sg:215:4ecc0ca415f27b19, sg:223:503487865ccbe701, sg:229:ffe959c28f930b9c, sg:230:8e3a080457b52971, sg:231:df82a72a916e2e39, sg:237:c0df5a88e98942f9, sg:245:88c5e56e84954b83, sg:251:a7661561df8dc40a, sg:252:b528a312a5f21438, sg:253:0cb356e7b6fa507b, sg:259:881f49b604e9cbd3, sg:267:92b6a086249dffe3, sg:273:868256386c8ff208, sg:274:6a558da4464d9df1, sg:275:5299338ac0a9a43c, sg:281:52e551b5fc9278ad, sg:289:30f1e565fa854137, sg:295:8e33873d245ad0bf, sg:296:aedd16d7928438c8, sg:302:56b983a216b4cd18, sg:310:451b8c6abb6d6996, sg:316:f060754097c8b8c2, sg:317:bdd759456a8aadde, sg:318:d12551e640049a82), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 24 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:152:f5dd0f16ab185e0b, sg:160:8732eae8813b1682, sg:167:af6bb479c89079c9, sg:173:6ce0b01108cbc4b8, sg:181:1d0e1089dc62847e, sg:188:95a9e64d9906694a, sg:194:38e25eb804466a9c, sg:202:e4c30c95efb6cf33, sg:208:0bfb428b6e0f581c, sg:209:971e683e2e94b943, sg:215:4ecc0ca415f27b19, sg:223:503487865ccbe701, sg:229:ffe959c28f930b9c, sg:230:8e3a080457b52971, sg:231:df82a72a916e2e39, sg:237:c0df5a88e98942f9, sg:245:88c5e56e84954b83, sg:251:a7661561df8dc40a, sg:252:b528a312a5f21438, sg:253:0cb356e7b6fa507b, sg:259:881f49b604e9cbd3, sg:267:92b6a086249dffe3, sg:273:868256386c8ff208, sg:274:6a558da4464d9df1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 34 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:152:f5dd0f16ab185e0b, sg:160:8732eae8813b1682, sg:167:af6bb479c89079c9, sg:173:6ce0b01108cbc4b8, sg:181:1d0e1089dc62847e, sg:188:95a9e64d9906694a, sg:194:38e25eb804466a9c, sg:202:e4c30c95efb6cf33, sg:208:0bfb428b6e0f581c, sg:209:971e683e2e94b943, sg:215:4ecc0ca415f27b19, sg:223:503487865ccbe701, sg:229:ffe959c28f930b9c, sg:230:8e3a080457b52971, sg:231:df82a72a916e2e39, sg:237:c0df5a88e98942f9, sg:245:88c5e56e84954b83, sg:251:a7661561df8dc40a, sg:252:b528a312a5f21438, sg:253:0cb356e7b6fa507b, sg:259:881f49b604e9cbd3, sg:267:92b6a086249dffe3, sg:273:868256386c8ff208, sg:274:6a558da4464d9df1, sg:275:5299338ac0a9a43c, sg:281:52e551b5fc9278ad, sg:289:30f1e565fa854137, sg:295:8e33873d245ad0bf, sg:296:aedd16d7928438c8, sg:302:56b983a216b4cd18, sg:310:451b8c6abb6d6996, sg:316:f060754097c8b8c2, sg:317:bdd759456a8aadde, sg:318:d12551e640049a82), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F4" s="18" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
-          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 12 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:163:4522da66473b0891, sg:184:c86849434d37f2ca, sg:204:9ea6d3672f1cbb6c, sg:205:3e8f79273c4d99e8, sg:225:80c4d796e03c26e4, sg:226:6a59e2af4b4ca71b, sg:240:a5d2cdeff651719f, sg:247:701124238565aea3, sg:248:8387bb110d3df1b5, sg:262:3469a49c5dfe33df, sg:269:1b515696ec660f7e, sg:270:bed799f2391778f8), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 18 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:163:4522da66473b0891, sg:184:c86849434d37f2ca, sg:204:9ea6d3672f1cbb6c, sg:205:3e8f79273c4d99e8, sg:225:80c4d796e03c26e4, sg:226:6a59e2af4b4ca71b, sg:240:a5d2cdeff651719f, sg:247:701124238565aea3, sg:248:8387bb110d3df1b5, sg:262:3469a49c5dfe33df, sg:269:1b515696ec660f7e, sg:270:bed799f2391778f8, sg:284:f0cc0e2554ff036e, sg:291:65036624ecd070da, sg:292:db118c5c341e9374, sg:305:13464f3fece64c57, sg:312:719cda02320ce051, sg:313:2c32160817ca4657), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F44" s="18" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 12 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:163:4522da66473b0891, sg:184:c86849434d37f2ca, sg:204:9ea6d3672f1cbb6c, sg:205:3e8f79273c4d99e8, sg:225:80c4d796e03c26e4, sg:226:6a59e2af4b4ca71b, sg:240:a5d2cdeff651719f, sg:247:701124238565aea3, sg:248:8387bb110d3df1b5, sg:262:3469a49c5dfe33df, sg:269:1b515696ec660f7e, sg:270:bed799f2391778f8), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 18 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:163:4522da66473b0891, sg:184:c86849434d37f2ca, sg:204:9ea6d3672f1cbb6c, sg:205:3e8f79273c4d99e8, sg:225:80c4d796e03c26e4, sg:226:6a59e2af4b4ca71b, sg:240:a5d2cdeff651719f, sg:247:701124238565aea3, sg:248:8387bb110d3df1b5, sg:262:3469a49c5dfe33df, sg:269:1b515696ec660f7e, sg:270:bed799f2391778f8, sg:284:f0cc0e2554ff036e, sg:291:65036624ecd070da, sg:292:db118c5c341e9374, sg:305:13464f3fece64c57, sg:312:719cda02320ce051, sg:313:2c32160817ca4657), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 12 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:147:9bebca7095710e7b, sg:164:0a17213da88916a0, sg:168:673efa781a5886af, sg:185:722aa012e9e81176, sg:189:6da7e8855e27abf3, sg:206:e376384aa84cb442, sg:210:b32620de15f05a8a, sg:227:395621be5822edd0, sg:232:51c5900fb397b7a9, sg:249:3593fb118d2fca63, sg:254:0db7ce23ccc53be3, sg:271:d364696547ebe95c), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 16 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:147:9bebca7095710e7b, sg:164:0a17213da88916a0, sg:168:673efa781a5886af, sg:185:722aa012e9e81176, sg:189:6da7e8855e27abf3, sg:206:e376384aa84cb442, sg:210:b32620de15f05a8a, sg:227:395621be5822edd0, sg:232:51c5900fb397b7a9, sg:249:3593fb118d2fca63, sg:254:0db7ce23ccc53be3, sg:271:d364696547ebe95c, sg:276:4bbae7bcafd12d98, sg:293:f73310695b98f452, sg:297:7e43ee8cd5f34c63, sg:314:c5482c11a08df3ec), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F112" s="18" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 12 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:147:9bebca7095710e7b, sg:164:0a17213da88916a0, sg:168:673efa781a5886af, sg:185:722aa012e9e81176, sg:189:6da7e8855e27abf3, sg:206:e376384aa84cb442, sg:210:b32620de15f05a8a, sg:227:395621be5822edd0, sg:232:51c5900fb397b7a9, sg:249:3593fb118d2fca63, sg:254:0db7ce23ccc53be3, sg:271:d364696547ebe95c), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 16 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:147:9bebca7095710e7b, sg:164:0a17213da88916a0, sg:168:673efa781a5886af, sg:185:722aa012e9e81176, sg:189:6da7e8855e27abf3, sg:206:e376384aa84cb442, sg:210:b32620de15f05a8a, sg:227:395621be5822edd0, sg:232:51c5900fb397b7a9, sg:249:3593fb118d2fca63, sg:254:0db7ce23ccc53be3, sg:271:d364696547ebe95c, sg:276:4bbae7bcafd12d98, sg:293:f73310695b98f452, sg:297:7e43ee8cd5f34c63, sg:314:c5482c11a08df3ec), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F113" s="14" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="E130" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 36 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:147:9bebca7095710e7b, sg:153:917bc028692cdd65, sg:154:2aafc34476d15d60, sg:161:031e2e8d26da6042, sg:167:af6bb479c89079c9, sg:168:673efa781a5886af, sg:174:13f58e0526f7181d, sg:175:ae266bdaf3bcce83, sg:182:316038988f1c15b5, sg:188:95a9e64d9906694a, sg:189:6da7e8855e27abf3, sg:195:7e21be5aabc730de, sg:196:658be324c2a38ac1, sg:203:35588c7155777fa3, sg:209:971e683e2e94b943, sg:210:b32620de15f05a8a, sg:216:41e4f43c86d8a50c, sg:217:3d31aa054b4df3be, sg:224:261113f46c0a132c, sg:230:8e3a080457b52971, sg:231:df82a72a916e2e39, sg:232:51c5900fb397b7a9, sg:238:79b0a819923d99e7, sg:239:480f556da4997f37, sg:240:a5d2cdeff651719f, sg:241:6ac43f1af968ab3b, sg:246:2f33e49e67f6479d, sg:252:b528a312a5f21438, sg:253:0cb356e7b6fa507b, sg:254:0db7ce23ccc53be3, sg:260:400efe2f44aa8a1d, sg:261:365b5881e76193a9, sg:262:3469a49c5dfe33df, sg:263:28fb5e8aa73620af, sg:268:2bee81eec3bf6fb7, sg:274:6a558da4464d9df1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 52 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:147:9bebca7095710e7b, sg:153:917bc028692cdd65, sg:154:2aafc34476d15d60, sg:161:031e2e8d26da6042, sg:167:af6bb479c89079c9, sg:168:673efa781a5886af, sg:174:13f58e0526f7181d, sg:175:ae266bdaf3bcce83, sg:182:316038988f1c15b5, sg:188:95a9e64d9906694a, sg:189:6da7e8855e27abf3, sg:195:7e21be5aabc730de, sg:196:658be324c2a38ac1, sg:203:35588c7155777fa3, sg:209:971e683e2e94b943, sg:210:b32620de15f05a8a, sg:216:41e4f43c86d8a50c, sg:217:3d31aa054b4df3be, sg:224:261113f46c0a132c, sg:230:8e3a080457b52971, sg:231:df82a72a916e2e39, sg:232:51c5900fb397b7a9, sg:238:79b0a819923d99e7, sg:239:480f556da4997f37, sg:240:a5d2cdeff651719f, sg:241:6ac43f1af968ab3b, sg:246:2f33e49e67f6479d, sg:252:b528a312a5f21438, sg:253:0cb356e7b6fa507b, sg:254:0db7ce23ccc53be3, sg:260:400efe2f44aa8a1d, sg:261:365b5881e76193a9, sg:262:3469a49c5dfe33df, sg:263:28fb5e8aa73620af, sg:268:2bee81eec3bf6fb7, sg:274:6a558da4464d9df1, sg:275:5299338ac0a9a43c, sg:276:4bbae7bcafd12d98, sg:282:cdc77fb63822474d, sg:283:896c397b8d94a589, sg:284:f0cc0e2554ff036e, sg:285:6ddb23f185aaff4f, sg:290:705836796517f406, sg:296:aedd16d7928438c8, sg:297:7e43ee8cd5f34c63, sg:303:e87c265eb14beb6d, sg:304:3ec3de027f118201, sg:305:13464f3fece64c57, sg:306:99555fd6fcbe2e30, sg:311:95ec1f7a98fc8040, sg:317:bdd759456a8aadde, sg:318:d12551e640049a82), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F130" s="18" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:164:0a17213da88916a0, sg:185:722aa012e9e81176, sg:206:e376384aa84cb442, sg:227:395621be5822edd0, sg:249:3593fb118d2fca63, sg:271:d364696547ebe95c), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 8 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:164:0a17213da88916a0, sg:185:722aa012e9e81176, sg:206:e376384aa84cb442, sg:227:395621be5822edd0, sg:249:3593fb118d2fca63, sg:271:d364696547ebe95c, sg:293:f73310695b98f452, sg:314:c5482c11a08df3ec), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F203" s="14" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="E204" s="18" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:164:0a17213da88916a0, sg:185:722aa012e9e81176, sg:206:e376384aa84cb442, sg:227:395621be5822edd0, sg:249:3593fb118d2fca63, sg:271:d364696547ebe95c), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 8 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:164:0a17213da88916a0, sg:185:722aa012e9e81176, sg:206:e376384aa84cb442, sg:227:395621be5822edd0, sg:249:3593fb118d2fca63, sg:271:d364696547ebe95c, sg:293:f73310695b98f452, sg:314:c5482c11a08df3ec), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F204" s="18" t="inlineStr">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 24 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:148:bf16ebd320021812, sg:151:09827d850c759c55, sg:152:f5dd0f16ab185e0b, sg:159:d2f56027459525a6, sg:169:48b4d0685cddb97c, sg:172:5926dd73b82f20ac, sg:173:6ce0b01108cbc4b8, sg:180:7bd687cabc9b8fae, sg:190:2c686e6a0a4325ea, sg:193:6533b7a7ff0dc797, sg:194:38e25eb804466a9c, sg:201:42177fa99ba5562a, sg:211:b0c734a6d6203dd9, sg:214:b56d0a70c597d937, sg:215:4ecc0ca415f27b19, sg:222:2c44c57502077f4b, sg:233:1efbe62fc88b526e, sg:236:7f50e965f9dc790f, sg:237:c0df5a88e98942f9, sg:244:8826477dd70d712c, sg:255:39ea635315afb679, sg:258:b0024a88e878db5d, sg:259:881f49b604e9cbd3, sg:266:92bc3e0f05ebea4e), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 33 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:148:bf16ebd320021812, sg:151:09827d850c759c55, sg:152:f5dd0f16ab185e0b, sg:159:d2f56027459525a6, sg:169:48b4d0685cddb97c, sg:172:5926dd73b82f20ac, sg:173:6ce0b01108cbc4b8, sg:180:7bd687cabc9b8fae, sg:190:2c686e6a0a4325ea, sg:193:6533b7a7ff0dc797, sg:194:38e25eb804466a9c, sg:201:42177fa99ba5562a, sg:211:b0c734a6d6203dd9, sg:214:b56d0a70c597d937, sg:215:4ecc0ca415f27b19, sg:222:2c44c57502077f4b, sg:233:1efbe62fc88b526e, sg:236:7f50e965f9dc790f, sg:237:c0df5a88e98942f9, sg:244:8826477dd70d712c, sg:255:39ea635315afb679, sg:258:b0024a88e878db5d, sg:259:881f49b604e9cbd3, sg:266:92bc3e0f05ebea4e, sg:277:fd3a8aa73909435b, sg:280:dd326b8bbbd4e63c, sg:281:52e551b5fc9278ad, sg:288:96af66ac3d62eb4b, sg:298:01ad0ac7f4518cb0, sg:301:6859f91aa9ed302a, sg:302:56b983a216b4cd18, sg:309:98823423f402cc78, sg:319:6573641a8a90838a), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F219" s="14" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="E220" s="18" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 24 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:148:bf16ebd320021812, sg:151:09827d850c759c55, sg:152:f5dd0f16ab185e0b, sg:159:d2f56027459525a6, sg:169:48b4d0685cddb97c, sg:172:5926dd73b82f20ac, sg:173:6ce0b01108cbc4b8, sg:180:7bd687cabc9b8fae, sg:190:2c686e6a0a4325ea, sg:193:6533b7a7ff0dc797, sg:194:38e25eb804466a9c, sg:201:42177fa99ba5562a, sg:211:b0c734a6d6203dd9, sg:214:b56d0a70c597d937, sg:215:4ecc0ca415f27b19, sg:222:2c44c57502077f4b, sg:233:1efbe62fc88b526e, sg:236:7f50e965f9dc790f, sg:237:c0df5a88e98942f9, sg:244:8826477dd70d712c, sg:255:39ea635315afb679, sg:258:b0024a88e878db5d, sg:259:881f49b604e9cbd3, sg:266:92bc3e0f05ebea4e), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 33 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:148:bf16ebd320021812, sg:151:09827d850c759c55, sg:152:f5dd0f16ab185e0b, sg:159:d2f56027459525a6, sg:169:48b4d0685cddb97c, sg:172:5926dd73b82f20ac, sg:173:6ce0b01108cbc4b8, sg:180:7bd687cabc9b8fae, sg:190:2c686e6a0a4325ea, sg:193:6533b7a7ff0dc797, sg:194:38e25eb804466a9c, sg:201:42177fa99ba5562a, sg:211:b0c734a6d6203dd9, sg:214:b56d0a70c597d937, sg:215:4ecc0ca415f27b19, sg:222:2c44c57502077f4b, sg:233:1efbe62fc88b526e, sg:236:7f50e965f9dc790f, sg:237:c0df5a88e98942f9, sg:244:8826477dd70d712c, sg:255:39ea635315afb679, sg:258:b0024a88e878db5d, sg:259:881f49b604e9cbd3, sg:266:92bc3e0f05ebea4e, sg:277:fd3a8aa73909435b, sg:280:dd326b8bbbd4e63c, sg:281:52e551b5fc9278ad, sg:288:96af66ac3d62eb4b, sg:298:01ad0ac7f4518cb0, sg:301:6859f91aa9ed302a, sg:302:56b983a216b4cd18, sg:309:98823423f402cc78, sg:319:6573641a8a90838a), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F220" s="18" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="E229" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; The recorder is not reachable by the agent it records: PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 36 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:148:bf16ebd320021812, sg:149:3a457b22d02d5d00, sg:150:c7d8c1f4e3ba922f, sg:158:990028f1af93efe0, sg:161:031e2e8d26da6042, sg:165:16a2dc1cdba5042c, sg:169:48b4d0685cddb97c, sg:170:0cac8deabbdeb2be, sg:171:668aeb3d76ddd965, sg:179:633e78abdb22cde9, sg:182:316038988f1c15b5, sg:186:c824e180049dd2b9, sg:190:2c686e6a0a4325ea, sg:191:1d4bb4d51ca47470, sg:192:d59dee5e3cfdf13f, sg:200:5b4e409881f95024, sg:203:35588c7155777fa3, sg:207:6c0a670149e7e8b4, sg:211:b0c734a6d6203dd9, sg:212:8d2949464058f0d6, sg:213:9702a206fa3a6787, sg:221:c0f53e4491dfaf77, sg:224:261113f46c0a132c, sg:228:81382ed63fbaed5e, sg:233:1efbe62fc88b526e, sg:234:97e84699bae989a7, sg:235:f85e4d3d4524f521, sg:243:afd6d8a495c70f64, sg:246:2f33e49e67f6479d, sg:250:53492bd4e3472c80, sg:255:39ea635315afb679, sg:256:8548adf23e7b24c7, sg:257:a9a52f5a89458875, sg:265:99c5554aae1129ba, sg:268:2bee81eec3bf6fb7, sg:272:1b9b7f40f252c52a), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; The recorder is not reachable by the agent it records: PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 49 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:148:bf16ebd320021812, sg:149:3a457b22d02d5d00, sg:150:c7d8c1f4e3ba922f, sg:158:990028f1af93efe0, sg:161:031e2e8d26da6042, sg:165:16a2dc1cdba5042c, sg:169:48b4d0685cddb97c, sg:170:0cac8deabbdeb2be, sg:171:668aeb3d76ddd965, sg:179:633e78abdb22cde9, sg:182:316038988f1c15b5, sg:186:c824e180049dd2b9, sg:190:2c686e6a0a4325ea, sg:191:1d4bb4d51ca47470, sg:192:d59dee5e3cfdf13f, sg:200:5b4e409881f95024, sg:203:35588c7155777fa3, sg:207:6c0a670149e7e8b4, sg:211:b0c734a6d6203dd9, sg:212:8d2949464058f0d6, sg:213:9702a206fa3a6787, sg:221:c0f53e4491dfaf77, sg:224:261113f46c0a132c, sg:228:81382ed63fbaed5e, sg:233:1efbe62fc88b526e, sg:234:97e84699bae989a7, sg:235:f85e4d3d4524f521, sg:243:afd6d8a495c70f64, sg:246:2f33e49e67f6479d, sg:250:53492bd4e3472c80, sg:255:39ea635315afb679, sg:256:8548adf23e7b24c7, sg:257:a9a52f5a89458875, sg:265:99c5554aae1129ba, sg:268:2bee81eec3bf6fb7, sg:272:1b9b7f40f252c52a, sg:277:fd3a8aa73909435b, sg:278:c4bf3eedc0efbd9d, sg:279:7142c6b87fd79ff2, sg:287:6ae0009f5fb3c8c9, sg:290:705836796517f406, sg:294:ff5c7e6fb37d81ef, sg:298:01ad0ac7f4518cb0, sg:299:aac6ce5f2fda13ce, sg:300:1b44cef550a2dd88, sg:308:ec5f2f5862aa4937, sg:311:95ec1f7a98fc8040, sg:315:2bc1dca6b1bab0e5, sg:319:6573641a8a90838a), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F229" s="14" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="E255" s="14" t="inlineStr">
         <is>
-          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:241:6ac43f1af968ab3b, sg:263:28fb5e8aa73620af), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:241:6ac43f1af968ab3b, sg:263:28fb5e8aa73620af, sg:285:6ddb23f185aaff4f, sg:306:99555fd6fcbe2e30), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F255" s="14" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="E256" s="18" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:159:d2f56027459525a6, sg:180:7bd687cabc9b8fae, sg:201:42177fa99ba5562a, sg:222:2c44c57502077f4b, sg:244:8826477dd70d712c, sg:266:92bc3e0f05ebea4e), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 8 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:159:d2f56027459525a6, sg:180:7bd687cabc9b8fae, sg:201:42177fa99ba5562a, sg:222:2c44c57502077f4b, sg:244:8826477dd70d712c, sg:266:92bc3e0f05ebea4e, sg:288:96af66ac3d62eb4b, sg:309:98823423f402cc78), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F256" s="18" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="E257" s="14" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:159:d2f56027459525a6, sg:180:7bd687cabc9b8fae, sg:201:42177fa99ba5562a, sg:222:2c44c57502077f4b, sg:244:8826477dd70d712c, sg:266:92bc3e0f05ebea4e), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 8 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:159:d2f56027459525a6, sg:180:7bd687cabc9b8fae, sg:201:42177fa99ba5562a, sg:222:2c44c57502077f4b, sg:244:8826477dd70d712c, sg:266:92bc3e0f05ebea4e, sg:288:96af66ac3d62eb4b, sg:309:98823423f402cc78), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F257" s="14" t="inlineStr">

--- a/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
+++ b/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
@@ -2078,7 +2078,7 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 34 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:152:f5dd0f16ab185e0b, sg:160:8732eae8813b1682, sg:167:af6bb479c89079c9, sg:173:6ce0b01108cbc4b8, sg:181:1d0e1089dc62847e, sg:188:95a9e64d9906694a, sg:194:38e25eb804466a9c, sg:202:e4c30c95efb6cf33, sg:208:0bfb428b6e0f581c, sg:209:971e683e2e94b943, sg:215:4ecc0ca415f27b19, sg:223:503487865ccbe701, sg:229:ffe959c28f930b9c, sg:230:8e3a080457b52971, sg:231:df82a72a916e2e39, sg:237:c0df5a88e98942f9, sg:245:88c5e56e84954b83, sg:251:a7661561df8dc40a, sg:252:b528a312a5f21438, sg:253:0cb356e7b6fa507b, sg:259:881f49b604e9cbd3, sg:267:92b6a086249dffe3, sg:273:868256386c8ff208, sg:274:6a558da4464d9df1, sg:275:5299338ac0a9a43c, sg:281:52e551b5fc9278ad, sg:289:30f1e565fa854137, sg:295:8e33873d245ad0bf, sg:296:aedd16d7928438c8, sg:302:56b983a216b4cd18, sg:310:451b8c6abb6d6996, sg:316:f060754097c8b8c2, sg:317:bdd759456a8aadde, sg:318:d12551e640049a82), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 39 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:152:f5dd0f16ab185e0b, sg:160:8732eae8813b1682, sg:167:af6bb479c89079c9, sg:173:6ce0b01108cbc4b8, sg:181:1d0e1089dc62847e, sg:188:95a9e64d9906694a, sg:194:38e25eb804466a9c, sg:202:e4c30c95efb6cf33, sg:208:0bfb428b6e0f581c, sg:209:971e683e2e94b943, sg:215:4ecc0ca415f27b19, sg:223:503487865ccbe701, sg:229:ffe959c28f930b9c, sg:230:8e3a080457b52971, sg:231:df82a72a916e2e39, sg:237:c0df5a88e98942f9, sg:245:88c5e56e84954b83, sg:251:a7661561df8dc40a, sg:252:b528a312a5f21438, sg:253:0cb356e7b6fa507b, sg:259:881f49b604e9cbd3, sg:267:92b6a086249dffe3, sg:273:868256386c8ff208, sg:274:6a558da4464d9df1, sg:275:5299338ac0a9a43c, sg:281:52e551b5fc9278ad, sg:289:30f1e565fa854137, sg:295:8e33873d245ad0bf, sg:296:aedd16d7928438c8, sg:302:56b983a216b4cd18, sg:310:451b8c6abb6d6996, sg:316:f060754097c8b8c2, sg:317:bdd759456a8aadde, sg:318:d12551e640049a82, sg:320:c727c52f6dd3db20, sg:327:7e26102923a5fa2a, sg:335:262ff98740f3cdc3, sg:341:3f75441deb6aa518, sg:342:e2d4439eae2b1f10), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 34 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:152:f5dd0f16ab185e0b, sg:160:8732eae8813b1682, sg:167:af6bb479c89079c9, sg:173:6ce0b01108cbc4b8, sg:181:1d0e1089dc62847e, sg:188:95a9e64d9906694a, sg:194:38e25eb804466a9c, sg:202:e4c30c95efb6cf33, sg:208:0bfb428b6e0f581c, sg:209:971e683e2e94b943, sg:215:4ecc0ca415f27b19, sg:223:503487865ccbe701, sg:229:ffe959c28f930b9c, sg:230:8e3a080457b52971, sg:231:df82a72a916e2e39, sg:237:c0df5a88e98942f9, sg:245:88c5e56e84954b83, sg:251:a7661561df8dc40a, sg:252:b528a312a5f21438, sg:253:0cb356e7b6fa507b, sg:259:881f49b604e9cbd3, sg:267:92b6a086249dffe3, sg:273:868256386c8ff208, sg:274:6a558da4464d9df1, sg:275:5299338ac0a9a43c, sg:281:52e551b5fc9278ad, sg:289:30f1e565fa854137, sg:295:8e33873d245ad0bf, sg:296:aedd16d7928438c8, sg:302:56b983a216b4cd18, sg:310:451b8c6abb6d6996, sg:316:f060754097c8b8c2, sg:317:bdd759456a8aadde, sg:318:d12551e640049a82), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 39 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:152:f5dd0f16ab185e0b, sg:160:8732eae8813b1682, sg:167:af6bb479c89079c9, sg:173:6ce0b01108cbc4b8, sg:181:1d0e1089dc62847e, sg:188:95a9e64d9906694a, sg:194:38e25eb804466a9c, sg:202:e4c30c95efb6cf33, sg:208:0bfb428b6e0f581c, sg:209:971e683e2e94b943, sg:215:4ecc0ca415f27b19, sg:223:503487865ccbe701, sg:229:ffe959c28f930b9c, sg:230:8e3a080457b52971, sg:231:df82a72a916e2e39, sg:237:c0df5a88e98942f9, sg:245:88c5e56e84954b83, sg:251:a7661561df8dc40a, sg:252:b528a312a5f21438, sg:253:0cb356e7b6fa507b, sg:259:881f49b604e9cbd3, sg:267:92b6a086249dffe3, sg:273:868256386c8ff208, sg:274:6a558da4464d9df1, sg:275:5299338ac0a9a43c, sg:281:52e551b5fc9278ad, sg:289:30f1e565fa854137, sg:295:8e33873d245ad0bf, sg:296:aedd16d7928438c8, sg:302:56b983a216b4cd18, sg:310:451b8c6abb6d6996, sg:316:f060754097c8b8c2, sg:317:bdd759456a8aadde, sg:318:d12551e640049a82, sg:320:c727c52f6dd3db20, sg:327:7e26102923a5fa2a, sg:335:262ff98740f3cdc3, sg:341:3f75441deb6aa518, sg:342:e2d4439eae2b1f10), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F4" s="18" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
-          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 18 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:163:4522da66473b0891, sg:184:c86849434d37f2ca, sg:204:9ea6d3672f1cbb6c, sg:205:3e8f79273c4d99e8, sg:225:80c4d796e03c26e4, sg:226:6a59e2af4b4ca71b, sg:240:a5d2cdeff651719f, sg:247:701124238565aea3, sg:248:8387bb110d3df1b5, sg:262:3469a49c5dfe33df, sg:269:1b515696ec660f7e, sg:270:bed799f2391778f8, sg:284:f0cc0e2554ff036e, sg:291:65036624ecd070da, sg:292:db118c5c341e9374, sg:305:13464f3fece64c57, sg:312:719cda02320ce051, sg:313:2c32160817ca4657), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 21 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:163:4522da66473b0891, sg:184:c86849434d37f2ca, sg:204:9ea6d3672f1cbb6c, sg:205:3e8f79273c4d99e8, sg:225:80c4d796e03c26e4, sg:226:6a59e2af4b4ca71b, sg:240:a5d2cdeff651719f, sg:247:701124238565aea3, sg:248:8387bb110d3df1b5, sg:262:3469a49c5dfe33df, sg:269:1b515696ec660f7e, sg:270:bed799f2391778f8, sg:284:f0cc0e2554ff036e, sg:291:65036624ecd070da, sg:292:db118c5c341e9374, sg:305:13464f3fece64c57, sg:312:719cda02320ce051, sg:313:2c32160817ca4657, sg:330:9885585e2ce75432, sg:337:caa73d022439fdbd, sg:338:a3d61192cd7bd32f), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F44" s="18" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 18 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:163:4522da66473b0891, sg:184:c86849434d37f2ca, sg:204:9ea6d3672f1cbb6c, sg:205:3e8f79273c4d99e8, sg:225:80c4d796e03c26e4, sg:226:6a59e2af4b4ca71b, sg:240:a5d2cdeff651719f, sg:247:701124238565aea3, sg:248:8387bb110d3df1b5, sg:262:3469a49c5dfe33df, sg:269:1b515696ec660f7e, sg:270:bed799f2391778f8, sg:284:f0cc0e2554ff036e, sg:291:65036624ecd070da, sg:292:db118c5c341e9374, sg:305:13464f3fece64c57, sg:312:719cda02320ce051, sg:313:2c32160817ca4657), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 21 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:163:4522da66473b0891, sg:184:c86849434d37f2ca, sg:204:9ea6d3672f1cbb6c, sg:205:3e8f79273c4d99e8, sg:225:80c4d796e03c26e4, sg:226:6a59e2af4b4ca71b, sg:240:a5d2cdeff651719f, sg:247:701124238565aea3, sg:248:8387bb110d3df1b5, sg:262:3469a49c5dfe33df, sg:269:1b515696ec660f7e, sg:270:bed799f2391778f8, sg:284:f0cc0e2554ff036e, sg:291:65036624ecd070da, sg:292:db118c5c341e9374, sg:305:13464f3fece64c57, sg:312:719cda02320ce051, sg:313:2c32160817ca4657, sg:330:9885585e2ce75432, sg:337:caa73d022439fdbd, sg:338:a3d61192cd7bd32f), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 16 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:147:9bebca7095710e7b, sg:164:0a17213da88916a0, sg:168:673efa781a5886af, sg:185:722aa012e9e81176, sg:189:6da7e8855e27abf3, sg:206:e376384aa84cb442, sg:210:b32620de15f05a8a, sg:227:395621be5822edd0, sg:232:51c5900fb397b7a9, sg:249:3593fb118d2fca63, sg:254:0db7ce23ccc53be3, sg:271:d364696547ebe95c, sg:276:4bbae7bcafd12d98, sg:293:f73310695b98f452, sg:297:7e43ee8cd5f34c63, sg:314:c5482c11a08df3ec), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 17 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:147:9bebca7095710e7b, sg:164:0a17213da88916a0, sg:168:673efa781a5886af, sg:185:722aa012e9e81176, sg:189:6da7e8855e27abf3, sg:206:e376384aa84cb442, sg:210:b32620de15f05a8a, sg:227:395621be5822edd0, sg:232:51c5900fb397b7a9, sg:249:3593fb118d2fca63, sg:254:0db7ce23ccc53be3, sg:271:d364696547ebe95c, sg:276:4bbae7bcafd12d98, sg:293:f73310695b98f452, sg:297:7e43ee8cd5f34c63, sg:314:c5482c11a08df3ec, sg:322:a4cb203e20d3eb1f), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F112" s="18" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 16 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:147:9bebca7095710e7b, sg:164:0a17213da88916a0, sg:168:673efa781a5886af, sg:185:722aa012e9e81176, sg:189:6da7e8855e27abf3, sg:206:e376384aa84cb442, sg:210:b32620de15f05a8a, sg:227:395621be5822edd0, sg:232:51c5900fb397b7a9, sg:249:3593fb118d2fca63, sg:254:0db7ce23ccc53be3, sg:271:d364696547ebe95c, sg:276:4bbae7bcafd12d98, sg:293:f73310695b98f452, sg:297:7e43ee8cd5f34c63, sg:314:c5482c11a08df3ec), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 17 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:147:9bebca7095710e7b, sg:164:0a17213da88916a0, sg:168:673efa781a5886af, sg:185:722aa012e9e81176, sg:189:6da7e8855e27abf3, sg:206:e376384aa84cb442, sg:210:b32620de15f05a8a, sg:227:395621be5822edd0, sg:232:51c5900fb397b7a9, sg:249:3593fb118d2fca63, sg:254:0db7ce23ccc53be3, sg:271:d364696547ebe95c, sg:276:4bbae7bcafd12d98, sg:293:f73310695b98f452, sg:297:7e43ee8cd5f34c63, sg:314:c5482c11a08df3ec, sg:322:a4cb203e20d3eb1f), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F113" s="14" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="E130" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 52 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:147:9bebca7095710e7b, sg:153:917bc028692cdd65, sg:154:2aafc34476d15d60, sg:161:031e2e8d26da6042, sg:167:af6bb479c89079c9, sg:168:673efa781a5886af, sg:174:13f58e0526f7181d, sg:175:ae266bdaf3bcce83, sg:182:316038988f1c15b5, sg:188:95a9e64d9906694a, sg:189:6da7e8855e27abf3, sg:195:7e21be5aabc730de, sg:196:658be324c2a38ac1, sg:203:35588c7155777fa3, sg:209:971e683e2e94b943, sg:210:b32620de15f05a8a, sg:216:41e4f43c86d8a50c, sg:217:3d31aa054b4df3be, sg:224:261113f46c0a132c, sg:230:8e3a080457b52971, sg:231:df82a72a916e2e39, sg:232:51c5900fb397b7a9, sg:238:79b0a819923d99e7, sg:239:480f556da4997f37, sg:240:a5d2cdeff651719f, sg:241:6ac43f1af968ab3b, sg:246:2f33e49e67f6479d, sg:252:b528a312a5f21438, sg:253:0cb356e7b6fa507b, sg:254:0db7ce23ccc53be3, sg:260:400efe2f44aa8a1d, sg:261:365b5881e76193a9, sg:262:3469a49c5dfe33df, sg:263:28fb5e8aa73620af, sg:268:2bee81eec3bf6fb7, sg:274:6a558da4464d9df1, sg:275:5299338ac0a9a43c, sg:276:4bbae7bcafd12d98, sg:282:cdc77fb63822474d, sg:283:896c397b8d94a589, sg:284:f0cc0e2554ff036e, sg:285:6ddb23f185aaff4f, sg:290:705836796517f406, sg:296:aedd16d7928438c8, sg:297:7e43ee8cd5f34c63, sg:303:e87c265eb14beb6d, sg:304:3ec3de027f118201, sg:305:13464f3fece64c57, sg:306:99555fd6fcbe2e30, sg:311:95ec1f7a98fc8040, sg:317:bdd759456a8aadde, sg:318:d12551e640049a82), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 60 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:147:9bebca7095710e7b, sg:153:917bc028692cdd65, sg:154:2aafc34476d15d60, sg:161:031e2e8d26da6042, sg:167:af6bb479c89079c9, sg:168:673efa781a5886af, sg:174:13f58e0526f7181d, sg:175:ae266bdaf3bcce83, sg:182:316038988f1c15b5, sg:188:95a9e64d9906694a, sg:189:6da7e8855e27abf3, sg:195:7e21be5aabc730de, sg:196:658be324c2a38ac1, sg:203:35588c7155777fa3, sg:209:971e683e2e94b943, sg:210:b32620de15f05a8a, sg:216:41e4f43c86d8a50c, sg:217:3d31aa054b4df3be, sg:224:261113f46c0a132c, sg:230:8e3a080457b52971, sg:231:df82a72a916e2e39, sg:232:51c5900fb397b7a9, sg:238:79b0a819923d99e7, sg:239:480f556da4997f37, sg:240:a5d2cdeff651719f, sg:241:6ac43f1af968ab3b, sg:246:2f33e49e67f6479d, sg:252:b528a312a5f21438, sg:253:0cb356e7b6fa507b, sg:254:0db7ce23ccc53be3, sg:260:400efe2f44aa8a1d, sg:261:365b5881e76193a9, sg:262:3469a49c5dfe33df, sg:263:28fb5e8aa73620af, sg:268:2bee81eec3bf6fb7, sg:274:6a558da4464d9df1, sg:275:5299338ac0a9a43c, sg:276:4bbae7bcafd12d98, sg:282:cdc77fb63822474d, sg:283:896c397b8d94a589, sg:284:f0cc0e2554ff036e, sg:285:6ddb23f185aaff4f, sg:290:705836796517f406, sg:296:aedd16d7928438c8, sg:297:7e43ee8cd5f34c63, sg:303:e87c265eb14beb6d, sg:304:3ec3de027f118201, sg:305:13464f3fece64c57, sg:306:99555fd6fcbe2e30, sg:311:95ec1f7a98fc8040, sg:317:bdd759456a8aadde, sg:318:d12551e640049a82, sg:320:c727c52f6dd3db20, sg:322:a4cb203e20d3eb1f, sg:328:742d8f3afc43b5fe, sg:329:76ba8e01f6a34dac, sg:330:9885585e2ce75432, sg:331:a5424bddd236dd80, sg:336:3b27b22bf6fb39ae, sg:342:e2d4439eae2b1f10), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F130" s="18" t="inlineStr">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 33 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:148:bf16ebd320021812, sg:151:09827d850c759c55, sg:152:f5dd0f16ab185e0b, sg:159:d2f56027459525a6, sg:169:48b4d0685cddb97c, sg:172:5926dd73b82f20ac, sg:173:6ce0b01108cbc4b8, sg:180:7bd687cabc9b8fae, sg:190:2c686e6a0a4325ea, sg:193:6533b7a7ff0dc797, sg:194:38e25eb804466a9c, sg:201:42177fa99ba5562a, sg:211:b0c734a6d6203dd9, sg:214:b56d0a70c597d937, sg:215:4ecc0ca415f27b19, sg:222:2c44c57502077f4b, sg:233:1efbe62fc88b526e, sg:236:7f50e965f9dc790f, sg:237:c0df5a88e98942f9, sg:244:8826477dd70d712c, sg:255:39ea635315afb679, sg:258:b0024a88e878db5d, sg:259:881f49b604e9cbd3, sg:266:92bc3e0f05ebea4e, sg:277:fd3a8aa73909435b, sg:280:dd326b8bbbd4e63c, sg:281:52e551b5fc9278ad, sg:288:96af66ac3d62eb4b, sg:298:01ad0ac7f4518cb0, sg:301:6859f91aa9ed302a, sg:302:56b983a216b4cd18, sg:309:98823423f402cc78, sg:319:6573641a8a90838a), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 37 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:148:bf16ebd320021812, sg:151:09827d850c759c55, sg:152:f5dd0f16ab185e0b, sg:159:d2f56027459525a6, sg:169:48b4d0685cddb97c, sg:172:5926dd73b82f20ac, sg:173:6ce0b01108cbc4b8, sg:180:7bd687cabc9b8fae, sg:190:2c686e6a0a4325ea, sg:193:6533b7a7ff0dc797, sg:194:38e25eb804466a9c, sg:201:42177fa99ba5562a, sg:211:b0c734a6d6203dd9, sg:214:b56d0a70c597d937, sg:215:4ecc0ca415f27b19, sg:222:2c44c57502077f4b, sg:233:1efbe62fc88b526e, sg:236:7f50e965f9dc790f, sg:237:c0df5a88e98942f9, sg:244:8826477dd70d712c, sg:255:39ea635315afb679, sg:258:b0024a88e878db5d, sg:259:881f49b604e9cbd3, sg:266:92bc3e0f05ebea4e, sg:277:fd3a8aa73909435b, sg:280:dd326b8bbbd4e63c, sg:281:52e551b5fc9278ad, sg:288:96af66ac3d62eb4b, sg:298:01ad0ac7f4518cb0, sg:301:6859f91aa9ed302a, sg:302:56b983a216b4cd18, sg:309:98823423f402cc78, sg:319:6573641a8a90838a, sg:323:98bec67565602291, sg:326:bbe8ec2e854fb444, sg:327:7e26102923a5fa2a, sg:334:d81ba83ba10a49f5), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F219" s="14" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="E220" s="18" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 33 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:148:bf16ebd320021812, sg:151:09827d850c759c55, sg:152:f5dd0f16ab185e0b, sg:159:d2f56027459525a6, sg:169:48b4d0685cddb97c, sg:172:5926dd73b82f20ac, sg:173:6ce0b01108cbc4b8, sg:180:7bd687cabc9b8fae, sg:190:2c686e6a0a4325ea, sg:193:6533b7a7ff0dc797, sg:194:38e25eb804466a9c, sg:201:42177fa99ba5562a, sg:211:b0c734a6d6203dd9, sg:214:b56d0a70c597d937, sg:215:4ecc0ca415f27b19, sg:222:2c44c57502077f4b, sg:233:1efbe62fc88b526e, sg:236:7f50e965f9dc790f, sg:237:c0df5a88e98942f9, sg:244:8826477dd70d712c, sg:255:39ea635315afb679, sg:258:b0024a88e878db5d, sg:259:881f49b604e9cbd3, sg:266:92bc3e0f05ebea4e, sg:277:fd3a8aa73909435b, sg:280:dd326b8bbbd4e63c, sg:281:52e551b5fc9278ad, sg:288:96af66ac3d62eb4b, sg:298:01ad0ac7f4518cb0, sg:301:6859f91aa9ed302a, sg:302:56b983a216b4cd18, sg:309:98823423f402cc78, sg:319:6573641a8a90838a), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 37 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:148:bf16ebd320021812, sg:151:09827d850c759c55, sg:152:f5dd0f16ab185e0b, sg:159:d2f56027459525a6, sg:169:48b4d0685cddb97c, sg:172:5926dd73b82f20ac, sg:173:6ce0b01108cbc4b8, sg:180:7bd687cabc9b8fae, sg:190:2c686e6a0a4325ea, sg:193:6533b7a7ff0dc797, sg:194:38e25eb804466a9c, sg:201:42177fa99ba5562a, sg:211:b0c734a6d6203dd9, sg:214:b56d0a70c597d937, sg:215:4ecc0ca415f27b19, sg:222:2c44c57502077f4b, sg:233:1efbe62fc88b526e, sg:236:7f50e965f9dc790f, sg:237:c0df5a88e98942f9, sg:244:8826477dd70d712c, sg:255:39ea635315afb679, sg:258:b0024a88e878db5d, sg:259:881f49b604e9cbd3, sg:266:92bc3e0f05ebea4e, sg:277:fd3a8aa73909435b, sg:280:dd326b8bbbd4e63c, sg:281:52e551b5fc9278ad, sg:288:96af66ac3d62eb4b, sg:298:01ad0ac7f4518cb0, sg:301:6859f91aa9ed302a, sg:302:56b983a216b4cd18, sg:309:98823423f402cc78, sg:319:6573641a8a90838a, sg:323:98bec67565602291, sg:326:bbe8ec2e854fb444, sg:327:7e26102923a5fa2a, sg:334:d81ba83ba10a49f5), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F220" s="18" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="E229" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; The recorder is not reachable by the agent it records: PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 49 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:148:bf16ebd320021812, sg:149:3a457b22d02d5d00, sg:150:c7d8c1f4e3ba922f, sg:158:990028f1af93efe0, sg:161:031e2e8d26da6042, sg:165:16a2dc1cdba5042c, sg:169:48b4d0685cddb97c, sg:170:0cac8deabbdeb2be, sg:171:668aeb3d76ddd965, sg:179:633e78abdb22cde9, sg:182:316038988f1c15b5, sg:186:c824e180049dd2b9, sg:190:2c686e6a0a4325ea, sg:191:1d4bb4d51ca47470, sg:192:d59dee5e3cfdf13f, sg:200:5b4e409881f95024, sg:203:35588c7155777fa3, sg:207:6c0a670149e7e8b4, sg:211:b0c734a6d6203dd9, sg:212:8d2949464058f0d6, sg:213:9702a206fa3a6787, sg:221:c0f53e4491dfaf77, sg:224:261113f46c0a132c, sg:228:81382ed63fbaed5e, sg:233:1efbe62fc88b526e, sg:234:97e84699bae989a7, sg:235:f85e4d3d4524f521, sg:243:afd6d8a495c70f64, sg:246:2f33e49e67f6479d, sg:250:53492bd4e3472c80, sg:255:39ea635315afb679, sg:256:8548adf23e7b24c7, sg:257:a9a52f5a89458875, sg:265:99c5554aae1129ba, sg:268:2bee81eec3bf6fb7, sg:272:1b9b7f40f252c52a, sg:277:fd3a8aa73909435b, sg:278:c4bf3eedc0efbd9d, sg:279:7142c6b87fd79ff2, sg:287:6ae0009f5fb3c8c9, sg:290:705836796517f406, sg:294:ff5c7e6fb37d81ef, sg:298:01ad0ac7f4518cb0, sg:299:aac6ce5f2fda13ce, sg:300:1b44cef550a2dd88, sg:308:ec5f2f5862aa4937, sg:311:95ec1f7a98fc8040, sg:315:2bc1dca6b1bab0e5, sg:319:6573641a8a90838a), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; The recorder is not reachable by the agent it records: PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 48 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:148:bf16ebd320021812, sg:149:3a457b22d02d5d00, sg:150:c7d8c1f4e3ba922f, sg:161:031e2e8d26da6042, sg:165:16a2dc1cdba5042c, sg:169:48b4d0685cddb97c, sg:170:0cac8deabbdeb2be, sg:171:668aeb3d76ddd965, sg:182:316038988f1c15b5, sg:186:c824e180049dd2b9, sg:190:2c686e6a0a4325ea, sg:191:1d4bb4d51ca47470, sg:192:d59dee5e3cfdf13f, sg:203:35588c7155777fa3, sg:207:6c0a670149e7e8b4, sg:211:b0c734a6d6203dd9, sg:212:8d2949464058f0d6, sg:213:9702a206fa3a6787, sg:224:261113f46c0a132c, sg:228:81382ed63fbaed5e, sg:233:1efbe62fc88b526e, sg:234:97e84699bae989a7, sg:235:f85e4d3d4524f521, sg:246:2f33e49e67f6479d, sg:250:53492bd4e3472c80, sg:255:39ea635315afb679, sg:256:8548adf23e7b24c7, sg:257:a9a52f5a89458875, sg:268:2bee81eec3bf6fb7, sg:272:1b9b7f40f252c52a, sg:277:fd3a8aa73909435b, sg:278:c4bf3eedc0efbd9d, sg:279:7142c6b87fd79ff2, sg:290:705836796517f406, sg:294:ff5c7e6fb37d81ef, sg:298:01ad0ac7f4518cb0, sg:299:aac6ce5f2fda13ce, sg:300:1b44cef550a2dd88, sg:311:95ec1f7a98fc8040, sg:315:2bc1dca6b1bab0e5, sg:319:6573641a8a90838a, sg:321:1bbead68531e5626, sg:323:98bec67565602291, sg:324:7488d2d0ae03eb49, sg:325:3b1d2672c8cb0051, sg:333:4c89c214286ce7ef, sg:336:3b27b22bf6fb39ae, sg:340:e730e19687343741), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F229" s="14" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="E255" s="14" t="inlineStr">
         <is>
-          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:241:6ac43f1af968ab3b, sg:263:28fb5e8aa73620af, sg:285:6ddb23f185aaff4f, sg:306:99555fd6fcbe2e30), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 5 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:241:6ac43f1af968ab3b, sg:263:28fb5e8aa73620af, sg:285:6ddb23f185aaff4f, sg:306:99555fd6fcbe2e30, sg:331:a5424bddd236dd80), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F255" s="14" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="E256" s="18" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 8 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:159:d2f56027459525a6, sg:180:7bd687cabc9b8fae, sg:201:42177fa99ba5562a, sg:222:2c44c57502077f4b, sg:244:8826477dd70d712c, sg:266:92bc3e0f05ebea4e, sg:288:96af66ac3d62eb4b, sg:309:98823423f402cc78), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 9 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:159:d2f56027459525a6, sg:180:7bd687cabc9b8fae, sg:201:42177fa99ba5562a, sg:222:2c44c57502077f4b, sg:244:8826477dd70d712c, sg:266:92bc3e0f05ebea4e, sg:288:96af66ac3d62eb4b, sg:309:98823423f402cc78, sg:334:d81ba83ba10a49f5), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F256" s="18" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="E257" s="14" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 8 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:159:d2f56027459525a6, sg:180:7bd687cabc9b8fae, sg:201:42177fa99ba5562a, sg:222:2c44c57502077f4b, sg:244:8826477dd70d712c, sg:266:92bc3e0f05ebea4e, sg:288:96af66ac3d62eb4b, sg:309:98823423f402cc78), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 9 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:159:d2f56027459525a6, sg:180:7bd687cabc9b8fae, sg:201:42177fa99ba5562a, sg:222:2c44c57502077f4b, sg:244:8826477dd70d712c, sg:266:92bc3e0f05ebea4e, sg:288:96af66ac3d62eb4b, sg:309:98823423f402cc78, sg:334:d81ba83ba10a49f5), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F257" s="14" t="inlineStr">

--- a/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
+++ b/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="Introduction" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="AI-CAIQv1.1.0" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="LLM Taxonomy" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Change Log" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Introduction" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI-CAIQv1.1.0" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM Taxonomy" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -335,6 +335,181 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1352550" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="0" name="image1.png"/>
+        <cNvPicPr preferRelativeResize="0"/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData fLocksWithSheet="0"/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1352550" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="0" name="image1.png"/>
+        <cNvPicPr preferRelativeResize="0"/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData fLocksWithSheet="0"/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1352550" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="0" name="image1.png"/>
+        <cNvPicPr preferRelativeResize="0"/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData fLocksWithSheet="0"/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1352550" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="0" name="image1.png"/>
+        <cNvPicPr preferRelativeResize="0"/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData fLocksWithSheet="0"/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1352550" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="0" name="image1.png"/>
+        <cNvPicPr preferRelativeResize="0"/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData fLocksWithSheet="0"/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1964,6 +2139,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2081,11 +2257,7 @@
           <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 39 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:152:f5dd0f16ab185e0b, sg:160:8732eae8813b1682, sg:167:af6bb479c89079c9, sg:173:6ce0b01108cbc4b8, sg:181:1d0e1089dc62847e, sg:188:95a9e64d9906694a, sg:194:38e25eb804466a9c, sg:202:e4c30c95efb6cf33, sg:208:0bfb428b6e0f581c, sg:209:971e683e2e94b943, sg:215:4ecc0ca415f27b19, sg:223:503487865ccbe701, sg:229:ffe959c28f930b9c, sg:230:8e3a080457b52971, sg:231:df82a72a916e2e39, sg:237:c0df5a88e98942f9, sg:245:88c5e56e84954b83, sg:251:a7661561df8dc40a, sg:252:b528a312a5f21438, sg:253:0cb356e7b6fa507b, sg:259:881f49b604e9cbd3, sg:267:92b6a086249dffe3, sg:273:868256386c8ff208, sg:274:6a558da4464d9df1, sg:275:5299338ac0a9a43c, sg:281:52e551b5fc9278ad, sg:289:30f1e565fa854137, sg:295:8e33873d245ad0bf, sg:296:aedd16d7928438c8, sg:302:56b983a216b4cd18, sg:310:451b8c6abb6d6996, sg:316:f060754097c8b8c2, sg:317:bdd759456a8aadde, sg:318:d12551e640049a82, sg:320:c727c52f6dd3db20, sg:327:7e26102923a5fa2a, sg:335:262ff98740f3cdc3, sg:341:3f75441deb6aa518, sg:342:e2d4439eae2b1f10), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F3" s="14" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F3" s="14" t="n"/>
       <c r="I3" s="21" t="inlineStr">
         <is>
           <t>A&amp;A-01</t>
@@ -2134,11 +2306,7 @@
           <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 39 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:152:f5dd0f16ab185e0b, sg:160:8732eae8813b1682, sg:167:af6bb479c89079c9, sg:173:6ce0b01108cbc4b8, sg:181:1d0e1089dc62847e, sg:188:95a9e64d9906694a, sg:194:38e25eb804466a9c, sg:202:e4c30c95efb6cf33, sg:208:0bfb428b6e0f581c, sg:209:971e683e2e94b943, sg:215:4ecc0ca415f27b19, sg:223:503487865ccbe701, sg:229:ffe959c28f930b9c, sg:230:8e3a080457b52971, sg:231:df82a72a916e2e39, sg:237:c0df5a88e98942f9, sg:245:88c5e56e84954b83, sg:251:a7661561df8dc40a, sg:252:b528a312a5f21438, sg:253:0cb356e7b6fa507b, sg:259:881f49b604e9cbd3, sg:267:92b6a086249dffe3, sg:273:868256386c8ff208, sg:274:6a558da4464d9df1, sg:275:5299338ac0a9a43c, sg:281:52e551b5fc9278ad, sg:289:30f1e565fa854137, sg:295:8e33873d245ad0bf, sg:296:aedd16d7928438c8, sg:302:56b983a216b4cd18, sg:310:451b8c6abb6d6996, sg:316:f060754097c8b8c2, sg:317:bdd759456a8aadde, sg:318:d12551e640049a82, sg:320:c727c52f6dd3db20, sg:327:7e26102923a5fa2a, sg:335:262ff98740f3cdc3, sg:341:3f75441deb6aa518, sg:342:e2d4439eae2b1f10), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F4" s="18" t="n"/>
       <c r="I4" s="27" t="n"/>
       <c r="J4" s="27" t="n"/>
       <c r="K4" s="27" t="n"/>
@@ -3342,11 +3510,7 @@
           <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 21 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:163:4522da66473b0891, sg:184:c86849434d37f2ca, sg:204:9ea6d3672f1cbb6c, sg:205:3e8f79273c4d99e8, sg:225:80c4d796e03c26e4, sg:226:6a59e2af4b4ca71b, sg:240:a5d2cdeff651719f, sg:247:701124238565aea3, sg:248:8387bb110d3df1b5, sg:262:3469a49c5dfe33df, sg:269:1b515696ec660f7e, sg:270:bed799f2391778f8, sg:284:f0cc0e2554ff036e, sg:291:65036624ecd070da, sg:292:db118c5c341e9374, sg:305:13464f3fece64c57, sg:312:719cda02320ce051, sg:313:2c32160817ca4657, sg:330:9885585e2ce75432, sg:337:caa73d022439fdbd, sg:338:a3d61192cd7bd32f), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F44" s="18" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F44" s="18" t="n"/>
       <c r="I44" s="21" t="inlineStr">
         <is>
           <t>CCC-01</t>
@@ -3394,11 +3558,7 @@
           <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 21 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:163:4522da66473b0891, sg:184:c86849434d37f2ca, sg:204:9ea6d3672f1cbb6c, sg:205:3e8f79273c4d99e8, sg:225:80c4d796e03c26e4, sg:226:6a59e2af4b4ca71b, sg:240:a5d2cdeff651719f, sg:247:701124238565aea3, sg:248:8387bb110d3df1b5, sg:262:3469a49c5dfe33df, sg:269:1b515696ec660f7e, sg:270:bed799f2391778f8, sg:284:f0cc0e2554ff036e, sg:291:65036624ecd070da, sg:292:db118c5c341e9374, sg:305:13464f3fece64c57, sg:312:719cda02320ce051, sg:313:2c32160817ca4657, sg:330:9885585e2ce75432, sg:337:caa73d022439fdbd, sg:338:a3d61192cd7bd32f), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F45" s="14" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F45" s="14" t="n"/>
       <c r="I45" s="27" t="n"/>
       <c r="J45" s="27" t="n"/>
       <c r="K45" s="27" t="n"/>
@@ -5384,11 +5544,7 @@
           <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 17 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:147:9bebca7095710e7b, sg:164:0a17213da88916a0, sg:168:673efa781a5886af, sg:185:722aa012e9e81176, sg:189:6da7e8855e27abf3, sg:206:e376384aa84cb442, sg:210:b32620de15f05a8a, sg:227:395621be5822edd0, sg:232:51c5900fb397b7a9, sg:249:3593fb118d2fca63, sg:254:0db7ce23ccc53be3, sg:271:d364696547ebe95c, sg:276:4bbae7bcafd12d98, sg:293:f73310695b98f452, sg:297:7e43ee8cd5f34c63, sg:314:c5482c11a08df3ec, sg:322:a4cb203e20d3eb1f), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F112" s="18" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F112" s="18" t="n"/>
       <c r="I112" s="21" t="inlineStr">
         <is>
           <t>DSP-05</t>
@@ -5432,11 +5588,7 @@
           <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 17 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:147:9bebca7095710e7b, sg:164:0a17213da88916a0, sg:168:673efa781a5886af, sg:185:722aa012e9e81176, sg:189:6da7e8855e27abf3, sg:206:e376384aa84cb442, sg:210:b32620de15f05a8a, sg:227:395621be5822edd0, sg:232:51c5900fb397b7a9, sg:249:3593fb118d2fca63, sg:254:0db7ce23ccc53be3, sg:271:d364696547ebe95c, sg:276:4bbae7bcafd12d98, sg:293:f73310695b98f452, sg:297:7e43ee8cd5f34c63, sg:314:c5482c11a08df3ec, sg:322:a4cb203e20d3eb1f), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F113" s="14" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F113" s="14" t="n"/>
       <c r="I113" s="27" t="n"/>
       <c r="J113" s="27" t="n"/>
       <c r="K113" s="27" t="n"/>
@@ -5957,11 +6109,7 @@
           <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 60 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:147:9bebca7095710e7b, sg:153:917bc028692cdd65, sg:154:2aafc34476d15d60, sg:161:031e2e8d26da6042, sg:167:af6bb479c89079c9, sg:168:673efa781a5886af, sg:174:13f58e0526f7181d, sg:175:ae266bdaf3bcce83, sg:182:316038988f1c15b5, sg:188:95a9e64d9906694a, sg:189:6da7e8855e27abf3, sg:195:7e21be5aabc730de, sg:196:658be324c2a38ac1, sg:203:35588c7155777fa3, sg:209:971e683e2e94b943, sg:210:b32620de15f05a8a, sg:216:41e4f43c86d8a50c, sg:217:3d31aa054b4df3be, sg:224:261113f46c0a132c, sg:230:8e3a080457b52971, sg:231:df82a72a916e2e39, sg:232:51c5900fb397b7a9, sg:238:79b0a819923d99e7, sg:239:480f556da4997f37, sg:240:a5d2cdeff651719f, sg:241:6ac43f1af968ab3b, sg:246:2f33e49e67f6479d, sg:252:b528a312a5f21438, sg:253:0cb356e7b6fa507b, sg:254:0db7ce23ccc53be3, sg:260:400efe2f44aa8a1d, sg:261:365b5881e76193a9, sg:262:3469a49c5dfe33df, sg:263:28fb5e8aa73620af, sg:268:2bee81eec3bf6fb7, sg:274:6a558da4464d9df1, sg:275:5299338ac0a9a43c, sg:276:4bbae7bcafd12d98, sg:282:cdc77fb63822474d, sg:283:896c397b8d94a589, sg:284:f0cc0e2554ff036e, sg:285:6ddb23f185aaff4f, sg:290:705836796517f406, sg:296:aedd16d7928438c8, sg:297:7e43ee8cd5f34c63, sg:303:e87c265eb14beb6d, sg:304:3ec3de027f118201, sg:305:13464f3fece64c57, sg:306:99555fd6fcbe2e30, sg:311:95ec1f7a98fc8040, sg:317:bdd759456a8aadde, sg:318:d12551e640049a82, sg:320:c727c52f6dd3db20, sg:322:a4cb203e20d3eb1f, sg:328:742d8f3afc43b5fe, sg:329:76ba8e01f6a34dac, sg:330:9885585e2ce75432, sg:331:a5424bddd236dd80, sg:336:3b27b22bf6fb39ae, sg:342:e2d4439eae2b1f10), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F130" s="18" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F130" s="18" t="n"/>
       <c r="I130" s="21" t="inlineStr">
         <is>
           <t>DSP-20</t>
@@ -8206,11 +8354,7 @@
           <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 8 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:164:0a17213da88916a0, sg:185:722aa012e9e81176, sg:206:e376384aa84cb442, sg:227:395621be5822edd0, sg:249:3593fb118d2fca63, sg:271:d364696547ebe95c, sg:293:f73310695b98f452, sg:314:c5482c11a08df3ec), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F203" s="14" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F203" s="14" t="n"/>
       <c r="I203" s="21" t="inlineStr">
         <is>
           <t>I&amp;S-01</t>
@@ -8258,11 +8402,7 @@
           <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 8 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:164:0a17213da88916a0, sg:185:722aa012e9e81176, sg:206:e376384aa84cb442, sg:227:395621be5822edd0, sg:249:3593fb118d2fca63, sg:271:d364696547ebe95c, sg:293:f73310695b98f452, sg:314:c5482c11a08df3ec), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F204" s="18" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F204" s="18" t="n"/>
       <c r="I204" s="27" t="n"/>
       <c r="J204" s="27" t="n"/>
       <c r="K204" s="27" t="n"/>
@@ -8708,11 +8848,7 @@
           <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 37 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:148:bf16ebd320021812, sg:151:09827d850c759c55, sg:152:f5dd0f16ab185e0b, sg:159:d2f56027459525a6, sg:169:48b4d0685cddb97c, sg:172:5926dd73b82f20ac, sg:173:6ce0b01108cbc4b8, sg:180:7bd687cabc9b8fae, sg:190:2c686e6a0a4325ea, sg:193:6533b7a7ff0dc797, sg:194:38e25eb804466a9c, sg:201:42177fa99ba5562a, sg:211:b0c734a6d6203dd9, sg:214:b56d0a70c597d937, sg:215:4ecc0ca415f27b19, sg:222:2c44c57502077f4b, sg:233:1efbe62fc88b526e, sg:236:7f50e965f9dc790f, sg:237:c0df5a88e98942f9, sg:244:8826477dd70d712c, sg:255:39ea635315afb679, sg:258:b0024a88e878db5d, sg:259:881f49b604e9cbd3, sg:266:92bc3e0f05ebea4e, sg:277:fd3a8aa73909435b, sg:280:dd326b8bbbd4e63c, sg:281:52e551b5fc9278ad, sg:288:96af66ac3d62eb4b, sg:298:01ad0ac7f4518cb0, sg:301:6859f91aa9ed302a, sg:302:56b983a216b4cd18, sg:309:98823423f402cc78, sg:319:6573641a8a90838a, sg:323:98bec67565602291, sg:326:bbe8ec2e854fb444, sg:327:7e26102923a5fa2a, sg:334:d81ba83ba10a49f5), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F219" s="14" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F219" s="14" t="n"/>
       <c r="I219" s="21" t="inlineStr">
         <is>
           <t>LOG-03</t>
@@ -8760,11 +8896,7 @@
           <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 37 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:148:bf16ebd320021812, sg:151:09827d850c759c55, sg:152:f5dd0f16ab185e0b, sg:159:d2f56027459525a6, sg:169:48b4d0685cddb97c, sg:172:5926dd73b82f20ac, sg:173:6ce0b01108cbc4b8, sg:180:7bd687cabc9b8fae, sg:190:2c686e6a0a4325ea, sg:193:6533b7a7ff0dc797, sg:194:38e25eb804466a9c, sg:201:42177fa99ba5562a, sg:211:b0c734a6d6203dd9, sg:214:b56d0a70c597d937, sg:215:4ecc0ca415f27b19, sg:222:2c44c57502077f4b, sg:233:1efbe62fc88b526e, sg:236:7f50e965f9dc790f, sg:237:c0df5a88e98942f9, sg:244:8826477dd70d712c, sg:255:39ea635315afb679, sg:258:b0024a88e878db5d, sg:259:881f49b604e9cbd3, sg:266:92bc3e0f05ebea4e, sg:277:fd3a8aa73909435b, sg:280:dd326b8bbbd4e63c, sg:281:52e551b5fc9278ad, sg:288:96af66ac3d62eb4b, sg:298:01ad0ac7f4518cb0, sg:301:6859f91aa9ed302a, sg:302:56b983a216b4cd18, sg:309:98823423f402cc78, sg:319:6573641a8a90838a, sg:323:98bec67565602291, sg:326:bbe8ec2e854fb444, sg:327:7e26102923a5fa2a, sg:334:d81ba83ba10a49f5), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F220" s="18" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F220" s="18" t="n"/>
       <c r="I220" s="27" t="n"/>
       <c r="J220" s="27" t="n"/>
       <c r="K220" s="27" t="n"/>
@@ -9037,11 +9169,7 @@
           <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; The recorder is not reachable by the agent it records: PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 48 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:148:bf16ebd320021812, sg:149:3a457b22d02d5d00, sg:150:c7d8c1f4e3ba922f, sg:161:031e2e8d26da6042, sg:165:16a2dc1cdba5042c, sg:169:48b4d0685cddb97c, sg:170:0cac8deabbdeb2be, sg:171:668aeb3d76ddd965, sg:182:316038988f1c15b5, sg:186:c824e180049dd2b9, sg:190:2c686e6a0a4325ea, sg:191:1d4bb4d51ca47470, sg:192:d59dee5e3cfdf13f, sg:203:35588c7155777fa3, sg:207:6c0a670149e7e8b4, sg:211:b0c734a6d6203dd9, sg:212:8d2949464058f0d6, sg:213:9702a206fa3a6787, sg:224:261113f46c0a132c, sg:228:81382ed63fbaed5e, sg:233:1efbe62fc88b526e, sg:234:97e84699bae989a7, sg:235:f85e4d3d4524f521, sg:246:2f33e49e67f6479d, sg:250:53492bd4e3472c80, sg:255:39ea635315afb679, sg:256:8548adf23e7b24c7, sg:257:a9a52f5a89458875, sg:268:2bee81eec3bf6fb7, sg:272:1b9b7f40f252c52a, sg:277:fd3a8aa73909435b, sg:278:c4bf3eedc0efbd9d, sg:279:7142c6b87fd79ff2, sg:290:705836796517f406, sg:294:ff5c7e6fb37d81ef, sg:298:01ad0ac7f4518cb0, sg:299:aac6ce5f2fda13ce, sg:300:1b44cef550a2dd88, sg:311:95ec1f7a98fc8040, sg:315:2bc1dca6b1bab0e5, sg:319:6573641a8a90838a, sg:321:1bbead68531e5626, sg:323:98bec67565602291, sg:324:7488d2d0ae03eb49, sg:325:3b1d2672c8cb0051, sg:333:4c89c214286ce7ef, sg:336:3b27b22bf6fb39ae, sg:340:e730e19687343741), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F229" s="14" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F229" s="14" t="n"/>
       <c r="I229" s="21" t="inlineStr">
         <is>
           <t>LOG-10</t>
@@ -9117,11 +9245,7 @@
           <t>No. There is artifact-level and decision-level provenance, but no continuous activity log for cryptographic key lifecycle events specifically. Evidence searched: stop_guessing/attest/keys.py, stop_guessing/ledger/, rules/, policy/coc.policy.d/.</t>
         </is>
       </c>
-      <c r="F231" s="14" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F231" s="14" t="n"/>
       <c r="I231" s="21" t="inlineStr">
         <is>
           <t>LOG-12</t>
@@ -9821,11 +9945,7 @@
           <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 5 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:241:6ac43f1af968ab3b, sg:263:28fb5e8aa73620af, sg:285:6ddb23f185aaff4f, sg:306:99555fd6fcbe2e30, sg:331:a5424bddd236dd80), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F255" s="14" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F255" s="14" t="n"/>
       <c r="I255" s="21" t="inlineStr">
         <is>
           <t>MDS-13</t>
@@ -9869,11 +9989,7 @@
           <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 9 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:159:d2f56027459525a6, sg:180:7bd687cabc9b8fae, sg:201:42177fa99ba5562a, sg:222:2c44c57502077f4b, sg:244:8826477dd70d712c, sg:266:92bc3e0f05ebea4e, sg:288:96af66ac3d62eb4b, sg:309:98823423f402cc78, sg:334:d81ba83ba10a49f5), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F256" s="18" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F256" s="18" t="n"/>
       <c r="I256" s="21" t="inlineStr">
         <is>
           <t>SEF-01</t>
@@ -9921,11 +10037,7 @@
           <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 9 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:159:d2f56027459525a6, sg:180:7bd687cabc9b8fae, sg:201:42177fa99ba5562a, sg:222:2c44c57502077f4b, sg:244:8826477dd70d712c, sg:266:92bc3e0f05ebea4e, sg:288:96af66ac3d62eb4b, sg:309:98823423f402cc78, sg:334:d81ba83ba10a49f5), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F257" s="14" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F257" s="14" t="n"/>
       <c r="I257" s="27" t="n"/>
       <c r="J257" s="27" t="n"/>
       <c r="K257" s="27" t="n"/>
@@ -10665,11 +10777,7 @@
           <t>No. A service Bill of Materials is not emitted. The in-toto Statement envelope and the pinned MANIFEST.sha256 over the vendored tree are adjacent but are not an SBOM. Evidence searched: stop_guessing/attest/, stop_guessing/compat/, .github/workflows/.</t>
         </is>
       </c>
-      <c r="F282" s="18" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F282" s="18" t="n"/>
       <c r="I282" s="21" t="inlineStr">
         <is>
           <t>STA-09</t>
@@ -10713,11 +10821,7 @@
           <t>No. A service Bill of Materials is not emitted. The in-toto Statement envelope and the pinned MANIFEST.sha256 over the vendored tree are adjacent but are not an SBOM. Evidence searched: stop_guessing/attest/, stop_guessing/compat/, .github/workflows/.</t>
         </is>
       </c>
-      <c r="F283" s="14" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F283" s="14" t="n"/>
       <c r="I283" s="27" t="n"/>
       <c r="J283" s="27" t="n"/>
       <c r="K283" s="27" t="n"/>
@@ -12891,6 +12995,7 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -15178,6 +15283,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -16325,5 +16431,6 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
+++ b/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Introduction" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI-CAIQv1.1.0" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM Taxonomy" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Introduction" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="AI-CAIQv1.1.0" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="LLM Taxonomy" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Change Log" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -335,181 +335,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1352550" cy="476250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="0" name="image1.png"/>
-        <cNvPicPr preferRelativeResize="0"/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData fLocksWithSheet="0"/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1352550" cy="476250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="0" name="image1.png"/>
-        <cNvPicPr preferRelativeResize="0"/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData fLocksWithSheet="0"/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1352550" cy="476250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="0" name="image1.png"/>
-        <cNvPicPr preferRelativeResize="0"/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData fLocksWithSheet="0"/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1352550" cy="476250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="0" name="image1.png"/>
-        <cNvPicPr preferRelativeResize="0"/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData fLocksWithSheet="0"/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1352550" cy="476250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="0" name="image1.png"/>
-        <cNvPicPr preferRelativeResize="0"/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData fLocksWithSheet="0"/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2139,7 +1964,6 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2254,10 +2078,14 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 39 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:152:f5dd0f16ab185e0b, sg:160:8732eae8813b1682, sg:167:af6bb479c89079c9, sg:173:6ce0b01108cbc4b8, sg:181:1d0e1089dc62847e, sg:188:95a9e64d9906694a, sg:194:38e25eb804466a9c, sg:202:e4c30c95efb6cf33, sg:208:0bfb428b6e0f581c, sg:209:971e683e2e94b943, sg:215:4ecc0ca415f27b19, sg:223:503487865ccbe701, sg:229:ffe959c28f930b9c, sg:230:8e3a080457b52971, sg:231:df82a72a916e2e39, sg:237:c0df5a88e98942f9, sg:245:88c5e56e84954b83, sg:251:a7661561df8dc40a, sg:252:b528a312a5f21438, sg:253:0cb356e7b6fa507b, sg:259:881f49b604e9cbd3, sg:267:92b6a086249dffe3, sg:273:868256386c8ff208, sg:274:6a558da4464d9df1, sg:275:5299338ac0a9a43c, sg:281:52e551b5fc9278ad, sg:289:30f1e565fa854137, sg:295:8e33873d245ad0bf, sg:296:aedd16d7928438c8, sg:302:56b983a216b4cd18, sg:310:451b8c6abb6d6996, sg:316:f060754097c8b8c2, sg:317:bdd759456a8aadde, sg:318:d12551e640049a82, sg:320:c727c52f6dd3db20, sg:327:7e26102923a5fa2a, sg:335:262ff98740f3cdc3, sg:341:3f75441deb6aa518, sg:342:e2d4439eae2b1f10), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F3" s="14" t="n"/>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:341:3f75441deb6aa518, sg:350:c3c3d55022e0fce4, sg:360:d2992df5128d3665), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I3" s="21" t="inlineStr">
         <is>
           <t>A&amp;A-01</t>
@@ -2303,10 +2131,14 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 39 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:152:f5dd0f16ab185e0b, sg:160:8732eae8813b1682, sg:167:af6bb479c89079c9, sg:173:6ce0b01108cbc4b8, sg:181:1d0e1089dc62847e, sg:188:95a9e64d9906694a, sg:194:38e25eb804466a9c, sg:202:e4c30c95efb6cf33, sg:208:0bfb428b6e0f581c, sg:209:971e683e2e94b943, sg:215:4ecc0ca415f27b19, sg:223:503487865ccbe701, sg:229:ffe959c28f930b9c, sg:230:8e3a080457b52971, sg:231:df82a72a916e2e39, sg:237:c0df5a88e98942f9, sg:245:88c5e56e84954b83, sg:251:a7661561df8dc40a, sg:252:b528a312a5f21438, sg:253:0cb356e7b6fa507b, sg:259:881f49b604e9cbd3, sg:267:92b6a086249dffe3, sg:273:868256386c8ff208, sg:274:6a558da4464d9df1, sg:275:5299338ac0a9a43c, sg:281:52e551b5fc9278ad, sg:289:30f1e565fa854137, sg:295:8e33873d245ad0bf, sg:296:aedd16d7928438c8, sg:302:56b983a216b4cd18, sg:310:451b8c6abb6d6996, sg:316:f060754097c8b8c2, sg:317:bdd759456a8aadde, sg:318:d12551e640049a82, sg:320:c727c52f6dd3db20, sg:327:7e26102923a5fa2a, sg:335:262ff98740f3cdc3, sg:341:3f75441deb6aa518, sg:342:e2d4439eae2b1f10), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F4" s="18" t="n"/>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:341:3f75441deb6aa518, sg:350:c3c3d55022e0fce4, sg:360:d2992df5128d3665), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I4" s="27" t="n"/>
       <c r="J4" s="27" t="n"/>
       <c r="K4" s="27" t="n"/>
@@ -3507,10 +3339,14 @@
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
-          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 21 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:163:4522da66473b0891, sg:184:c86849434d37f2ca, sg:204:9ea6d3672f1cbb6c, sg:205:3e8f79273c4d99e8, sg:225:80c4d796e03c26e4, sg:226:6a59e2af4b4ca71b, sg:240:a5d2cdeff651719f, sg:247:701124238565aea3, sg:248:8387bb110d3df1b5, sg:262:3469a49c5dfe33df, sg:269:1b515696ec660f7e, sg:270:bed799f2391778f8, sg:284:f0cc0e2554ff036e, sg:291:65036624ecd070da, sg:292:db118c5c341e9374, sg:305:13464f3fece64c57, sg:312:719cda02320ce051, sg:313:2c32160817ca4657, sg:330:9885585e2ce75432, sg:337:caa73d022439fdbd, sg:338:a3d61192cd7bd32f), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F44" s="18" t="n"/>
+          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:337:caa73d022439fdbd, sg:338:a3d61192cd7bd32f, sg:353:d46b783a7f07f51c), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F44" s="18" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I44" s="21" t="inlineStr">
         <is>
           <t>CCC-01</t>
@@ -3555,10 +3391,14 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 21 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:163:4522da66473b0891, sg:184:c86849434d37f2ca, sg:204:9ea6d3672f1cbb6c, sg:205:3e8f79273c4d99e8, sg:225:80c4d796e03c26e4, sg:226:6a59e2af4b4ca71b, sg:240:a5d2cdeff651719f, sg:247:701124238565aea3, sg:248:8387bb110d3df1b5, sg:262:3469a49c5dfe33df, sg:269:1b515696ec660f7e, sg:270:bed799f2391778f8, sg:284:f0cc0e2554ff036e, sg:291:65036624ecd070da, sg:292:db118c5c341e9374, sg:305:13464f3fece64c57, sg:312:719cda02320ce051, sg:313:2c32160817ca4657, sg:330:9885585e2ce75432, sg:337:caa73d022439fdbd, sg:338:a3d61192cd7bd32f), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F45" s="14" t="n"/>
+          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:337:caa73d022439fdbd, sg:338:a3d61192cd7bd32f, sg:353:d46b783a7f07f51c), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I45" s="27" t="n"/>
       <c r="J45" s="27" t="n"/>
       <c r="K45" s="27" t="n"/>
@@ -5541,10 +5381,14 @@
       </c>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 17 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:147:9bebca7095710e7b, sg:164:0a17213da88916a0, sg:168:673efa781a5886af, sg:185:722aa012e9e81176, sg:189:6da7e8855e27abf3, sg:206:e376384aa84cb442, sg:210:b32620de15f05a8a, sg:227:395621be5822edd0, sg:232:51c5900fb397b7a9, sg:249:3593fb118d2fca63, sg:254:0db7ce23ccc53be3, sg:271:d364696547ebe95c, sg:276:4bbae7bcafd12d98, sg:293:f73310695b98f452, sg:297:7e43ee8cd5f34c63, sg:314:c5482c11a08df3ec, sg:322:a4cb203e20d3eb1f), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F112" s="18" t="n"/>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:314:c5482c11a08df3ec, sg:345:2dcfc0fc6daab8ac), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F112" s="18" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I112" s="21" t="inlineStr">
         <is>
           <t>DSP-05</t>
@@ -5585,10 +5429,14 @@
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 17 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:147:9bebca7095710e7b, sg:164:0a17213da88916a0, sg:168:673efa781a5886af, sg:185:722aa012e9e81176, sg:189:6da7e8855e27abf3, sg:206:e376384aa84cb442, sg:210:b32620de15f05a8a, sg:227:395621be5822edd0, sg:232:51c5900fb397b7a9, sg:249:3593fb118d2fca63, sg:254:0db7ce23ccc53be3, sg:271:d364696547ebe95c, sg:276:4bbae7bcafd12d98, sg:293:f73310695b98f452, sg:297:7e43ee8cd5f34c63, sg:314:c5482c11a08df3ec, sg:322:a4cb203e20d3eb1f), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F113" s="14" t="n"/>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:314:c5482c11a08df3ec, sg:345:2dcfc0fc6daab8ac), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F113" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I113" s="27" t="n"/>
       <c r="J113" s="27" t="n"/>
       <c r="K113" s="27" t="n"/>
@@ -6106,10 +5954,14 @@
       </c>
       <c r="E130" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; This toolchain's own AI-CAIQ was filled from proofs produced by this toolchain, as the last step, and every answer's evidence resolves to a verified ledger record. Proven by 60 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:147:9bebca7095710e7b, sg:153:917bc028692cdd65, sg:154:2aafc34476d15d60, sg:161:031e2e8d26da6042, sg:167:af6bb479c89079c9, sg:168:673efa781a5886af, sg:174:13f58e0526f7181d, sg:175:ae266bdaf3bcce83, sg:182:316038988f1c15b5, sg:188:95a9e64d9906694a, sg:189:6da7e8855e27abf3, sg:195:7e21be5aabc730de, sg:196:658be324c2a38ac1, sg:203:35588c7155777fa3, sg:209:971e683e2e94b943, sg:210:b32620de15f05a8a, sg:216:41e4f43c86d8a50c, sg:217:3d31aa054b4df3be, sg:224:261113f46c0a132c, sg:230:8e3a080457b52971, sg:231:df82a72a916e2e39, sg:232:51c5900fb397b7a9, sg:238:79b0a819923d99e7, sg:239:480f556da4997f37, sg:240:a5d2cdeff651719f, sg:241:6ac43f1af968ab3b, sg:246:2f33e49e67f6479d, sg:252:b528a312a5f21438, sg:253:0cb356e7b6fa507b, sg:254:0db7ce23ccc53be3, sg:260:400efe2f44aa8a1d, sg:261:365b5881e76193a9, sg:262:3469a49c5dfe33df, sg:263:28fb5e8aa73620af, sg:268:2bee81eec3bf6fb7, sg:274:6a558da4464d9df1, sg:275:5299338ac0a9a43c, sg:276:4bbae7bcafd12d98, sg:282:cdc77fb63822474d, sg:283:896c397b8d94a589, sg:284:f0cc0e2554ff036e, sg:285:6ddb23f185aaff4f, sg:290:705836796517f406, sg:296:aedd16d7928438c8, sg:297:7e43ee8cd5f34c63, sg:303:e87c265eb14beb6d, sg:304:3ec3de027f118201, sg:305:13464f3fece64c57, sg:306:99555fd6fcbe2e30, sg:311:95ec1f7a98fc8040, sg:317:bdd759456a8aadde, sg:318:d12551e640049a82, sg:320:c727c52f6dd3db20, sg:322:a4cb203e20d3eb1f, sg:328:742d8f3afc43b5fe, sg:329:76ba8e01f6a34dac, sg:330:9885585e2ce75432, sg:331:a5424bddd236dd80, sg:336:3b27b22bf6fb39ae, sg:342:e2d4439eae2b1f10), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F130" s="18" t="n"/>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:328:742d8f3afc43b5fe, sg:329:76ba8e01f6a34dac, sg:345:2dcfc0fc6daab8ac, sg:353:d46b783a7f07f51c, sg:354:218870a4d725b4d6, sg:361:5c26c533f82a73ca), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F130" s="18" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I130" s="21" t="inlineStr">
         <is>
           <t>DSP-20</t>
@@ -8351,10 +8203,14 @@
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 8 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:164:0a17213da88916a0, sg:185:722aa012e9e81176, sg:206:e376384aa84cb442, sg:227:395621be5822edd0, sg:249:3593fb118d2fca63, sg:271:d364696547ebe95c, sg:293:f73310695b98f452, sg:314:c5482c11a08df3ec), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F203" s="14" t="n"/>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:314:c5482c11a08df3ec), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F203" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I203" s="21" t="inlineStr">
         <is>
           <t>I&amp;S-01</t>
@@ -8399,10 +8255,14 @@
       </c>
       <c r="E204" s="18" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 8 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:164:0a17213da88916a0, sg:185:722aa012e9e81176, sg:206:e376384aa84cb442, sg:227:395621be5822edd0, sg:249:3593fb118d2fca63, sg:271:d364696547ebe95c, sg:293:f73310695b98f452, sg:314:c5482c11a08df3ec), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F204" s="18" t="n"/>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:314:c5482c11a08df3ec), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F204" s="18" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I204" s="27" t="n"/>
       <c r="J204" s="27" t="n"/>
       <c r="K204" s="27" t="n"/>
@@ -8845,10 +8705,14 @@
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 37 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:148:bf16ebd320021812, sg:151:09827d850c759c55, sg:152:f5dd0f16ab185e0b, sg:159:d2f56027459525a6, sg:169:48b4d0685cddb97c, sg:172:5926dd73b82f20ac, sg:173:6ce0b01108cbc4b8, sg:180:7bd687cabc9b8fae, sg:190:2c686e6a0a4325ea, sg:193:6533b7a7ff0dc797, sg:194:38e25eb804466a9c, sg:201:42177fa99ba5562a, sg:211:b0c734a6d6203dd9, sg:214:b56d0a70c597d937, sg:215:4ecc0ca415f27b19, sg:222:2c44c57502077f4b, sg:233:1efbe62fc88b526e, sg:236:7f50e965f9dc790f, sg:237:c0df5a88e98942f9, sg:244:8826477dd70d712c, sg:255:39ea635315afb679, sg:258:b0024a88e878db5d, sg:259:881f49b604e9cbd3, sg:266:92bc3e0f05ebea4e, sg:277:fd3a8aa73909435b, sg:280:dd326b8bbbd4e63c, sg:281:52e551b5fc9278ad, sg:288:96af66ac3d62eb4b, sg:298:01ad0ac7f4518cb0, sg:301:6859f91aa9ed302a, sg:302:56b983a216b4cd18, sg:309:98823423f402cc78, sg:319:6573641a8a90838a, sg:323:98bec67565602291, sg:326:bbe8ec2e854fb444, sg:327:7e26102923a5fa2a, sg:334:d81ba83ba10a49f5), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F219" s="14" t="n"/>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:346:235607a86a8e1be2, sg:349:1d19a578934b6ed3, sg:350:c3c3d55022e0fce4, sg:357:4d19d87c964f6ddd), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F219" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I219" s="21" t="inlineStr">
         <is>
           <t>LOG-03</t>
@@ -8893,10 +8757,14 @@
       </c>
       <c r="E220" s="18" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 37 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:148:bf16ebd320021812, sg:151:09827d850c759c55, sg:152:f5dd0f16ab185e0b, sg:159:d2f56027459525a6, sg:169:48b4d0685cddb97c, sg:172:5926dd73b82f20ac, sg:173:6ce0b01108cbc4b8, sg:180:7bd687cabc9b8fae, sg:190:2c686e6a0a4325ea, sg:193:6533b7a7ff0dc797, sg:194:38e25eb804466a9c, sg:201:42177fa99ba5562a, sg:211:b0c734a6d6203dd9, sg:214:b56d0a70c597d937, sg:215:4ecc0ca415f27b19, sg:222:2c44c57502077f4b, sg:233:1efbe62fc88b526e, sg:236:7f50e965f9dc790f, sg:237:c0df5a88e98942f9, sg:244:8826477dd70d712c, sg:255:39ea635315afb679, sg:258:b0024a88e878db5d, sg:259:881f49b604e9cbd3, sg:266:92bc3e0f05ebea4e, sg:277:fd3a8aa73909435b, sg:280:dd326b8bbbd4e63c, sg:281:52e551b5fc9278ad, sg:288:96af66ac3d62eb4b, sg:298:01ad0ac7f4518cb0, sg:301:6859f91aa9ed302a, sg:302:56b983a216b4cd18, sg:309:98823423f402cc78, sg:319:6573641a8a90838a, sg:323:98bec67565602291, sg:326:bbe8ec2e854fb444, sg:327:7e26102923a5fa2a, sg:334:d81ba83ba10a49f5), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F220" s="18" t="n"/>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:346:235607a86a8e1be2, sg:349:1d19a578934b6ed3, sg:350:c3c3d55022e0fce4, sg:357:4d19d87c964f6ddd), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F220" s="18" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I220" s="27" t="n"/>
       <c r="J220" s="27" t="n"/>
       <c r="K220" s="27" t="n"/>
@@ -9166,10 +9034,14 @@
       </c>
       <c r="E229" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; The recorder is not reachable by the agent it records: PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 48 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:148:bf16ebd320021812, sg:149:3a457b22d02d5d00, sg:150:c7d8c1f4e3ba922f, sg:161:031e2e8d26da6042, sg:165:16a2dc1cdba5042c, sg:169:48b4d0685cddb97c, sg:170:0cac8deabbdeb2be, sg:171:668aeb3d76ddd965, sg:182:316038988f1c15b5, sg:186:c824e180049dd2b9, sg:190:2c686e6a0a4325ea, sg:191:1d4bb4d51ca47470, sg:192:d59dee5e3cfdf13f, sg:203:35588c7155777fa3, sg:207:6c0a670149e7e8b4, sg:211:b0c734a6d6203dd9, sg:212:8d2949464058f0d6, sg:213:9702a206fa3a6787, sg:224:261113f46c0a132c, sg:228:81382ed63fbaed5e, sg:233:1efbe62fc88b526e, sg:234:97e84699bae989a7, sg:235:f85e4d3d4524f521, sg:246:2f33e49e67f6479d, sg:250:53492bd4e3472c80, sg:255:39ea635315afb679, sg:256:8548adf23e7b24c7, sg:257:a9a52f5a89458875, sg:268:2bee81eec3bf6fb7, sg:272:1b9b7f40f252c52a, sg:277:fd3a8aa73909435b, sg:278:c4bf3eedc0efbd9d, sg:279:7142c6b87fd79ff2, sg:290:705836796517f406, sg:294:ff5c7e6fb37d81ef, sg:298:01ad0ac7f4518cb0, sg:299:aac6ce5f2fda13ce, sg:300:1b44cef550a2dd88, sg:311:95ec1f7a98fc8040, sg:315:2bc1dca6b1bab0e5, sg:319:6573641a8a90838a, sg:321:1bbead68531e5626, sg:323:98bec67565602291, sg:324:7488d2d0ae03eb49, sg:325:3b1d2672c8cb0051, sg:333:4c89c214286ce7ef, sg:336:3b27b22bf6fb39ae, sg:340:e730e19687343741), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F229" s="14" t="n"/>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; The recorder is not reachable by the agent it records: PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:333:4c89c214286ce7ef, sg:340:e730e19687343741, sg:346:235607a86a8e1be2, sg:347:a08d64d5f7f01847, sg:348:0facb1ac78b92a7e, sg:361:5c26c533f82a73ca), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F229" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I229" s="21" t="inlineStr">
         <is>
           <t>LOG-10</t>
@@ -9245,7 +9117,11 @@
           <t>No. There is artifact-level and decision-level provenance, but no continuous activity log for cryptographic key lifecycle events specifically. Evidence searched: stop_guessing/attest/keys.py, stop_guessing/ledger/, rules/, policy/coc.policy.d/.</t>
         </is>
       </c>
-      <c r="F231" s="14" t="n"/>
+      <c r="F231" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I231" s="21" t="inlineStr">
         <is>
           <t>LOG-12</t>
@@ -9942,10 +9818,14 @@
       </c>
       <c r="E255" s="14" t="inlineStr">
         <is>
-          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 5 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:241:6ac43f1af968ab3b, sg:263:28fb5e8aa73620af, sg:285:6ddb23f185aaff4f, sg:306:99555fd6fcbe2e30, sg:331:a5424bddd236dd80), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F255" s="14" t="n"/>
+          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:354:218870a4d725b4d6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F255" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I255" s="21" t="inlineStr">
         <is>
           <t>MDS-13</t>
@@ -9986,10 +9866,14 @@
       </c>
       <c r="E256" s="18" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 9 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:159:d2f56027459525a6, sg:180:7bd687cabc9b8fae, sg:201:42177fa99ba5562a, sg:222:2c44c57502077f4b, sg:244:8826477dd70d712c, sg:266:92bc3e0f05ebea4e, sg:288:96af66ac3d62eb4b, sg:309:98823423f402cc78, sg:334:d81ba83ba10a49f5), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F256" s="18" t="n"/>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:357:4d19d87c964f6ddd), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F256" s="18" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I256" s="21" t="inlineStr">
         <is>
           <t>SEF-01</t>
@@ -10034,10 +9918,14 @@
       </c>
       <c r="E257" s="14" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 9 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:159:d2f56027459525a6, sg:180:7bd687cabc9b8fae, sg:201:42177fa99ba5562a, sg:222:2c44c57502077f4b, sg:244:8826477dd70d712c, sg:266:92bc3e0f05ebea4e, sg:288:96af66ac3d62eb4b, sg:309:98823423f402cc78, sg:334:d81ba83ba10a49f5), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F257" s="14" t="n"/>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:357:4d19d87c964f6ddd), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F257" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I257" s="27" t="n"/>
       <c r="J257" s="27" t="n"/>
       <c r="K257" s="27" t="n"/>
@@ -10777,7 +10665,11 @@
           <t>No. A service Bill of Materials is not emitted. The in-toto Statement envelope and the pinned MANIFEST.sha256 over the vendored tree are adjacent but are not an SBOM. Evidence searched: stop_guessing/attest/, stop_guessing/compat/, .github/workflows/.</t>
         </is>
       </c>
-      <c r="F282" s="18" t="n"/>
+      <c r="F282" s="18" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I282" s="21" t="inlineStr">
         <is>
           <t>STA-09</t>
@@ -10821,7 +10713,11 @@
           <t>No. A service Bill of Materials is not emitted. The in-toto Statement envelope and the pinned MANIFEST.sha256 over the vendored tree are adjacent but are not an SBOM. Evidence searched: stop_guessing/attest/, stop_guessing/compat/, .github/workflows/.</t>
         </is>
       </c>
-      <c r="F283" s="14" t="n"/>
+      <c r="F283" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I283" s="27" t="n"/>
       <c r="J283" s="27" t="n"/>
       <c r="K283" s="27" t="n"/>
@@ -12995,7 +12891,6 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -15283,7 +15178,6 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -16431,6 +16325,5 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
+++ b/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
@@ -2078,7 +2078,7 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:341:3f75441deb6aa518, sg:350:c3c3d55022e0fce4, sg:360:d2992df5128d3665), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:445:ef794a50bad7de42, sg:453:2c4e74bce1740263, sg:459:b1b09ab469c88359), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — has been exercised by at least one live-run proof recorded in this toolchain's own ledger. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:341:3f75441deb6aa518, sg:350:c3c3d55022e0fce4, sg:360:d2992df5128d3665), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:445:ef794a50bad7de42, sg:453:2c4e74bce1740263, sg:459:b1b09ab469c88359), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F4" s="18" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
-          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:337:caa73d022439fdbd, sg:338:a3d61192cd7bd32f, sg:353:d46b783a7f07f51c), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:448:38b3ae19527aee8e, sg:455:2dc6f3bf1f6f5111, sg:456:63c43f0460f03e9a), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F44" s="18" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:337:caa73d022439fdbd, sg:338:a3d61192cd7bd32f, sg:353:d46b783a7f07f51c), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:448:38b3ae19527aee8e, sg:455:2dc6f3bf1f6f5111, sg:456:63c43f0460f03e9a), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:314:c5482c11a08df3ec, sg:345:2dcfc0fc6daab8ac), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:440:d566bf994a240f57, sg:457:d23f9829cfaf7b52), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F112" s="18" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:314:c5482c11a08df3ec, sg:345:2dcfc0fc6daab8ac), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:440:d566bf994a240f57, sg:457:d23f9829cfaf7b52), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F113" s="14" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="E130" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; A delegated script cannot touch live data until its paired test has passed, and cannot run at all if its digest changed after the test passed; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:328:742d8f3afc43b5fe, sg:329:76ba8e01f6a34dac, sg:345:2dcfc0fc6daab8ac, sg:353:d46b783a7f07f51c, sg:354:218870a4d725b4d6, sg:361:5c26c533f82a73ca), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:440:d566bf994a240f57, sg:446:ab850312354b2807, sg:447:2d67d35939bc9546, sg:448:38b3ae19527aee8e, sg:449:6e7a2fb4a742f903, sg:454:c06f0641ecb8964f), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F130" s="18" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:314:c5482c11a08df3ec), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:457:d23f9829cfaf7b52), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F203" s="14" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="E204" s="18" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception, and CI performs no fetch. This is a source audit, not a proof of no network activity: it cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:314:c5482c11a08df3ec), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:457:d23f9829cfaf7b52), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F204" s="18" t="inlineStr">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:346:235607a86a8e1be2, sg:349:1d19a578934b6ed3, sg:350:c3c3d55022e0fce4, sg:357:4d19d87c964f6ddd), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:441:018f0180d7b74aa1, sg:444:09062a8c812b706b, sg:445:ef794a50bad7de42, sg:452:969ce06cd6dd9ccd), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F219" s="14" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="E220" s="18" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:346:235607a86a8e1be2, sg:349:1d19a578934b6ed3, sg:350:c3c3d55022e0fce4, sg:357:4d19d87c964f6ddd), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:441:018f0180d7b74aa1, sg:444:09062a8c812b706b, sg:445:ef794a50bad7de42, sg:452:969ce06cd6dd9ccd), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F220" s="18" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="E229" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; The recorder is not reachable by the agent it records: PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:333:4c89c214286ce7ef, sg:340:e730e19687343741, sg:346:235607a86a8e1be2, sg:347:a08d64d5f7f01847, sg:348:0facb1ac78b92a7e, sg:361:5c26c533f82a73ca), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected. NARROWED 2026-08-04 (SG-HARD-006/007/010). This is no longer the broader claim that the recorder is unreachable by the agent it records. At the tiers the installer can actually deliver (0 and 1) the recorder runs under the agent's own uid, the chain key is a mode-600 file that anything the agent runs can read, and the socket authenticates ordering rather than the caller. The four named attacks are refused or detected. An agent that simply reads the key is not among them; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:441:018f0180d7b74aa1, sg:442:df161837a1613632, sg:443:dc52c3f278e13441, sg:451:46de29d6551d509f, sg:454:c06f0641ecb8964f, sg:458:2597d2ed9e5fe617), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F229" s="14" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="E255" s="14" t="inlineStr">
         <is>
-          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:354:218870a4d725b4d6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:449:6e7a2fb4a742f903), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F255" s="14" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="E256" s="18" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:357:4d19d87c964f6ddd), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:452:969ce06cd6dd9ccd), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F256" s="18" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="E257" s="14" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:357:4d19d87c964f6ddd), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:452:969ce06cd6dd9ccd), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F257" s="14" t="inlineStr">

--- a/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
+++ b/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
@@ -2081,11 +2081,7 @@
           <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:445:ef794a50bad7de42, sg:453:2c4e74bce1740263, sg:459:b1b09ab469c88359), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F3" s="14" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F3" s="14" t="n"/>
       <c r="I3" s="21" t="inlineStr">
         <is>
           <t>A&amp;A-01</t>
@@ -2134,11 +2130,7 @@
           <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:445:ef794a50bad7de42, sg:453:2c4e74bce1740263, sg:459:b1b09ab469c88359), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F4" s="18" t="n"/>
       <c r="I4" s="27" t="n"/>
       <c r="J4" s="27" t="n"/>
       <c r="K4" s="27" t="n"/>
@@ -3342,11 +3334,7 @@
           <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:448:38b3ae19527aee8e, sg:455:2dc6f3bf1f6f5111, sg:456:63c43f0460f03e9a), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F44" s="18" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F44" s="18" t="n"/>
       <c r="I44" s="21" t="inlineStr">
         <is>
           <t>CCC-01</t>
@@ -3394,11 +3382,7 @@
           <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:448:38b3ae19527aee8e, sg:455:2dc6f3bf1f6f5111, sg:456:63c43f0460f03e9a), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F45" s="14" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F45" s="14" t="n"/>
       <c r="I45" s="27" t="n"/>
       <c r="J45" s="27" t="n"/>
       <c r="K45" s="27" t="n"/>
@@ -5384,11 +5368,7 @@
           <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:440:d566bf994a240f57, sg:457:d23f9829cfaf7b52), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F112" s="18" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F112" s="18" t="n"/>
       <c r="I112" s="21" t="inlineStr">
         <is>
           <t>DSP-05</t>
@@ -5432,11 +5412,7 @@
           <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:440:d566bf994a240f57, sg:457:d23f9829cfaf7b52), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F113" s="14" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F113" s="14" t="n"/>
       <c r="I113" s="27" t="n"/>
       <c r="J113" s="27" t="n"/>
       <c r="K113" s="27" t="n"/>
@@ -5957,11 +5933,7 @@
           <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:440:d566bf994a240f57, sg:446:ab850312354b2807, sg:447:2d67d35939bc9546, sg:448:38b3ae19527aee8e, sg:449:6e7a2fb4a742f903, sg:454:c06f0641ecb8964f), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F130" s="18" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F130" s="18" t="n"/>
       <c r="I130" s="21" t="inlineStr">
         <is>
           <t>DSP-20</t>
@@ -8206,11 +8178,7 @@
           <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:457:d23f9829cfaf7b52), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F203" s="14" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F203" s="14" t="n"/>
       <c r="I203" s="21" t="inlineStr">
         <is>
           <t>I&amp;S-01</t>
@@ -8258,11 +8226,7 @@
           <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:457:d23f9829cfaf7b52), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F204" s="18" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F204" s="18" t="n"/>
       <c r="I204" s="27" t="n"/>
       <c r="J204" s="27" t="n"/>
       <c r="K204" s="27" t="n"/>
@@ -8708,11 +8672,7 @@
           <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:441:018f0180d7b74aa1, sg:444:09062a8c812b706b, sg:445:ef794a50bad7de42, sg:452:969ce06cd6dd9ccd), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F219" s="14" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F219" s="14" t="n"/>
       <c r="I219" s="21" t="inlineStr">
         <is>
           <t>LOG-03</t>
@@ -8760,11 +8720,7 @@
           <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:441:018f0180d7b74aa1, sg:444:09062a8c812b706b, sg:445:ef794a50bad7de42, sg:452:969ce06cd6dd9ccd), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F220" s="18" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F220" s="18" t="n"/>
       <c r="I220" s="27" t="n"/>
       <c r="J220" s="27" t="n"/>
       <c r="K220" s="27" t="n"/>
@@ -9037,11 +8993,7 @@
           <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected. NARROWED 2026-08-04 (SG-HARD-006/007/010). This is no longer the broader claim that the recorder is unreachable by the agent it records. At the tiers the installer can actually deliver (0 and 1) the recorder runs under the agent's own uid, the chain key is a mode-600 file that anything the agent runs can read, and the socket authenticates ordering rather than the caller. The four named attacks are refused or detected. An agent that simply reads the key is not among them; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:441:018f0180d7b74aa1, sg:442:df161837a1613632, sg:443:dc52c3f278e13441, sg:451:46de29d6551d509f, sg:454:c06f0641ecb8964f, sg:458:2597d2ed9e5fe617), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F229" s="14" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F229" s="14" t="n"/>
       <c r="I229" s="21" t="inlineStr">
         <is>
           <t>LOG-10</t>
@@ -9117,11 +9069,7 @@
           <t>No. There is artifact-level and decision-level provenance, but no continuous activity log for cryptographic key lifecycle events specifically. Evidence searched: stop_guessing/attest/keys.py, stop_guessing/ledger/, rules/, policy/coc.policy.d/.</t>
         </is>
       </c>
-      <c r="F231" s="14" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F231" s="14" t="n"/>
       <c r="I231" s="21" t="inlineStr">
         <is>
           <t>LOG-12</t>
@@ -9821,11 +9769,7 @@
           <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:449:6e7a2fb4a742f903), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F255" s="14" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F255" s="14" t="n"/>
       <c r="I255" s="21" t="inlineStr">
         <is>
           <t>MDS-13</t>
@@ -9869,11 +9813,7 @@
           <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:452:969ce06cd6dd9ccd), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F256" s="18" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F256" s="18" t="n"/>
       <c r="I256" s="21" t="inlineStr">
         <is>
           <t>SEF-01</t>
@@ -9921,11 +9861,7 @@
           <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:452:969ce06cd6dd9ccd), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
-      <c r="F257" s="14" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F257" s="14" t="n"/>
       <c r="I257" s="27" t="n"/>
       <c r="J257" s="27" t="n"/>
       <c r="K257" s="27" t="n"/>
@@ -10665,11 +10601,7 @@
           <t>No. A service Bill of Materials is not emitted. The in-toto Statement envelope and the pinned MANIFEST.sha256 over the vendored tree are adjacent but are not an SBOM. Evidence searched: stop_guessing/attest/, stop_guessing/compat/, .github/workflows/.</t>
         </is>
       </c>
-      <c r="F282" s="18" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F282" s="18" t="n"/>
       <c r="I282" s="21" t="inlineStr">
         <is>
           <t>STA-09</t>
@@ -10713,11 +10645,7 @@
           <t>No. A service Bill of Materials is not emitted. The in-toto Statement envelope and the pinned MANIFEST.sha256 over the vendored tree are adjacent but are not an SBOM. Evidence searched: stop_guessing/attest/, stop_guessing/compat/, .github/workflows/.</t>
         </is>
       </c>
-      <c r="F283" s="14" t="inlineStr">
-        <is>
-          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
-        </is>
-      </c>
+      <c r="F283" s="14" t="n"/>
       <c r="I283" s="27" t="n"/>
       <c r="J283" s="27" t="n"/>
       <c r="K283" s="27" t="n"/>

--- a/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
+++ b/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
@@ -2078,10 +2078,14 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:445:ef794a50bad7de42, sg:453:2c4e74bce1740263, sg:459:b1b09ab469c88359), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F3" s="14" t="n"/>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:518:49c764aecaf36916, sg:526:0073429f71140623, sg:532:dfb4767ca222722b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I3" s="21" t="inlineStr">
         <is>
           <t>A&amp;A-01</t>
@@ -2127,10 +2131,14 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:445:ef794a50bad7de42, sg:453:2c4e74bce1740263, sg:459:b1b09ab469c88359), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F4" s="18" t="n"/>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:518:49c764aecaf36916, sg:526:0073429f71140623, sg:532:dfb4767ca222722b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I4" s="27" t="n"/>
       <c r="J4" s="27" t="n"/>
       <c r="K4" s="27" t="n"/>
@@ -3331,10 +3339,14 @@
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
-          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:448:38b3ae19527aee8e, sg:455:2dc6f3bf1f6f5111, sg:456:63c43f0460f03e9a), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F44" s="18" t="n"/>
+          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:521:19086a0e78b7df22, sg:528:dbcea33269b83b51, sg:529:07c2eeb96f1b5d52), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F44" s="18" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I44" s="21" t="inlineStr">
         <is>
           <t>CCC-01</t>
@@ -3379,10 +3391,14 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:448:38b3ae19527aee8e, sg:455:2dc6f3bf1f6f5111, sg:456:63c43f0460f03e9a), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F45" s="14" t="n"/>
+          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:521:19086a0e78b7df22, sg:528:dbcea33269b83b51, sg:529:07c2eeb96f1b5d52), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I45" s="27" t="n"/>
       <c r="J45" s="27" t="n"/>
       <c r="K45" s="27" t="n"/>
@@ -5365,10 +5381,14 @@
       </c>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:440:d566bf994a240f57, sg:457:d23f9829cfaf7b52), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F112" s="18" t="n"/>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:513:b51e5b180a2e7598, sg:530:4ab8d9232aee1269), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F112" s="18" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I112" s="21" t="inlineStr">
         <is>
           <t>DSP-05</t>
@@ -5409,10 +5429,14 @@
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:440:d566bf994a240f57, sg:457:d23f9829cfaf7b52), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F113" s="14" t="n"/>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:513:b51e5b180a2e7598, sg:530:4ab8d9232aee1269), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F113" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I113" s="27" t="n"/>
       <c r="J113" s="27" t="n"/>
       <c r="K113" s="27" t="n"/>
@@ -5930,10 +5954,14 @@
       </c>
       <c r="E130" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:440:d566bf994a240f57, sg:446:ab850312354b2807, sg:447:2d67d35939bc9546, sg:448:38b3ae19527aee8e, sg:449:6e7a2fb4a742f903, sg:454:c06f0641ecb8964f), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F130" s="18" t="n"/>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:513:b51e5b180a2e7598, sg:519:ce4bb0064c062681, sg:520:927096b97a9ff436, sg:521:19086a0e78b7df22, sg:522:78f45a6425fd06b5, sg:527:d51b0a90e8f59905), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F130" s="18" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I130" s="21" t="inlineStr">
         <is>
           <t>DSP-20</t>
@@ -8175,10 +8203,14 @@
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:457:d23f9829cfaf7b52), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F203" s="14" t="n"/>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:530:4ab8d9232aee1269), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F203" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I203" s="21" t="inlineStr">
         <is>
           <t>I&amp;S-01</t>
@@ -8223,10 +8255,14 @@
       </c>
       <c r="E204" s="18" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:457:d23f9829cfaf7b52), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F204" s="18" t="n"/>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:530:4ab8d9232aee1269), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F204" s="18" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I204" s="27" t="n"/>
       <c r="J204" s="27" t="n"/>
       <c r="K204" s="27" t="n"/>
@@ -8669,10 +8705,14 @@
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:441:018f0180d7b74aa1, sg:444:09062a8c812b706b, sg:445:ef794a50bad7de42, sg:452:969ce06cd6dd9ccd), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F219" s="14" t="n"/>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:514:38b7456d79bfb182, sg:517:eb69fe957360034a, sg:518:49c764aecaf36916, sg:525:ab91d3da9236dd8d), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F219" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I219" s="21" t="inlineStr">
         <is>
           <t>LOG-03</t>
@@ -8717,10 +8757,14 @@
       </c>
       <c r="E220" s="18" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:441:018f0180d7b74aa1, sg:444:09062a8c812b706b, sg:445:ef794a50bad7de42, sg:452:969ce06cd6dd9ccd), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F220" s="18" t="n"/>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:514:38b7456d79bfb182, sg:517:eb69fe957360034a, sg:518:49c764aecaf36916, sg:525:ab91d3da9236dd8d), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F220" s="18" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I220" s="27" t="n"/>
       <c r="J220" s="27" t="n"/>
       <c r="K220" s="27" t="n"/>
@@ -8990,10 +9034,14 @@
       </c>
       <c r="E229" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected. NARROWED 2026-08-04 (SG-HARD-006/007/010). This is no longer the broader claim that the recorder is unreachable by the agent it records. At the tiers the installer can actually deliver (0 and 1) the recorder runs under the agent's own uid, the chain key is a mode-600 file that anything the agent runs can read, and the socket authenticates ordering rather than the caller. The four named attacks are refused or detected. An agent that simply reads the key is not among them; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:441:018f0180d7b74aa1, sg:442:df161837a1613632, sg:443:dc52c3f278e13441, sg:451:46de29d6551d509f, sg:454:c06f0641ecb8964f, sg:458:2597d2ed9e5fe617), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F229" s="14" t="n"/>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected. NARROWED 2026-08-04 (SG-HARD-006/007/010). This is no longer the broader claim that the recorder is unreachable by the agent it records. At the tiers the installer can actually deliver (0 and 1) the recorder runs under the agent's own uid, the chain key is a mode-600 file that anything the agent runs can read, and the socket authenticates ordering rather than the caller. The four named attacks are refused or detected. An agent that simply reads the key is not among them; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:514:38b7456d79bfb182, sg:515:49bd386c23eca3ed, sg:516:246bc4c6e6c4ab41, sg:524:f5b11aa1b11f9bbe, sg:527:d51b0a90e8f59905, sg:531:20f4c11d9597425d), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F229" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I229" s="21" t="inlineStr">
         <is>
           <t>LOG-10</t>
@@ -9069,7 +9117,11 @@
           <t>No. There is artifact-level and decision-level provenance, but no continuous activity log for cryptographic key lifecycle events specifically. Evidence searched: stop_guessing/attest/keys.py, stop_guessing/ledger/, rules/, policy/coc.policy.d/.</t>
         </is>
       </c>
-      <c r="F231" s="14" t="n"/>
+      <c r="F231" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I231" s="21" t="inlineStr">
         <is>
           <t>LOG-12</t>
@@ -9766,10 +9818,14 @@
       </c>
       <c r="E255" s="14" t="inlineStr">
         <is>
-          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:449:6e7a2fb4a742f903), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F255" s="14" t="n"/>
+          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:522:78f45a6425fd06b5), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F255" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I255" s="21" t="inlineStr">
         <is>
           <t>MDS-13</t>
@@ -9810,10 +9866,14 @@
       </c>
       <c r="E256" s="18" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:452:969ce06cd6dd9ccd), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F256" s="18" t="n"/>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:525:ab91d3da9236dd8d), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F256" s="18" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I256" s="21" t="inlineStr">
         <is>
           <t>SEF-01</t>
@@ -9858,10 +9918,14 @@
       </c>
       <c r="E257" s="14" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:452:969ce06cd6dd9ccd), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
-        </is>
-      </c>
-      <c r="F257" s="14" t="n"/>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:525:ab91d3da9236dd8d), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+        </is>
+      </c>
+      <c r="F257" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I257" s="27" t="n"/>
       <c r="J257" s="27" t="n"/>
       <c r="K257" s="27" t="n"/>
@@ -10601,7 +10665,11 @@
           <t>No. A service Bill of Materials is not emitted. The in-toto Statement envelope and the pinned MANIFEST.sha256 over the vendored tree are adjacent but are not an SBOM. Evidence searched: stop_guessing/attest/, stop_guessing/compat/, .github/workflows/.</t>
         </is>
       </c>
-      <c r="F282" s="18" t="n"/>
+      <c r="F282" s="18" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I282" s="21" t="inlineStr">
         <is>
           <t>STA-09</t>
@@ -10645,7 +10713,11 @@
           <t>No. A service Bill of Materials is not emitted. The in-toto Statement envelope and the pinned MANIFEST.sha256 over the vendored tree are adjacent but are not an SBOM. Evidence searched: stop_guessing/attest/, stop_guessing/compat/, .github/workflows/.</t>
         </is>
       </c>
-      <c r="F283" s="14" t="n"/>
+      <c r="F283" s="14" t="inlineStr">
+        <is>
+          <t>Install with `install.sh --all-profiles`, keep the chain key in the OS keychain rather than the environment, and run `stop-guessing attest --self` before relying on any claim.</t>
+        </is>
+      </c>
       <c r="I283" s="27" t="n"/>
       <c r="J283" s="27" t="n"/>
       <c r="K283" s="27" t="n"/>

--- a/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
+++ b/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
@@ -2078,7 +2078,7 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:518:49c764aecaf36916, sg:526:0073429f71140623, sg:532:dfb4767ca222722b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:539:cbbeb79ed833d3b8, sg:547:f33d92d467239ee0, sg:553:6abfe8183a178376), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:518:49c764aecaf36916, sg:526:0073429f71140623, sg:532:dfb4767ca222722b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:539:cbbeb79ed833d3b8, sg:547:f33d92d467239ee0, sg:553:6abfe8183a178376), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F4" s="18" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
-          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:521:19086a0e78b7df22, sg:528:dbcea33269b83b51, sg:529:07c2eeb96f1b5d52), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:542:30280382d03df282, sg:549:e7caba8051f7831a, sg:550:388d34145b912de3), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F44" s="18" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:521:19086a0e78b7df22, sg:528:dbcea33269b83b51, sg:529:07c2eeb96f1b5d52), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:542:30280382d03df282, sg:549:e7caba8051f7831a, sg:550:388d34145b912de3), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:513:b51e5b180a2e7598, sg:530:4ab8d9232aee1269), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:534:964accc8ed7028f7, sg:551:3bc766e39a382363), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F112" s="18" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:513:b51e5b180a2e7598, sg:530:4ab8d9232aee1269), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:534:964accc8ed7028f7, sg:551:3bc766e39a382363), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F113" s="14" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="E130" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:513:b51e5b180a2e7598, sg:519:ce4bb0064c062681, sg:520:927096b97a9ff436, sg:521:19086a0e78b7df22, sg:522:78f45a6425fd06b5, sg:527:d51b0a90e8f59905), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:534:964accc8ed7028f7, sg:540:e91c86aeac162a3e, sg:541:9a1f5bf48331cd25, sg:542:30280382d03df282, sg:543:687bded188010ece, sg:548:712f84e32e8626f7), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F130" s="18" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:530:4ab8d9232aee1269), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:551:3bc766e39a382363), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F203" s="14" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="E204" s="18" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:530:4ab8d9232aee1269), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:551:3bc766e39a382363), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F204" s="18" t="inlineStr">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:514:38b7456d79bfb182, sg:517:eb69fe957360034a, sg:518:49c764aecaf36916, sg:525:ab91d3da9236dd8d), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:535:4de191336cbedfc8, sg:538:824e5be61afc0314, sg:539:cbbeb79ed833d3b8, sg:546:d7cd108bd6a7ac51), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F219" s="14" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="E220" s="18" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:514:38b7456d79bfb182, sg:517:eb69fe957360034a, sg:518:49c764aecaf36916, sg:525:ab91d3da9236dd8d), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:535:4de191336cbedfc8, sg:538:824e5be61afc0314, sg:539:cbbeb79ed833d3b8, sg:546:d7cd108bd6a7ac51), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F220" s="18" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="E229" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected. NARROWED 2026-08-04 (SG-HARD-006/007/010). This is no longer the broader claim that the recorder is unreachable by the agent it records. At the tiers the installer can actually deliver (0 and 1) the recorder runs under the agent's own uid, the chain key is a mode-600 file that anything the agent runs can read, and the socket authenticates ordering rather than the caller. The four named attacks are refused or detected. An agent that simply reads the key is not among them; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:514:38b7456d79bfb182, sg:515:49bd386c23eca3ed, sg:516:246bc4c6e6c4ab41, sg:524:f5b11aa1b11f9bbe, sg:527:d51b0a90e8f59905, sg:531:20f4c11d9597425d), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected. NARROWED 2026-08-04 (SG-HARD-006/007/010). This is no longer the broader claim that the recorder is unreachable by the agent it records. At the tiers the installer can actually deliver (0 and 1) the recorder runs under the agent's own uid, the chain key is a mode-600 file that anything the agent runs can read, and the socket authenticates ordering rather than the caller. The four named attacks are refused or detected. An agent that simply reads the key is not among them; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:535:4de191336cbedfc8, sg:536:3c3ea9d7f8a9729e, sg:537:636e84368f6b69aa, sg:545:9e1b55a8dca3c731, sg:548:712f84e32e8626f7, sg:552:bbd66349cc0a6e81), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F229" s="14" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="E255" s="14" t="inlineStr">
         <is>
-          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:522:78f45a6425fd06b5), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:543:687bded188010ece), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F255" s="14" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="E256" s="18" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:525:ab91d3da9236dd8d), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:546:d7cd108bd6a7ac51), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F256" s="18" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="E257" s="14" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:525:ab91d3da9236dd8d), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:546:d7cd108bd6a7ac51), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F257" s="14" t="inlineStr">

--- a/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
+++ b/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
@@ -2078,7 +2078,7 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:539:cbbeb79ed833d3b8, sg:547:f33d92d467239ee0, sg:553:6abfe8183a178376), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:560:69a40dd8e5f2d4f2, sg:568:4685de24842e2393, sg:574:cae3e1696e3aa98d), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:539:cbbeb79ed833d3b8, sg:547:f33d92d467239ee0, sg:553:6abfe8183a178376), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:560:69a40dd8e5f2d4f2, sg:568:4685de24842e2393, sg:574:cae3e1696e3aa98d), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F4" s="18" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
-          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:542:30280382d03df282, sg:549:e7caba8051f7831a, sg:550:388d34145b912de3), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:563:62103f13a5936d74, sg:570:201899cf8d1f81b0, sg:571:897c4efa591298f8), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F44" s="18" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:542:30280382d03df282, sg:549:e7caba8051f7831a, sg:550:388d34145b912de3), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:563:62103f13a5936d74, sg:570:201899cf8d1f81b0, sg:571:897c4efa591298f8), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:534:964accc8ed7028f7, sg:551:3bc766e39a382363), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:555:6b313bd23044c13b, sg:572:9e1d127db99aacc0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F112" s="18" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:534:964accc8ed7028f7, sg:551:3bc766e39a382363), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:555:6b313bd23044c13b, sg:572:9e1d127db99aacc0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F113" s="14" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="E130" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:534:964accc8ed7028f7, sg:540:e91c86aeac162a3e, sg:541:9a1f5bf48331cd25, sg:542:30280382d03df282, sg:543:687bded188010ece, sg:548:712f84e32e8626f7), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:555:6b313bd23044c13b, sg:561:8603442068b76e5f, sg:562:7f289e99ee8f93cb, sg:563:62103f13a5936d74, sg:564:b2b28e3e428a9712, sg:569:f44cd1c023977234), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F130" s="18" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:551:3bc766e39a382363), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:572:9e1d127db99aacc0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F203" s="14" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="E204" s="18" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:551:3bc766e39a382363), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:572:9e1d127db99aacc0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F204" s="18" t="inlineStr">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:535:4de191336cbedfc8, sg:538:824e5be61afc0314, sg:539:cbbeb79ed833d3b8, sg:546:d7cd108bd6a7ac51), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:556:4446d240f2371f47, sg:559:6b9b4881cf2645b2, sg:560:69a40dd8e5f2d4f2, sg:567:4d04ccb1e96a7ac0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F219" s="14" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="E220" s="18" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:535:4de191336cbedfc8, sg:538:824e5be61afc0314, sg:539:cbbeb79ed833d3b8, sg:546:d7cd108bd6a7ac51), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:556:4446d240f2371f47, sg:559:6b9b4881cf2645b2, sg:560:69a40dd8e5f2d4f2, sg:567:4d04ccb1e96a7ac0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F220" s="18" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="E229" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected. NARROWED 2026-08-04 (SG-HARD-006/007/010). This is no longer the broader claim that the recorder is unreachable by the agent it records. At the tiers the installer can actually deliver (0 and 1) the recorder runs under the agent's own uid, the chain key is a mode-600 file that anything the agent runs can read, and the socket authenticates ordering rather than the caller. The four named attacks are refused or detected. An agent that simply reads the key is not among them; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:535:4de191336cbedfc8, sg:536:3c3ea9d7f8a9729e, sg:537:636e84368f6b69aa, sg:545:9e1b55a8dca3c731, sg:548:712f84e32e8626f7, sg:552:bbd66349cc0a6e81), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected. NARROWED 2026-08-04 (SG-HARD-006/007/010). This is no longer the broader claim that the recorder is unreachable by the agent it records. At the tiers the installer can actually deliver (0 and 1) the recorder runs under the agent's own uid, the chain key is a mode-600 file that anything the agent runs can read, and the socket authenticates ordering rather than the caller. The four named attacks are refused or detected. An agent that simply reads the key is not among them; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:556:4446d240f2371f47, sg:557:c9e6a8065cccb1c7, sg:558:cbe80b09e55f2654, sg:566:d8eb11c476e2f3c8, sg:569:f44cd1c023977234, sg:573:b8e076360fdca4f0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F229" s="14" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="E255" s="14" t="inlineStr">
         <is>
-          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:543:687bded188010ece), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:564:b2b28e3e428a9712), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F255" s="14" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="E256" s="18" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:546:d7cd108bd6a7ac51), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:567:4d04ccb1e96a7ac0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F256" s="18" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="E257" s="14" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:546:d7cd108bd6a7ac51), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:567:4d04ccb1e96a7ac0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F257" s="14" t="inlineStr">

--- a/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
+++ b/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
@@ -2078,7 +2078,7 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:560:69a40dd8e5f2d4f2, sg:568:4685de24842e2393, sg:574:cae3e1696e3aa98d), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:581:e455fe0a6a6d9792, sg:589:529f0052ae6a9365, sg:595:77ee5d0cdf5f2bc9), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:560:69a40dd8e5f2d4f2, sg:568:4685de24842e2393, sg:574:cae3e1696e3aa98d), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:581:e455fe0a6a6d9792, sg:589:529f0052ae6a9365, sg:595:77ee5d0cdf5f2bc9), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F4" s="18" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
-          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:563:62103f13a5936d74, sg:570:201899cf8d1f81b0, sg:571:897c4efa591298f8), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:584:04ca582d03bc6e12, sg:591:e441f87301451eb1, sg:592:88ac03891f719f82), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F44" s="18" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:563:62103f13a5936d74, sg:570:201899cf8d1f81b0, sg:571:897c4efa591298f8), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:584:04ca582d03bc6e12, sg:591:e441f87301451eb1, sg:592:88ac03891f719f82), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:555:6b313bd23044c13b, sg:572:9e1d127db99aacc0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:576:7f7283f8995c9d4c, sg:593:54db81a0b9dd03b1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F112" s="18" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:555:6b313bd23044c13b, sg:572:9e1d127db99aacc0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:576:7f7283f8995c9d4c, sg:593:54db81a0b9dd03b1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F113" s="14" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="E130" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:555:6b313bd23044c13b, sg:561:8603442068b76e5f, sg:562:7f289e99ee8f93cb, sg:563:62103f13a5936d74, sg:564:b2b28e3e428a9712, sg:569:f44cd1c023977234), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:564:b2b28e3e428a9712, sg:576:7f7283f8995c9d4c, sg:582:d770a688a085feaa, sg:583:bee86eaeffa359a9, sg:584:04ca582d03bc6e12, sg:590:c4043105f321bf3d), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F130" s="18" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:572:9e1d127db99aacc0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:593:54db81a0b9dd03b1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F203" s="14" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="E204" s="18" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:572:9e1d127db99aacc0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:593:54db81a0b9dd03b1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F204" s="18" t="inlineStr">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:556:4446d240f2371f47, sg:559:6b9b4881cf2645b2, sg:560:69a40dd8e5f2d4f2, sg:567:4d04ccb1e96a7ac0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:577:5da9d45a74bcfaa8, sg:580:b5899b4373a5f1cc, sg:581:e455fe0a6a6d9792, sg:588:f1f9d44b4c7d95f5), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F219" s="14" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="E220" s="18" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:556:4446d240f2371f47, sg:559:6b9b4881cf2645b2, sg:560:69a40dd8e5f2d4f2, sg:567:4d04ccb1e96a7ac0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:577:5da9d45a74bcfaa8, sg:580:b5899b4373a5f1cc, sg:581:e455fe0a6a6d9792, sg:588:f1f9d44b4c7d95f5), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F220" s="18" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="E229" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected. NARROWED 2026-08-04 (SG-HARD-006/007/010). This is no longer the broader claim that the recorder is unreachable by the agent it records. At the tiers the installer can actually deliver (0 and 1) the recorder runs under the agent's own uid, the chain key is a mode-600 file that anything the agent runs can read, and the socket authenticates ordering rather than the caller. The four named attacks are refused or detected. An agent that simply reads the key is not among them; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:556:4446d240f2371f47, sg:557:c9e6a8065cccb1c7, sg:558:cbe80b09e55f2654, sg:566:d8eb11c476e2f3c8, sg:569:f44cd1c023977234, sg:573:b8e076360fdca4f0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected. NARROWED 2026-08-04 (SG-HARD-006/007/010). This is no longer the broader claim that the recorder is unreachable by the agent it records. At the tiers the installer can actually deliver (0 and 1) the recorder runs under the agent's own uid, the chain key is a mode-600 file that anything the agent runs can read, and the socket authenticates ordering rather than the caller. The four named attacks are refused or detected. An agent that simply reads the key is not among them; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:577:5da9d45a74bcfaa8, sg:578:122eca34e4349989, sg:579:d95ceed970b134b4, sg:587:bb90a3125e0c0208, sg:590:c4043105f321bf3d, sg:594:8b0c0aac1ae43918), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F229" s="14" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="E256" s="18" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:567:4d04ccb1e96a7ac0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:588:f1f9d44b4c7d95f5), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F256" s="18" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="E257" s="14" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:567:4d04ccb1e96a7ac0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:588:f1f9d44b4c7d95f5), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F257" s="14" t="inlineStr">

--- a/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
+++ b/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
@@ -2078,7 +2078,7 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:581:e455fe0a6a6d9792, sg:589:529f0052ae6a9365, sg:595:77ee5d0cdf5f2bc9), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:648:79f65700d3c4a9fc, sg:656:178bff302940ad33, sg:662:1e576c03b5ac9c4b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:581:e455fe0a6a6d9792, sg:589:529f0052ae6a9365, sg:595:77ee5d0cdf5f2bc9), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:648:79f65700d3c4a9fc, sg:656:178bff302940ad33, sg:662:1e576c03b5ac9c4b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F4" s="18" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
-          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:584:04ca582d03bc6e12, sg:591:e441f87301451eb1, sg:592:88ac03891f719f82), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:651:1262ef5bb2387bfe, sg:658:0033bd2a12742b57, sg:659:752d57e295e7b0e5), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F44" s="18" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:584:04ca582d03bc6e12, sg:591:e441f87301451eb1, sg:592:88ac03891f719f82), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:651:1262ef5bb2387bfe, sg:658:0033bd2a12742b57, sg:659:752d57e295e7b0e5), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:576:7f7283f8995c9d4c, sg:593:54db81a0b9dd03b1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:643:e3bf55b116877a50, sg:660:34446b9cc3ca3590), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F112" s="18" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:576:7f7283f8995c9d4c, sg:593:54db81a0b9dd03b1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:643:e3bf55b116877a50, sg:660:34446b9cc3ca3590), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F113" s="14" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="E130" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:564:b2b28e3e428a9712, sg:576:7f7283f8995c9d4c, sg:582:d770a688a085feaa, sg:583:bee86eaeffa359a9, sg:584:04ca582d03bc6e12, sg:590:c4043105f321bf3d), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:643:e3bf55b116877a50, sg:649:79710cd629593242, sg:650:642a850b9a4cdf32, sg:651:1262ef5bb2387bfe, sg:652:8716292f832baf2f, sg:657:9ddadaf9413cdfa6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F130" s="18" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:593:54db81a0b9dd03b1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:660:34446b9cc3ca3590), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F203" s="14" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="E204" s="18" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:593:54db81a0b9dd03b1), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:660:34446b9cc3ca3590), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F204" s="18" t="inlineStr">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:577:5da9d45a74bcfaa8, sg:580:b5899b4373a5f1cc, sg:581:e455fe0a6a6d9792, sg:588:f1f9d44b4c7d95f5), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:644:3fca24ca5e10365e, sg:647:d422d47a98a34232, sg:648:79f65700d3c4a9fc, sg:655:9dc1a2015e0663df), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F219" s="14" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="E220" s="18" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:577:5da9d45a74bcfaa8, sg:580:b5899b4373a5f1cc, sg:581:e455fe0a6a6d9792, sg:588:f1f9d44b4c7d95f5), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:644:3fca24ca5e10365e, sg:647:d422d47a98a34232, sg:648:79f65700d3c4a9fc, sg:655:9dc1a2015e0663df), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F220" s="18" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="E229" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected. NARROWED 2026-08-04 (SG-HARD-006/007/010). This is no longer the broader claim that the recorder is unreachable by the agent it records. At the tiers the installer can actually deliver (0 and 1) the recorder runs under the agent's own uid, the chain key is a mode-600 file that anything the agent runs can read, and the socket authenticates ordering rather than the caller. The four named attacks are refused or detected. An agent that simply reads the key is not among them; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:577:5da9d45a74bcfaa8, sg:578:122eca34e4349989, sg:579:d95ceed970b134b4, sg:587:bb90a3125e0c0208, sg:590:c4043105f321bf3d, sg:594:8b0c0aac1ae43918), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected. NARROWED 2026-08-04 (SG-HARD-006/007/010). This is no longer the broader claim that the recorder is unreachable by the agent it records. At the tiers the installer can actually deliver (0 and 1) the recorder runs under the agent's own uid, the chain key is a mode-600 file that anything the agent runs can read, and the socket authenticates ordering rather than the caller. The four named attacks are refused or detected. An agent that simply reads the key is not among them; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:644:3fca24ca5e10365e, sg:645:8a7430b57a445c03, sg:646:6d68fc7f1692ff02, sg:654:32b6ba2fc56ce716, sg:657:9ddadaf9413cdfa6, sg:661:01cbc3bb6c4ad8ca), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F229" s="14" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="E255" s="14" t="inlineStr">
         <is>
-          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:564:b2b28e3e428a9712), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:652:8716292f832baf2f), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F255" s="14" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="E256" s="18" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:588:f1f9d44b4c7d95f5), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:655:9dc1a2015e0663df), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F256" s="18" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="E257" s="14" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:588:f1f9d44b4c7d95f5), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:655:9dc1a2015e0663df), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F257" s="14" t="inlineStr">

--- a/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
+++ b/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
@@ -2078,7 +2078,7 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:648:79f65700d3c4a9fc, sg:656:178bff302940ad33, sg:662:1e576c03b5ac9c4b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:763:caa4ed175bfaaf2d, sg:771:bad301b8df4d97b4, sg:777:95d4ccd4a0509476), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:648:79f65700d3c4a9fc, sg:656:178bff302940ad33, sg:662:1e576c03b5ac9c4b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:763:caa4ed175bfaaf2d, sg:771:bad301b8df4d97b4, sg:777:95d4ccd4a0509476), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F4" s="18" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
-          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:651:1262ef5bb2387bfe, sg:658:0033bd2a12742b57, sg:659:752d57e295e7b0e5), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:766:02bab40a66508590, sg:773:6a7723d631cd73bf, sg:774:c0b60c1fa08f1be8), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F44" s="18" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:651:1262ef5bb2387bfe, sg:658:0033bd2a12742b57, sg:659:752d57e295e7b0e5), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:766:02bab40a66508590, sg:773:6a7723d631cd73bf, sg:774:c0b60c1fa08f1be8), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:643:e3bf55b116877a50, sg:660:34446b9cc3ca3590), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:758:c94a8157129589e9, sg:775:413d7a97db267d3e), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F112" s="18" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:643:e3bf55b116877a50, sg:660:34446b9cc3ca3590), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:758:c94a8157129589e9, sg:775:413d7a97db267d3e), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F113" s="14" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="E130" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:643:e3bf55b116877a50, sg:649:79710cd629593242, sg:650:642a850b9a4cdf32, sg:651:1262ef5bb2387bfe, sg:652:8716292f832baf2f, sg:657:9ddadaf9413cdfa6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:758:c94a8157129589e9, sg:764:ec1e8191680d4ee8, sg:765:0af46a9021074df3, sg:766:02bab40a66508590, sg:767:3ab17dd8a15a9b85, sg:772:3606c568ca280b3f), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F130" s="18" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:660:34446b9cc3ca3590), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:775:413d7a97db267d3e), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F203" s="14" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="E204" s="18" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:660:34446b9cc3ca3590), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:775:413d7a97db267d3e), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F204" s="18" t="inlineStr">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:644:3fca24ca5e10365e, sg:647:d422d47a98a34232, sg:648:79f65700d3c4a9fc, sg:655:9dc1a2015e0663df), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:759:7f56c88e7b1f4e9d, sg:762:aeadbd7d2c1232e1, sg:763:caa4ed175bfaaf2d, sg:770:29c8ad6c083e83ca), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F219" s="14" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="E220" s="18" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:644:3fca24ca5e10365e, sg:647:d422d47a98a34232, sg:648:79f65700d3c4a9fc, sg:655:9dc1a2015e0663df), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:759:7f56c88e7b1f4e9d, sg:762:aeadbd7d2c1232e1, sg:763:caa4ed175bfaaf2d, sg:770:29c8ad6c083e83ca), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F220" s="18" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="E229" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected. NARROWED 2026-08-04 (SG-HARD-006/007/010). This is no longer the broader claim that the recorder is unreachable by the agent it records. At the tiers the installer can actually deliver (0 and 1) the recorder runs under the agent's own uid, the chain key is a mode-600 file that anything the agent runs can read, and the socket authenticates ordering rather than the caller. The four named attacks are refused or detected. An agent that simply reads the key is not among them; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:644:3fca24ca5e10365e, sg:645:8a7430b57a445c03, sg:646:6d68fc7f1692ff02, sg:654:32b6ba2fc56ce716, sg:657:9ddadaf9413cdfa6, sg:661:01cbc3bb6c4ad8ca), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected. NARROWED 2026-08-04 (SG-HARD-006/007/010). This is no longer the broader claim that the recorder is unreachable by the agent it records. At the tiers the installer can actually deliver (0 and 1) the recorder runs under the agent's own uid, the chain key is a mode-600 file that anything the agent runs can read, and the socket authenticates ordering rather than the caller. The four named attacks are refused or detected. An agent that simply reads the key is not among them; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:759:7f56c88e7b1f4e9d, sg:760:e72891ce82ce4708, sg:761:d4842047f7706afc, sg:769:70e3dd2d9b6d100a, sg:772:3606c568ca280b3f, sg:776:c87c776c23bdff35), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F229" s="14" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="E255" s="14" t="inlineStr">
         <is>
-          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:652:8716292f832baf2f), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:767:3ab17dd8a15a9b85), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F255" s="14" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="E256" s="18" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:655:9dc1a2015e0663df), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:770:29c8ad6c083e83ca), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F256" s="18" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="E257" s="14" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:655:9dc1a2015e0663df), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:770:29c8ad6c083e83ca), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F257" s="14" t="inlineStr">

--- a/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
+++ b/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
@@ -2078,7 +2078,7 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:763:caa4ed175bfaaf2d, sg:771:bad301b8df4d97b4, sg:777:95d4ccd4a0509476), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:784:c8c48a4d73308ebb, sg:792:deb6f14a8a42be81, sg:798:616d464a9f45a718), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:763:caa4ed175bfaaf2d, sg:771:bad301b8df4d97b4, sg:777:95d4ccd4a0509476), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:784:c8c48a4d73308ebb, sg:792:deb6f14a8a42be81, sg:798:616d464a9f45a718), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F4" s="18" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
-          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:766:02bab40a66508590, sg:773:6a7723d631cd73bf, sg:774:c0b60c1fa08f1be8), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:787:f4ac10a82c4e57e3, sg:794:b783e1cf897a05b1, sg:795:e32c2afee224a616), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F44" s="18" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:766:02bab40a66508590, sg:773:6a7723d631cd73bf, sg:774:c0b60c1fa08f1be8), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:787:f4ac10a82c4e57e3, sg:794:b783e1cf897a05b1, sg:795:e32c2afee224a616), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:758:c94a8157129589e9, sg:775:413d7a97db267d3e), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:779:2c8d35998ad6eccf, sg:796:eb94f89d8c988568), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F112" s="18" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:758:c94a8157129589e9, sg:775:413d7a97db267d3e), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:779:2c8d35998ad6eccf, sg:796:eb94f89d8c988568), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F113" s="14" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="E130" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:758:c94a8157129589e9, sg:764:ec1e8191680d4ee8, sg:765:0af46a9021074df3, sg:766:02bab40a66508590, sg:767:3ab17dd8a15a9b85, sg:772:3606c568ca280b3f), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:779:2c8d35998ad6eccf, sg:785:29380601e6b48695, sg:786:009577b73f893a5d, sg:787:f4ac10a82c4e57e3, sg:788:aea879f85d3e1436, sg:793:662c2f2110ceac70), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F130" s="18" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:775:413d7a97db267d3e), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:796:eb94f89d8c988568), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F203" s="14" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="E204" s="18" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:775:413d7a97db267d3e), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:796:eb94f89d8c988568), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F204" s="18" t="inlineStr">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:759:7f56c88e7b1f4e9d, sg:762:aeadbd7d2c1232e1, sg:763:caa4ed175bfaaf2d, sg:770:29c8ad6c083e83ca), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:780:97188d96cec3a302, sg:783:82a65f30aeacbaa3, sg:784:c8c48a4d73308ebb, sg:791:231c6bcb96ee74af), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F219" s="14" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="E220" s="18" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:759:7f56c88e7b1f4e9d, sg:762:aeadbd7d2c1232e1, sg:763:caa4ed175bfaaf2d, sg:770:29c8ad6c083e83ca), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:780:97188d96cec3a302, sg:783:82a65f30aeacbaa3, sg:784:c8c48a4d73308ebb, sg:791:231c6bcb96ee74af), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F220" s="18" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="E229" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected. NARROWED 2026-08-04 (SG-HARD-006/007/010). This is no longer the broader claim that the recorder is unreachable by the agent it records. At the tiers the installer can actually deliver (0 and 1) the recorder runs under the agent's own uid, the chain key is a mode-600 file that anything the agent runs can read, and the socket authenticates ordering rather than the caller. The four named attacks are refused or detected. An agent that simply reads the key is not among them; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:759:7f56c88e7b1f4e9d, sg:760:e72891ce82ce4708, sg:761:d4842047f7706afc, sg:769:70e3dd2d9b6d100a, sg:772:3606c568ca280b3f, sg:776:c87c776c23bdff35), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected. NARROWED 2026-08-04 (SG-HARD-006/007/010). This is no longer the broader claim that the recorder is unreachable by the agent it records. At the tiers the installer can actually deliver (0 and 1) the recorder runs under the agent's own uid, the chain key is a mode-600 file that anything the agent runs can read, and the socket authenticates ordering rather than the caller. The four named attacks are refused or detected. An agent that simply reads the key is not among them; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:780:97188d96cec3a302, sg:781:f0d4f207af1237d1, sg:782:7ca87b2a8f3a88cb, sg:790:7c2730dfd48eb40b, sg:793:662c2f2110ceac70, sg:797:0a1aef1ba350377d), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F229" s="14" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="E255" s="14" t="inlineStr">
         <is>
-          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:767:3ab17dd8a15a9b85), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:788:aea879f85d3e1436), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F255" s="14" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="E256" s="18" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:770:29c8ad6c083e83ca), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:791:231c6bcb96ee74af), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F256" s="18" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="E257" s="14" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:770:29c8ad6c083e83ca), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:791:231c6bcb96ee74af), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F257" s="14" t="inlineStr">

--- a/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
+++ b/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
@@ -2078,7 +2078,7 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:784:c8c48a4d73308ebb, sg:792:deb6f14a8a42be81, sg:798:616d464a9f45a718), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration. SURFACE NARROWED 2026-08-05 (R2-003). This claim previously declared hook:SessionStart; its proof exercises the mechanism directly rather than driving that hook, and registration is not execution. The surface is withdrawn rather than asserted. Deployed-hook behaviour is a separate claim, and it has not been made; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:851:22f751f9dc2fae59, sg:859:02e44cb93e7a4560, sg:865:17fce297e11b3fd7), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:784:c8c48a4d73308ebb, sg:792:deb6f14a8a42be81, sg:798:616d464a9f45a718), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration. SURFACE NARROWED 2026-08-05 (R2-003). This claim previously declared hook:SessionStart; its proof exercises the mechanism directly rather than driving that hook, and registration is not execution. The surface is withdrawn rather than asserted. Deployed-hook behaviour is a separate claim, and it has not been made; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:851:22f751f9dc2fae59, sg:859:02e44cb93e7a4560, sg:865:17fce297e11b3fd7), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F4" s="18" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
-          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:787:f4ac10a82c4e57e3, sg:794:b783e1cf897a05b1, sg:795:e32c2afee224a616), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:854:8892fdc4cc4bee3f, sg:861:7004f70221a62847, sg:862:1c8867ccb0cdaa2a), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F44" s="18" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:787:f4ac10a82c4e57e3, sg:794:b783e1cf897a05b1, sg:795:e32c2afee224a616), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:854:8892fdc4cc4bee3f, sg:861:7004f70221a62847, sg:862:1c8867ccb0cdaa2a), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:779:2c8d35998ad6eccf, sg:796:eb94f89d8c988568), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE NARROWED 2026-08-05 (R2-003). This claim previously declared hook:PostToolUse; its proof exercises the mechanism directly rather than driving that hook, and registration is not execution. The surface is withdrawn rather than asserted. Deployed-hook behaviour is a separate claim, and it has not been made; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:846:90609585c37284cb, sg:863:c55bb0a4b78ade09), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F112" s="18" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:779:2c8d35998ad6eccf, sg:796:eb94f89d8c988568), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE NARROWED 2026-08-05 (R2-003). This claim previously declared hook:PostToolUse; its proof exercises the mechanism directly rather than driving that hook, and registration is not execution. The surface is withdrawn rather than asserted. Deployed-hook behaviour is a separate claim, and it has not been made; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:846:90609585c37284cb, sg:863:c55bb0a4b78ade09), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F113" s="14" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="E130" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read; The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Under `bar` the model receives only a handle or summary, and an unsigned script is refused; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:779:2c8d35998ad6eccf, sg:785:29380601e6b48695, sg:786:009577b73f893a5d, sg:787:f4ac10a82c4e57e3, sg:788:aea879f85d3e1436, sg:793:662c2f2110ceac70), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE NARROWED 2026-08-05 (R2-003). This claim previously declared hook:PostToolUse; its proof exercises the mechanism directly rather than driving that hook, and registration is not execution. The surface is withdrawn rather than asserted. Deployed-hook behaviour is a separate claim, and it has not been made; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read. SURFACE NARROWED 2026-08-05 (R2-003). This claim previously declared hook:PreToolUse; its proof exercises the mechanism directly rather than driving that hook, and registration is not execution. The surface is withdrawn rather than asserted. Deployed-hook behaviour is a separate claim, and it has not been made; The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Under `bar` the model receives only a handle or summary, and an unsigned script is refused. SURFACE NARROWED 2026-08-05 (R2-003). This claim previously declared hook:PreToolUse; its proof exercises the mechanism directly rather than driving that hook, and registration is not execution. The surface is withdrawn rather than asserted. Deployed-hook behaviour is a separate claim, and it has not been made; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:846:90609585c37284cb, sg:852:a9fb3c60b2fa3a61, sg:853:e97f062f71d01a32, sg:854:8892fdc4cc4bee3f, sg:855:71a7902ef91a590d, sg:860:1309b4778cefca07), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F130" s="18" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:796:eb94f89d8c988568), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:863:c55bb0a4b78ade09), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F203" s="14" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="E204" s="18" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:796:eb94f89d8c988568), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:863:c55bb0a4b78ade09), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F204" s="18" t="inlineStr">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:780:97188d96cec3a302, sg:783:82a65f30aeacbaa3, sg:784:c8c48a4d73308ebb, sg:791:231c6bcb96ee74af), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE NARROWED 2026-08-05 (R2-003). This claim previously declared hook:Stop; its proof exercises the mechanism directly rather than driving that hook, and registration is not execution. The surface is withdrawn rather than asserted. Deployed-hook behaviour is a separate claim, and it has not been made. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:847:41824c299ad00074, sg:850:3dc422f62c5bd481, sg:851:22f751f9dc2fae59, sg:858:3831940b083ee1b4), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F219" s="14" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="E220" s="18" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:780:97188d96cec3a302, sg:783:82a65f30aeacbaa3, sg:784:c8c48a4d73308ebb, sg:791:231c6bcb96ee74af), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE NARROWED 2026-08-05 (R2-003). This claim previously declared hook:Stop; its proof exercises the mechanism directly rather than driving that hook, and registration is not execution. The surface is withdrawn rather than asserted. Deployed-hook behaviour is a separate claim, and it has not been made. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:847:41824c299ad00074, sg:850:3dc422f62c5bd481, sg:851:22f751f9dc2fae59, sg:858:3831940b083ee1b4), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F220" s="18" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="E229" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected. NARROWED 2026-08-04 (SG-HARD-006/007/010). This is no longer the broader claim that the recorder is unreachable by the agent it records. At the tiers the installer can actually deliver (0 and 1) the recorder runs under the agent's own uid, the chain key is a mode-600 file that anything the agent runs can read, and the socket authenticates ordering rather than the caller. The four named attacks are refused or detected. An agent that simply reads the key is not among them; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:780:97188d96cec3a302, sg:781:f0d4f207af1237d1, sg:782:7ca87b2a8f3a88cb, sg:790:7c2730dfd48eb40b, sg:793:662c2f2110ceac70, sg:797:0a1aef1ba350377d), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected. NARROWED 2026-08-04 (SG-HARD-006/007/010). This is no longer the broader claim that the recorder is unreachable by the agent it records. At the tiers the installer can actually deliver (0 and 1) the recorder runs under the agent's own uid, the chain key is a mode-600 file that anything the agent runs can read, and the socket authenticates ordering rather than the caller. The four named attacks are refused or detected. An agent that simply reads the key is not among them; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:847:41824c299ad00074, sg:848:b5df7a32140d368c, sg:849:47e3eb06a6e56040, sg:857:ddf9c21d14dc3079, sg:860:1309b4778cefca07, sg:864:18e115ac5361c74c), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F229" s="14" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="E255" s="14" t="inlineStr">
         <is>
-          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:788:aea879f85d3e1436), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. SURFACE NARROWED 2026-08-05 (R2-003). This claim previously declared hook:PreToolUse; its proof exercises the mechanism directly rather than driving that hook, and registration is not execution. The surface is withdrawn rather than asserted. Deployed-hook behaviour is a separate claim, and it has not been made. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:855:71a7902ef91a590d), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F255" s="14" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="E256" s="18" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:791:231c6bcb96ee74af), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE NARROWED 2026-08-05 (R2-003). This claim previously declared hook:Stop; its proof exercises the mechanism directly rather than driving that hook, and registration is not execution. The surface is withdrawn rather than asserted. Deployed-hook behaviour is a separate claim, and it has not been made. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:858:3831940b083ee1b4), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F256" s="18" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="E257" s="14" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:791:231c6bcb96ee74af), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE NARROWED 2026-08-05 (R2-003). This claim previously declared hook:Stop; its proof exercises the mechanism directly rather than driving that hook, and registration is not execution. The surface is withdrawn rather than asserted. Deployed-hook behaviour is a separate claim, and it has not been made. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:858:3831940b083ee1b4), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F257" s="14" t="inlineStr">

--- a/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
+++ b/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
@@ -2078,7 +2078,7 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration. SURFACE NARROWED 2026-08-05 (R2-003). This claim previously declared hook:SessionStart; its proof exercises the mechanism directly rather than driving that hook, and registration is not execution. The surface is withdrawn rather than asserted. Deployed-hook behaviour is a separate claim, and it has not been made; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:851:22f751f9dc2fae59, sg:859:02e44cb93e7a4560, sg:865:17fce297e11b3fd7), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration. SURFACE RESTORED 2026-08-05: hook:SessionStart was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. SURFACE RESTORED 2026-08-05: plugin:stop-guessing, skill:stop-guessing, command:/custody was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1251:c9b8e88a9b11e91d, sg:1267:b962d2e4c1d7f35c, sg:1279:40ffa82d48d50a14), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration. SURFACE NARROWED 2026-08-05 (R2-003). This claim previously declared hook:SessionStart; its proof exercises the mechanism directly rather than driving that hook, and registration is not execution. The surface is withdrawn rather than asserted. Deployed-hook behaviour is a separate claim, and it has not been made; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:851:22f751f9dc2fae59, sg:859:02e44cb93e7a4560, sg:865:17fce297e11b3fd7), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration. SURFACE RESTORED 2026-08-05: hook:SessionStart was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. SURFACE RESTORED 2026-08-05: plugin:stop-guessing, skill:stop-guessing, command:/custody was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1251:c9b8e88a9b11e91d, sg:1267:b962d2e4c1d7f35c, sg:1279:40ffa82d48d50a14), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F4" s="18" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
-          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:854:8892fdc4cc4bee3f, sg:861:7004f70221a62847, sg:862:1c8867ccb0cdaa2a), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. SURFACE RESTORED 2026-08-05: command:/no-noodle, command:/noodle-options was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1257:2e437463cee9c902, sg:1271:16f320f0608ba99d, sg:1273:17cc306d3ae0e12c), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F44" s="18" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:854:8892fdc4cc4bee3f, sg:861:7004f70221a62847, sg:862:1c8867ccb0cdaa2a), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. SURFACE RESTORED 2026-08-05: command:/no-noodle, command:/noodle-options was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1257:2e437463cee9c902, sg:1271:16f320f0608ba99d, sg:1273:17cc306d3ae0e12c), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE NARROWED 2026-08-05 (R2-003). This claim previously declared hook:PostToolUse; its proof exercises the mechanism directly rather than driving that hook, and registration is not execution. The surface is withdrawn rather than asserted. Deployed-hook behaviour is a separate claim, and it has not been made; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:846:90609585c37284cb, sg:863:c55bb0a4b78ade09), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE RESTORED 2026-08-05: hook:PostToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1241:53d48a71bce84e54, sg:1275:62cfef10ed45a048), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F112" s="18" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE NARROWED 2026-08-05 (R2-003). This claim previously declared hook:PostToolUse; its proof exercises the mechanism directly rather than driving that hook, and registration is not execution. The surface is withdrawn rather than asserted. Deployed-hook behaviour is a separate claim, and it has not been made; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:846:90609585c37284cb, sg:863:c55bb0a4b78ade09), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE RESTORED 2026-08-05: hook:PostToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1241:53d48a71bce84e54, sg:1275:62cfef10ed45a048), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F113" s="14" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="E130" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE NARROWED 2026-08-05 (R2-003). This claim previously declared hook:PostToolUse; its proof exercises the mechanism directly rather than driving that hook, and registration is not execution. The surface is withdrawn rather than asserted. Deployed-hook behaviour is a separate claim, and it has not been made; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read. SURFACE NARROWED 2026-08-05 (R2-003). This claim previously declared hook:PreToolUse; its proof exercises the mechanism directly rather than driving that hook, and registration is not execution. The surface is withdrawn rather than asserted. Deployed-hook behaviour is a separate claim, and it has not been made; The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Under `bar` the model receives only a handle or summary, and an unsigned script is refused. SURFACE NARROWED 2026-08-05 (R2-003). This claim previously declared hook:PreToolUse; its proof exercises the mechanism directly rather than driving that hook, and registration is not execution. The surface is withdrawn rather than asserted. Deployed-hook behaviour is a separate claim, and it has not been made; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:846:90609585c37284cb, sg:852:a9fb3c60b2fa3a61, sg:853:e97f062f71d01a32, sg:854:8892fdc4cc4bee3f, sg:855:71a7902ef91a590d, sg:860:1309b4778cefca07), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE RESTORED 2026-08-05: hook:PostToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted. SURFACE RESTORED 2026-08-05: cli:"stop-guessing demo --posture steer" was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read. SURFACE RESTORED 2026-08-05: hook:PreToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Under `bar` the model receives only a handle or summary, and an unsigned script is refused. SURFACE RESTORED 2026-08-05: hook:PreToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1241:53d48a71bce84e54, sg:1253:ce188adc8c45053e, sg:1255:dbd256da1b8149d7, sg:1257:2e437463cee9c902, sg:1259:0ce46ab15368c1a0, sg:1269:9a568ef8d688b310), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F130" s="18" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:863:c55bb0a4b78ade09), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1275:62cfef10ed45a048), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F203" s="14" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="E204" s="18" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:863:c55bb0a4b78ade09), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1275:62cfef10ed45a048), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F204" s="18" t="inlineStr">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE NARROWED 2026-08-05 (R2-003). This claim previously declared hook:Stop; its proof exercises the mechanism directly rather than driving that hook, and registration is not execution. The surface is withdrawn rather than asserted. Deployed-hook behaviour is a separate claim, and it has not been made. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:847:41824c299ad00074, sg:850:3dc422f62c5bd481, sg:851:22f751f9dc2fae59, sg:858:3831940b083ee1b4), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked. SURFACE RESTORED 2026-08-05: cli:"stop-guessing record emit" was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1243:9a7637ff3b5ee4ff, sg:1249:3a2de856d5ca6a8e, sg:1251:c9b8e88a9b11e91d, sg:1265:aefda3c1e886576a), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F219" s="14" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="E220" s="18" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE NARROWED 2026-08-05 (R2-003). This claim previously declared hook:Stop; its proof exercises the mechanism directly rather than driving that hook, and registration is not execution. The surface is withdrawn rather than asserted. Deployed-hook behaviour is a separate claim, and it has not been made. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:847:41824c299ad00074, sg:850:3dc422f62c5bd481, sg:851:22f751f9dc2fae59, sg:858:3831940b083ee1b4), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked. SURFACE RESTORED 2026-08-05: cli:"stop-guessing record emit" was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1243:9a7637ff3b5ee4ff, sg:1249:3a2de856d5ca6a8e, sg:1251:c9b8e88a9b11e91d, sg:1265:aefda3c1e886576a), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F220" s="18" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="E229" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected. NARROWED 2026-08-04 (SG-HARD-006/007/010). This is no longer the broader claim that the recorder is unreachable by the agent it records. At the tiers the installer can actually deliver (0 and 1) the recorder runs under the agent's own uid, the chain key is a mode-600 file that anything the agent runs can read, and the socket authenticates ordering rather than the caller. The four named attacks are refused or detected. An agent that simply reads the key is not among them; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:847:41824c299ad00074, sg:848:b5df7a32140d368c, sg:849:47e3eb06a6e56040, sg:857:ddf9c21d14dc3079, sg:860:1309b4778cefca07, sg:864:18e115ac5361c74c), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected. NARROWED 2026-08-04 (SG-HARD-006/007/010). This is no longer the broader claim that the recorder is unreachable by the agent it records. At the tiers the installer can actually deliver (0 and 1) the recorder runs under the agent's own uid, the chain key is a mode-600 file that anything the agent runs can read, and the socket authenticates ordering rather than the caller. The four named attacks are refused or detected. An agent that simply reads the key is not among them; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1243:9a7637ff3b5ee4ff, sg:1245:836310689b1fc489, sg:1247:d2756310f2ecfa67, sg:1263:84b55825f80b1720, sg:1269:9a568ef8d688b310, sg:1277:21eaeadba806469a), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F229" s="14" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="E255" s="14" t="inlineStr">
         <is>
-          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. SURFACE NARROWED 2026-08-05 (R2-003). This claim previously declared hook:PreToolUse; its proof exercises the mechanism directly rather than driving that hook, and registration is not execution. The surface is withdrawn rather than asserted. Deployed-hook behaviour is a separate claim, and it has not been made. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:855:71a7902ef91a590d), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. SURFACE RESTORED 2026-08-05: hook:PreToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1259:0ce46ab15368c1a0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F255" s="14" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="E256" s="18" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE NARROWED 2026-08-05 (R2-003). This claim previously declared hook:Stop; its proof exercises the mechanism directly rather than driving that hook, and registration is not execution. The surface is withdrawn rather than asserted. Deployed-hook behaviour is a separate claim, and it has not been made. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:858:3831940b083ee1b4), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1265:aefda3c1e886576a), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F256" s="18" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="E257" s="14" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE NARROWED 2026-08-05 (R2-003). This claim previously declared hook:Stop; its proof exercises the mechanism directly rather than driving that hook, and registration is not execution. The surface is withdrawn rather than asserted. Deployed-hook behaviour is a separate claim, and it has not been made. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:858:3831940b083ee1b4), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1265:aefda3c1e886576a), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F257" s="14" t="inlineStr">

--- a/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
+++ b/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
@@ -2078,7 +2078,7 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration. SURFACE RESTORED 2026-08-05: hook:SessionStart was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. SURFACE RESTORED 2026-08-05: plugin:stop-guessing, skill:stop-guessing, command:/custody was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1251:c9b8e88a9b11e91d, sg:1267:b962d2e4c1d7f35c, sg:1279:40ffa82d48d50a14), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration. SURFACE RESTORED 2026-08-05: hook:SessionStart was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. SURFACE RESTORED 2026-08-05: plugin:stop-guessing, skill:stop-guessing, command:/custody was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1377:f2e620b51f56ba80, sg:1393:756cb0fadce91a5c, sg:1405:ac40f4ea3e73ae01), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration. SURFACE RESTORED 2026-08-05: hook:SessionStart was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. SURFACE RESTORED 2026-08-05: plugin:stop-guessing, skill:stop-guessing, command:/custody was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1251:c9b8e88a9b11e91d, sg:1267:b962d2e4c1d7f35c, sg:1279:40ffa82d48d50a14), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration. SURFACE RESTORED 2026-08-05: hook:SessionStart was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. SURFACE RESTORED 2026-08-05: plugin:stop-guessing, skill:stop-guessing, command:/custody was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1377:f2e620b51f56ba80, sg:1393:756cb0fadce91a5c, sg:1405:ac40f4ea3e73ae01), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F4" s="18" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
-          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. SURFACE RESTORED 2026-08-05: command:/no-noodle, command:/noodle-options was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1257:2e437463cee9c902, sg:1271:16f320f0608ba99d, sg:1273:17cc306d3ae0e12c), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. SURFACE RESTORED 2026-08-05: command:/no-noodle, command:/noodle-options was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1383:56a30014dd4fb1ef, sg:1397:6be771a1609f1f04, sg:1399:2bed589e4c313ad9), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F44" s="18" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. SURFACE RESTORED 2026-08-05: command:/no-noodle, command:/noodle-options was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1257:2e437463cee9c902, sg:1271:16f320f0608ba99d, sg:1273:17cc306d3ae0e12c), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. SURFACE RESTORED 2026-08-05: command:/no-noodle, command:/noodle-options was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1383:56a30014dd4fb1ef, sg:1397:6be771a1609f1f04, sg:1399:2bed589e4c313ad9), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE RESTORED 2026-08-05: hook:PostToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1241:53d48a71bce84e54, sg:1275:62cfef10ed45a048), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE RESTORED 2026-08-05: hook:PostToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1367:a97c45f0b06c9f8a, sg:1401:1c4947958496cf25), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F112" s="18" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE RESTORED 2026-08-05: hook:PostToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1241:53d48a71bce84e54, sg:1275:62cfef10ed45a048), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE RESTORED 2026-08-05: hook:PostToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1367:a97c45f0b06c9f8a, sg:1401:1c4947958496cf25), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F113" s="14" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="E130" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE RESTORED 2026-08-05: hook:PostToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted. SURFACE RESTORED 2026-08-05: cli:"stop-guessing demo --posture steer" was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read. SURFACE RESTORED 2026-08-05: hook:PreToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Under `bar` the model receives only a handle or summary, and an unsigned script is refused. SURFACE RESTORED 2026-08-05: hook:PreToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1241:53d48a71bce84e54, sg:1253:ce188adc8c45053e, sg:1255:dbd256da1b8149d7, sg:1257:2e437463cee9c902, sg:1259:0ce46ab15368c1a0, sg:1269:9a568ef8d688b310), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE RESTORED 2026-08-05: hook:PostToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted. SURFACE RESTORED 2026-08-05: cli:"stop-guessing demo --posture steer" was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read. SURFACE RESTORED 2026-08-05: hook:PreToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Under `bar` the model receives only a handle or summary, and an unsigned script is refused. SURFACE RESTORED 2026-08-05: hook:PreToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1367:a97c45f0b06c9f8a, sg:1379:d802935a895e96f5, sg:1381:505fdfbedbb5e088, sg:1383:56a30014dd4fb1ef, sg:1385:71b5c8293bcf13bc, sg:1395:5769d2ad015984b2), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F130" s="18" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1275:62cfef10ed45a048), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1401:1c4947958496cf25), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F203" s="14" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="E204" s="18" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1275:62cfef10ed45a048), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1401:1c4947958496cf25), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F204" s="18" t="inlineStr">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked. SURFACE RESTORED 2026-08-05: cli:"stop-guessing record emit" was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1243:9a7637ff3b5ee4ff, sg:1249:3a2de856d5ca6a8e, sg:1251:c9b8e88a9b11e91d, sg:1265:aefda3c1e886576a), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked. SURFACE RESTORED 2026-08-05: cli:"stop-guessing record emit" was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1369:fa724260dfc6fb61, sg:1375:dc5b338c7cf61d3e, sg:1377:f2e620b51f56ba80, sg:1391:9f29530c0b6bea25), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F219" s="14" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="E220" s="18" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked. SURFACE RESTORED 2026-08-05: cli:"stop-guessing record emit" was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1243:9a7637ff3b5ee4ff, sg:1249:3a2de856d5ca6a8e, sg:1251:c9b8e88a9b11e91d, sg:1265:aefda3c1e886576a), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked. SURFACE RESTORED 2026-08-05: cli:"stop-guessing record emit" was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1369:fa724260dfc6fb61, sg:1375:dc5b338c7cf61d3e, sg:1377:f2e620b51f56ba80, sg:1391:9f29530c0b6bea25), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F220" s="18" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="E229" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected. NARROWED 2026-08-04 (SG-HARD-006/007/010). This is no longer the broader claim that the recorder is unreachable by the agent it records. At the tiers the installer can actually deliver (0 and 1) the recorder runs under the agent's own uid, the chain key is a mode-600 file that anything the agent runs can read, and the socket authenticates ordering rather than the caller. The four named attacks are refused or detected. An agent that simply reads the key is not among them; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1243:9a7637ff3b5ee4ff, sg:1245:836310689b1fc489, sg:1247:d2756310f2ecfa67, sg:1263:84b55825f80b1720, sg:1269:9a568ef8d688b310, sg:1277:21eaeadba806469a), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected. NARROWED 2026-08-04 (SG-HARD-006/007/010). This is no longer the broader claim that the recorder is unreachable by the agent it records. At the tiers the installer can actually deliver (0 and 1) the recorder runs under the agent's own uid, the chain key is a mode-600 file that anything the agent runs can read, and the socket authenticates ordering rather than the caller. The four named attacks are refused or detected. An agent that simply reads the key is not among them; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1369:fa724260dfc6fb61, sg:1371:8a2c9814c7c48cdd, sg:1373:056c5788b481d80e, sg:1389:1a1f9ee0a2a009e5, sg:1395:5769d2ad015984b2, sg:1403:5103275a02d42445), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F229" s="14" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="E255" s="14" t="inlineStr">
         <is>
-          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. SURFACE RESTORED 2026-08-05: hook:PreToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1259:0ce46ab15368c1a0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. SURFACE RESTORED 2026-08-05: hook:PreToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1385:71b5c8293bcf13bc), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F255" s="14" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="E256" s="18" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1265:aefda3c1e886576a), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1391:9f29530c0b6bea25), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F256" s="18" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="E257" s="14" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1265:aefda3c1e886576a), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1391:9f29530c0b6bea25), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F257" s="14" t="inlineStr">

--- a/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
+++ b/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
@@ -2078,7 +2078,7 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration. SURFACE RESTORED 2026-08-05: hook:SessionStart was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. SURFACE RESTORED 2026-08-05: plugin:stop-guessing, skill:stop-guessing, command:/custody was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1377:f2e620b51f56ba80, sg:1393:756cb0fadce91a5c, sg:1405:ac40f4ea3e73ae01), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration. SURFACE RESTORED 2026-08-05: hook:SessionStart was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. SURFACE RESTORED 2026-08-05: plugin:stop-guessing, skill:stop-guessing, command:/custody was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1419:473372eed5c569c1, sg:1435:071c785792443e03, sg:1447:a4353dcfd3a4edb6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration. SURFACE RESTORED 2026-08-05: hook:SessionStart was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. SURFACE RESTORED 2026-08-05: plugin:stop-guessing, skill:stop-guessing, command:/custody was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1377:f2e620b51f56ba80, sg:1393:756cb0fadce91a5c, sg:1405:ac40f4ea3e73ae01), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration. SURFACE RESTORED 2026-08-05: hook:SessionStart was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. SURFACE RESTORED 2026-08-05: plugin:stop-guessing, skill:stop-guessing, command:/custody was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1419:473372eed5c569c1, sg:1435:071c785792443e03, sg:1447:a4353dcfd3a4edb6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F4" s="18" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
-          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. SURFACE RESTORED 2026-08-05: command:/no-noodle, command:/noodle-options was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1383:56a30014dd4fb1ef, sg:1397:6be771a1609f1f04, sg:1399:2bed589e4c313ad9), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. SURFACE RESTORED 2026-08-05: command:/no-noodle, command:/noodle-options was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1425:c2242747be45d536, sg:1439:5004a3e05273d055, sg:1441:6f8245510780eab0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F44" s="18" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. SURFACE RESTORED 2026-08-05: command:/no-noodle, command:/noodle-options was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1383:56a30014dd4fb1ef, sg:1397:6be771a1609f1f04, sg:1399:2bed589e4c313ad9), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. SURFACE RESTORED 2026-08-05: command:/no-noodle, command:/noodle-options was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1425:c2242747be45d536, sg:1439:5004a3e05273d055, sg:1441:6f8245510780eab0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE RESTORED 2026-08-05: hook:PostToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1367:a97c45f0b06c9f8a, sg:1401:1c4947958496cf25), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE RESTORED 2026-08-05: hook:PostToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1409:98a3fa7e5522e981, sg:1443:c602903462fb1760), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F112" s="18" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE RESTORED 2026-08-05: hook:PostToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1367:a97c45f0b06c9f8a, sg:1401:1c4947958496cf25), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE RESTORED 2026-08-05: hook:PostToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1409:98a3fa7e5522e981, sg:1443:c602903462fb1760), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F113" s="14" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="E130" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE RESTORED 2026-08-05: hook:PostToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted. SURFACE RESTORED 2026-08-05: cli:"stop-guessing demo --posture steer" was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read. SURFACE RESTORED 2026-08-05: hook:PreToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Under `bar` the model receives only a handle or summary, and an unsigned script is refused. SURFACE RESTORED 2026-08-05: hook:PreToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1367:a97c45f0b06c9f8a, sg:1379:d802935a895e96f5, sg:1381:505fdfbedbb5e088, sg:1383:56a30014dd4fb1ef, sg:1385:71b5c8293bcf13bc, sg:1395:5769d2ad015984b2), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE RESTORED 2026-08-05: hook:PostToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted. SURFACE RESTORED 2026-08-05: cli:"stop-guessing demo --posture steer" was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read. SURFACE RESTORED 2026-08-05: hook:PreToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Under `bar` the model receives only a handle or summary, and an unsigned script is refused. SURFACE RESTORED 2026-08-05: hook:PreToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1409:98a3fa7e5522e981, sg:1421:7dc82ae505411ada, sg:1423:fe8489aef0034cc1, sg:1425:c2242747be45d536, sg:1427:b11d95b6bceb8b87, sg:1437:eca8ad675fe785ed), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F130" s="18" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1401:1c4947958496cf25), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1443:c602903462fb1760), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F203" s="14" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="E204" s="18" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1401:1c4947958496cf25), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1443:c602903462fb1760), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F204" s="18" t="inlineStr">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked. SURFACE RESTORED 2026-08-05: cli:"stop-guessing record emit" was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1369:fa724260dfc6fb61, sg:1375:dc5b338c7cf61d3e, sg:1377:f2e620b51f56ba80, sg:1391:9f29530c0b6bea25), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked. SURFACE RESTORED 2026-08-05: cli:"stop-guessing record emit" was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1411:516e8ab7a989c5c3, sg:1417:7f60548dce3e4726, sg:1419:473372eed5c569c1, sg:1433:b847d03253d43103), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F219" s="14" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="E220" s="18" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked. SURFACE RESTORED 2026-08-05: cli:"stop-guessing record emit" was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1369:fa724260dfc6fb61, sg:1375:dc5b338c7cf61d3e, sg:1377:f2e620b51f56ba80, sg:1391:9f29530c0b6bea25), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked. SURFACE RESTORED 2026-08-05: cli:"stop-guessing record emit" was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1411:516e8ab7a989c5c3, sg:1417:7f60548dce3e4726, sg:1419:473372eed5c569c1, sg:1433:b847d03253d43103), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F220" s="18" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="E229" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected. NARROWED 2026-08-04 (SG-HARD-006/007/010). This is no longer the broader claim that the recorder is unreachable by the agent it records. At the tiers the installer can actually deliver (0 and 1) the recorder runs under the agent's own uid, the chain key is a mode-600 file that anything the agent runs can read, and the socket authenticates ordering rather than the caller. The four named attacks are refused or detected. An agent that simply reads the key is not among them; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1369:fa724260dfc6fb61, sg:1371:8a2c9814c7c48cdd, sg:1373:056c5788b481d80e, sg:1389:1a1f9ee0a2a009e5, sg:1395:5769d2ad015984b2, sg:1403:5103275a02d42445), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected. NARROWED 2026-08-04 (SG-HARD-006/007/010). This is no longer the broader claim that the recorder is unreachable by the agent it records. At the tiers the installer can actually deliver (0 and 1) the recorder runs under the agent's own uid, the chain key is a mode-600 file that anything the agent runs can read, and the socket authenticates ordering rather than the caller. The four named attacks are refused or detected. An agent that simply reads the key is not among them; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1411:516e8ab7a989c5c3, sg:1413:29492e5380680e12, sg:1415:ee8af7599c8ffb39, sg:1431:0bc09f0056dc73f6, sg:1437:eca8ad675fe785ed, sg:1445:fc133e3424bda18b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F229" s="14" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="E255" s="14" t="inlineStr">
         <is>
-          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. SURFACE RESTORED 2026-08-05: hook:PreToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1385:71b5c8293bcf13bc), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. SURFACE RESTORED 2026-08-05: hook:PreToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1427:b11d95b6bceb8b87), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F255" s="14" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="E256" s="18" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1391:9f29530c0b6bea25), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1433:b847d03253d43103), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F256" s="18" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="E257" s="14" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1391:9f29530c0b6bea25), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1433:b847d03253d43103), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F257" s="14" t="inlineStr">

--- a/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
+++ b/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
@@ -2078,7 +2078,7 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration. SURFACE RESTORED 2026-08-05: hook:SessionStart was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. SURFACE RESTORED 2026-08-05: plugin:stop-guessing, skill:stop-guessing, command:/custody was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1419:473372eed5c569c1, sg:1435:071c785792443e03, sg:1447:a4353dcfd3a4edb6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration. SURFACE RESTORED 2026-08-05: hook:SessionStart was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. SURFACE RESTORED 2026-08-05: plugin:stop-guessing, skill:stop-guessing, command:/custody was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1461:e7cc6126236ac65b, sg:1477:dca5f77404ee6a35, sg:1489:b1e0ca04f461b2c0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration. SURFACE RESTORED 2026-08-05: hook:SessionStart was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. SURFACE RESTORED 2026-08-05: plugin:stop-guessing, skill:stop-guessing, command:/custody was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1419:473372eed5c569c1, sg:1435:071c785792443e03, sg:1447:a4353dcfd3a4edb6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration. SURFACE RESTORED 2026-08-05: hook:SessionStart was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. SURFACE RESTORED 2026-08-05: plugin:stop-guessing, skill:stop-guessing, command:/custody was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1461:e7cc6126236ac65b, sg:1477:dca5f77404ee6a35, sg:1489:b1e0ca04f461b2c0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F4" s="18" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
-          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. SURFACE RESTORED 2026-08-05: command:/no-noodle, command:/noodle-options was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1425:c2242747be45d536, sg:1439:5004a3e05273d055, sg:1441:6f8245510780eab0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. SURFACE RESTORED 2026-08-05: command:/no-noodle, command:/noodle-options was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1467:0584d45d76a63934, sg:1481:2dbfc7aa506461dd, sg:1483:ca8653cd01b651f9), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F44" s="18" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. SURFACE RESTORED 2026-08-05: command:/no-noodle, command:/noodle-options was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1425:c2242747be45d536, sg:1439:5004a3e05273d055, sg:1441:6f8245510780eab0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. SURFACE RESTORED 2026-08-05: command:/no-noodle, command:/noodle-options was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1467:0584d45d76a63934, sg:1481:2dbfc7aa506461dd, sg:1483:ca8653cd01b651f9), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE RESTORED 2026-08-05: hook:PostToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1409:98a3fa7e5522e981, sg:1443:c602903462fb1760), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE RESTORED 2026-08-05: hook:PostToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1451:b47381c648536197, sg:1485:c321c7b25edd65eb), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F112" s="18" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE RESTORED 2026-08-05: hook:PostToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1409:98a3fa7e5522e981, sg:1443:c602903462fb1760), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE RESTORED 2026-08-05: hook:PostToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1451:b47381c648536197, sg:1485:c321c7b25edd65eb), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F113" s="14" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="E130" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE RESTORED 2026-08-05: hook:PostToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted. SURFACE RESTORED 2026-08-05: cli:"stop-guessing demo --posture steer" was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read. SURFACE RESTORED 2026-08-05: hook:PreToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Under `bar` the model receives only a handle or summary, and an unsigned script is refused. SURFACE RESTORED 2026-08-05: hook:PreToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1409:98a3fa7e5522e981, sg:1421:7dc82ae505411ada, sg:1423:fe8489aef0034cc1, sg:1425:c2242747be45d536, sg:1427:b11d95b6bceb8b87, sg:1437:eca8ad675fe785ed), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE RESTORED 2026-08-05: hook:PostToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted. SURFACE RESTORED 2026-08-05: cli:"stop-guessing demo --posture steer" was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read. SURFACE RESTORED 2026-08-05: hook:PreToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Under `bar` the model receives only a handle or summary, and an unsigned script is refused. SURFACE RESTORED 2026-08-05: hook:PreToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1451:b47381c648536197, sg:1463:8d8bab12ee4081be, sg:1465:08702db24217888b, sg:1467:0584d45d76a63934, sg:1469:7270ea13b82dadcb, sg:1479:86fe43a9e97990e3), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F130" s="18" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1443:c602903462fb1760), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1485:c321c7b25edd65eb), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F203" s="14" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="E204" s="18" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1443:c602903462fb1760), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1485:c321c7b25edd65eb), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F204" s="18" t="inlineStr">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked. SURFACE RESTORED 2026-08-05: cli:"stop-guessing record emit" was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1411:516e8ab7a989c5c3, sg:1417:7f60548dce3e4726, sg:1419:473372eed5c569c1, sg:1433:b847d03253d43103), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked. SURFACE RESTORED 2026-08-05: cli:"stop-guessing record emit" was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1453:99e2337da1b42770, sg:1459:725af837a1edbd5d, sg:1461:e7cc6126236ac65b, sg:1475:fdc3575b6fdcdeca), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F219" s="14" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="E220" s="18" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked. SURFACE RESTORED 2026-08-05: cli:"stop-guessing record emit" was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1411:516e8ab7a989c5c3, sg:1417:7f60548dce3e4726, sg:1419:473372eed5c569c1, sg:1433:b847d03253d43103), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked. SURFACE RESTORED 2026-08-05: cli:"stop-guessing record emit" was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1453:99e2337da1b42770, sg:1459:725af837a1edbd5d, sg:1461:e7cc6126236ac65b, sg:1475:fdc3575b6fdcdeca), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F220" s="18" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="E229" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected. NARROWED 2026-08-04 (SG-HARD-006/007/010). This is no longer the broader claim that the recorder is unreachable by the agent it records. At the tiers the installer can actually deliver (0 and 1) the recorder runs under the agent's own uid, the chain key is a mode-600 file that anything the agent runs can read, and the socket authenticates ordering rather than the caller. The four named attacks are refused or detected. An agent that simply reads the key is not among them; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1411:516e8ab7a989c5c3, sg:1413:29492e5380680e12, sg:1415:ee8af7599c8ffb39, sg:1431:0bc09f0056dc73f6, sg:1437:eca8ad675fe785ed, sg:1445:fc133e3424bda18b), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected. NARROWED 2026-08-04 (SG-HARD-006/007/010). This is no longer the broader claim that the recorder is unreachable by the agent it records. At the tiers the installer can actually deliver (0 and 1) the recorder runs under the agent's own uid, the chain key is a mode-600 file that anything the agent runs can read, and the socket authenticates ordering rather than the caller. The four named attacks are refused or detected. An agent that simply reads the key is not among them; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1453:99e2337da1b42770, sg:1455:cb3428b0d3e9fcbe, sg:1457:3b2dcebc80d9819b, sg:1473:2ff0807cb078087f, sg:1479:86fe43a9e97990e3, sg:1487:1eca758caa70e29e), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F229" s="14" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="E255" s="14" t="inlineStr">
         <is>
-          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. SURFACE RESTORED 2026-08-05: hook:PreToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1427:b11d95b6bceb8b87), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. SURFACE RESTORED 2026-08-05: hook:PreToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1469:7270ea13b82dadcb), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F255" s="14" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="E256" s="18" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1433:b847d03253d43103), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1475:fdc3575b6fdcdeca), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F256" s="18" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="E257" s="14" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1433:b847d03253d43103), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1475:fdc3575b6fdcdeca), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F257" s="14" t="inlineStr">

--- a/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
+++ b/docs/ai-caiq/AI-CAIQ-stop-guessing-v1.1.0.xlsx
@@ -2078,7 +2078,7 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration. SURFACE RESTORED 2026-08-05: hook:SessionStart was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. SURFACE RESTORED 2026-08-05: plugin:stop-guessing, skill:stop-guessing, command:/custody was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1461:e7cc6126236ac65b, sg:1477:dca5f77404ee6a35, sg:1489:b1e0ca04f461b2c0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration. SURFACE RESTORED 2026-08-05: hook:SessionStart was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. SURFACE RESTORED 2026-08-05: plugin:stop-guessing, skill:stop-guessing, command:/custody was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1675:f71d929a7d5967c3, sg:1691:9eb174f2d48a08f1, sg:1703:8b70faeaaa7d68d9), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration. SURFACE RESTORED 2026-08-05: hook:SessionStart was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. SURFACE RESTORED 2026-08-05: plugin:stop-guessing, skill:stop-guessing, command:/custody was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1461:e7cc6126236ac65b, sg:1477:dca5f77404ee6a35, sg:1489:b1e0ca04f461b2c0), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>`verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; The carried AI-CAIQ version is inspected on every run by parsing cell A1's JSON blob, not by trusting the sheet name, and a drifted workbook refuses regeneration. SURFACE RESTORED 2026-08-05: hook:SessionStart was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; Every distributed surface — plugin, skill, slash-command and CLI — is accounted for by a live-run proof recorded in this toolchain's own ledger. NARROWED 2026-08-04 (SG-HARD-045). "Accounted for" is deliberately weaker than "exercised": CLI surfaces are invoked, but the proof accepts exit code 1 as a successful exercise, runs repository modules rather than a clean marketplace install, and establishes plugin, skill and command surfaces by manifest and file presence rather than by loading or invoking them. Clean-environment black-box matrices are required before this claims per-surface behaviour. SURFACE RESTORED 2026-08-05: plugin:stop-guessing, skill:stop-guessing, command:/custody was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1675:f71d929a7d5967c3, sg:1691:9eb174f2d48a08f1, sg:1703:8b70faeaaa7d68d9), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F4" s="18" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
-          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. SURFACE RESTORED 2026-08-05: command:/no-noodle, command:/noodle-options was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1467:0584d45d76a63934, sg:1481:2dbfc7aa506461dd, sg:1483:ca8653cd01b651f9), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. SURFACE RESTORED 2026-08-05: command:/no-noodle, command:/noodle-options was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1681:6e5395375b804b2f, sg:1695:fb9cbdfd82d66b60, sg:1697:b426ad05206fb126), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F44" s="18" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. SURFACE RESTORED 2026-08-05: command:/no-noodle, command:/noodle-options was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1467:0584d45d76a63934, sg:1481:2dbfc7aa506461dd, sg:1483:ca8653cd01b651f9), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Superseding no-noodles is byte-compatible: every payload in the corpus produces an identical (exit_code, stdout) through the dispatcher as through the standalone hooks; Every no-noodles surface keeps working after supersession — the three escape markers, the config chain, `grant_session_trust.sh`, `/no-noodle`, `/noodle-options`, and `risk_summary.py` parsing `observations.jsonl`. SURFACE RESTORED 2026-08-05: command:/no-noodle, command:/noodle-options was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false. Proven by 3 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1681:6e5395375b804b2f, sg:1695:fb9cbdfd82d66b60, sg:1697:b426ad05206fb126), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE RESTORED 2026-08-05: hook:PostToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1451:b47381c648536197, sg:1485:c321c7b25edd65eb), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE RESTORED 2026-08-05: hook:PostToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1665:16e56c3735f18f77, sg:1699:0af4d5ce9c015555), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F112" s="18" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE RESTORED 2026-08-05: hook:PostToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1451:b47381c648536197, sg:1485:c321c7b25edd65eb), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE RESTORED 2026-08-05: hook:PostToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 2 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1665:16e56c3735f18f77, sg:1699:0af4d5ce9c015555), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F113" s="14" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="E130" s="18" t="inlineStr">
         <is>
-          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE RESTORED 2026-08-05: hook:PostToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; Accumulated session taint denies an egress that the identical call would have been allowed to make earlier in the same session, the denial names the contributing artifacts, and this holds through the real hook across separate processes and with the state cache deleted. SURFACE RESTORED 2026-08-05: cli:"stop-guessing demo --posture steer" was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read. SURFACE RESTORED 2026-08-05: hook:PreToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Under `bar` the model receives only a handle or summary, and an unsigned script is refused. SURFACE RESTORED 2026-08-05: hook:PreToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1451:b47381c648536197, sg:1463:8d8bab12ee4081be, sg:1465:08702db24217888b, sg:1467:0584d45d76a63934, sg:1469:7270ea13b82dadcb, sg:1479:86fe43a9e97990e3), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>The ledger records data flow, not only actions: a read, a transform and a write are linked by an explicit derivation edge naming the artifacts and the script that joined them. SURFACE RESTORED 2026-08-05: hook:PostToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; `steer` asks on first touch of a classified artifact and offers a recorded script delegation; it does not deny the first read. SURFACE RESTORED 2026-08-05: hook:PreToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; The delegation sequence enforces test-before-live-data, and refuses a script whose digest changed after its test passed. NARROWED 2026-08-04 (SG-HARD-018/019). This holds against a cooperative script, not an adversarial one. The security subject is a mutable pathname, so a concurrent replacer can swap the bytes between the digest check and execution; and the paired test itself runs unsigned and can rewrite the script it has just certified. Immutable content-addressed execution is required before this is a security property rather than a discipline; Under `bar` the model receives only a handle or summary, and an unsigned script is refused. SURFACE RESTORED 2026-08-05: hook:PreToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration. Proven by 5 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1665:16e56c3735f18f77, sg:1679:b62fd3d582937eba, sg:1681:6e5395375b804b2f, sg:1683:cd4b91d1b9766f09, sg:1693:f187247e1601df73), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F130" s="18" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1485:c321c7b25edd65eb), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1699:0af4d5ce9c015555), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F203" s="14" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="E204" s="18" t="inlineStr">
         <is>
-          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1485:c321c7b25edd65eb), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>No statically detectable network call site exists in the shipped Python package except the named opt-in anchoring exception. This is a source audit, not a proof of no network activity. It cannot see indirect subprocess calls, shell network programs, dynamic imports or commands assembled at runtime. SUB-CLAIM WITHDRAWN 2026-08-04 (SG-HARD-039): this also asserted "and CI performs no fetch", which is false. CI runs actions/checkout, actions/setup-python and pip install, every one of which resolves a remote action or package. The proof equated the absence of literal curl and wget text with the absence of fetching. Build-time dependency retrieval is real and is not claimed away. SURFACE CORRECTED 2026-08-05 (R2-003/R2-039): this claim declared cli:"stop-guessing doctor --network", which the CLI does not provide — argparse rejects it. Replaced with cli:"stop-guessing doctor". A claim naming a command that does not exist is an overclaim, and it survived because non-hook surfaces were never executed. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1699:0af4d5ce9c015555), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F204" s="18" t="inlineStr">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked. SURFACE RESTORED 2026-08-05: cli:"stop-guessing record emit" was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1453:99e2337da1b42770, sg:1459:725af837a1edbd5d, sg:1461:e7cc6126236ac65b, sg:1475:fdc3575b6fdcdeca), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked. SURFACE RESTORED 2026-08-05: cli:"stop-guessing record emit" was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1667:8e27e4313b40297f, sg:1673:ce6cd25db9f16578, sg:1675:f71d929a7d5967c3, sg:1689:781c34056024c596), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F219" s="14" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="E220" s="18" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked. SURFACE RESTORED 2026-08-05: cli:"stop-guessing record emit" was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1453:99e2337da1b42770, sg:1459:725af837a1edbd5d, sg:1461:e7cc6126236ac65b, sg:1475:fdc3575b6fdcdeca), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; A record missing the `alterations` key is refused at write, while `alterations: []` is accepted — an empty list asserts nothing was altered, a missing key means nobody looked. SURFACE RESTORED 2026-08-05: cli:"stop-guessing record emit" was removed from this claim while closing an audit finding, which narrowed the assertion to fit the metric rather than reporting the gap. IMPLEMENTATION_PLAN.md §2.1 names plugins, skills and slash-commands as things that must be PROVEN TO RUN, and §15 names `demo` as the single command a reviewer runs. The surface is declared again and is NOT exercised: `surface_validated` is false because it is false; `verify --sufficiency` reports `incomplete` and names the unpopulated evidence regime rather than claiming sufficiency it cannot back; Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 4 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1667:8e27e4313b40297f, sg:1673:ce6cd25db9f16578, sg:1675:f71d929a7d5967c3, sg:1689:781c34056024c596), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F220" s="18" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="E229" s="14" t="inlineStr">
         <is>
-          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected. NARROWED 2026-08-04 (SG-HARD-006/007/010). This is no longer the broader claim that the recorder is unreachable by the agent it records. At the tiers the installer can actually deliver (0 and 1) the recorder runs under the agent's own uid, the chain key is a mode-600 file that anything the agent runs can read, and the socket authenticates ordering rather than the caller. The four named attacks are refused or detected. An agent that simply reads the key is not among them; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1453:99e2337da1b42770, sg:1455:cb3428b0d3e9fcbe, sg:1457:3b2dcebc80d9819b, sg:1473:2ff0807cb078087f, sg:1479:86fe43a9e97990e3, sg:1487:1eca758caa70e29e), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>A keyed chain defeats truncate-and-recompute. Without the session key held in the OS keychain, a forged chain that is internally consistent still fails verification; The sink refuses to append onto a broken or truncated chain, rather than burying the break under new entries; Sealing archives a segment and chains the next segment to the sealed digest; no ledger rotation ever truncates history; PATH-shadowing the CLI, direct ledger writes, hook-script substitution and daemon kill are each refused or detected. NARROWED 2026-08-04 (SG-HARD-006/007/010). This is no longer the broader claim that the recorder is unreachable by the agent it records. At the tiers the installer can actually deliver (0 and 1) the recorder runs under the agent's own uid, the chain key is a mode-600 file that anything the agent runs can read, and the socket authenticates ordering rather than the caller. The four named attacks are refused or detected. An agent that simply reads the key is not among them; The blank AI-CAIQ template is never modified. A fill leaves its digest and mtime unchanged, and an altered template refuses regeneration; A full uninstall removes hooks and registrations while preserving the accumulated ledger and observation log. Proven by 6 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1667:8e27e4313b40297f, sg:1669:2f71fdab9ba1686b, sg:1671:8e582742e2bf1dc7, sg:1687:e5679f0211aedefc, sg:1693:f187247e1601df73, sg:1701:0fdf83bf2a69e2e6), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F229" s="14" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="E255" s="14" t="inlineStr">
         <is>
-          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. SURFACE RESTORED 2026-08-05: hook:PreToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1469:7270ea13b82dadcb), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Under `bar` the model receives only a handle or summary, and an unsigned script is refused. SURFACE RESTORED 2026-08-05: hook:PreToolUse was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1683:cd4b91d1b9766f09), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F255" s="14" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="E256" s="18" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1475:fdc3575b6fdcdeca), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1689:781c34056024c596), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F256" s="18" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="E257" s="14" t="inlineStr">
         <is>
-          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1475:fdc3575b6fdcdeca), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
+          <t>Execution claims made by the agent are reconciled against the hook-side dispatch ledger; a fabricated or replayed claim is detected and escalated to a human. SURFACE RESTORED 2026-08-05: hook:Stop was withdrawn from this claim while closing an audit finding, which narrowed the claim to fit the metric instead of reporting that the proof does not drive the deployed hook. It is declared again and is NOT exercised, so this claim is UNPROVEN until a proof drives the hook in a real process. Proven by 1 record(s) in this toolchain's own keyed chain-of-custody ledger (sg:1689:781c34056024c596), each produced by an executable procedure and re-verified by `stop-guessing claims check`.</t>
         </is>
       </c>
       <c r="F257" s="14" t="inlineStr">
